--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E256FC-D1D2-479D-947A-A096D89AC52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D2BAAC-C70D-40E1-AF31-06BC38C4B3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="2" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
   <si>
     <t>Totales</t>
   </si>
@@ -216,9 +219,6 @@
   </si>
   <si>
     <t>Tasa cero Sillones</t>
-  </si>
-  <si>
-    <t>x</t>
   </si>
 </sst>
 </file>
@@ -713,6 +713,68 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="21" formatCode="d\-mmm"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -858,68 +920,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="d\-mmm"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -939,7 +939,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="28" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="13" tableBorderDxfId="12">
   <autoFilter ref="A2:K14" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K14">
     <sortCondition ref="D3:D14"/>
@@ -947,15 +947,15 @@
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{4E2F1548-5DA7-4ADC-946F-053ED807460A}" name="Banco"/>
     <tableColumn id="2" xr3:uid="{11D77EA7-239F-47E1-9378-FFBA07ACDD06}" name="Tarjeta"/>
-    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="24"/>
-    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="23"/>
-    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="18" dataCellStyle="Porcentaje"/>
+    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="3" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1259,16 +1259,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0DE2A9-9218-4E10-883D-DF66D771FC39}">
   <dimension ref="B1:H37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="3.109375" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="3.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
         <v>14</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
@@ -1307,11 +1307,8 @@
       <c r="F3" s="8">
         <v>50</v>
       </c>
-      <c r="G3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
@@ -1325,7 +1322,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
@@ -1339,7 +1336,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
@@ -1353,7 +1350,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>17</v>
       </c>
@@ -1366,11 +1363,8 @@
       <c r="F7" s="8">
         <v>100</v>
       </c>
-      <c r="G7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -1381,7 +1375,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -1392,7 +1386,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -1400,7 +1394,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -1410,11 +1404,8 @@
       <c r="F11">
         <v>25</v>
       </c>
-      <c r="G11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>9</v>
       </c>
@@ -1427,14 +1418,11 @@
       <c r="F12">
         <v>5</v>
       </c>
-      <c r="G12" t="s">
-        <v>60</v>
-      </c>
       <c r="H12">
         <v>8286917</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>10</v>
       </c>
@@ -1442,7 +1430,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>15</v>
       </c>
@@ -1452,11 +1440,8 @@
       <c r="F14">
         <v>31</v>
       </c>
-      <c r="G14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>59</v>
       </c>
@@ -1467,7 +1452,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="7" t="s">
         <v>11</v>
       </c>
@@ -1481,7 +1466,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
         <v>12</v>
       </c>
@@ -1494,7 +1479,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>13</v>
       </c>
@@ -1508,24 +1493,24 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="37" ht="30.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
       <formula>$C$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
       <formula>$C$7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="equal">
       <formula>$C$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="4" operator="equal">
       <formula>$C$2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1537,22 +1522,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B43D18-F407-4702-B159-A2C7E22E2016}">
   <dimension ref="A1:N131"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" style="19" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" style="12" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" style="12" customWidth="1"/>
-    <col min="7" max="8" width="16.109375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" style="10" customWidth="1"/>
-    <col min="10" max="10" width="17.44140625" style="12" customWidth="1"/>
-    <col min="11" max="11" width="7.109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" style="12" customWidth="1"/>
+    <col min="7" max="8" width="16.140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" style="10" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" style="12" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" style="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>19</v>
       </c>
@@ -1587,7 +1572,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
         <v>40</v>
       </c>
@@ -1610,7 +1595,7 @@
       <c r="J3" s="42"/>
       <c r="K3" s="43"/>
     </row>
-    <row r="4" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="34" t="s">
         <v>56</v>
       </c>
@@ -1633,7 +1618,7 @@
       <c r="J4" s="37"/>
       <c r="K4" s="38"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -1651,14 +1636,14 @@
         <v>46118</v>
       </c>
       <c r="J5" s="12">
-        <v>586.71</v>
+        <v>612.54</v>
       </c>
       <c r="K5" s="31">
         <v>0.27900000000000003</v>
       </c>
       <c r="N5" s="4"/>
     </row>
-    <row r="6" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1683,7 +1668,7 @@
       </c>
       <c r="K6" s="31"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -1705,7 +1690,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
         <v>39</v>
       </c>
@@ -1728,7 +1713,7 @@
       <c r="J8" s="37"/>
       <c r="K8" s="38"/>
     </row>
-    <row r="9" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
         <v>29</v>
       </c>
@@ -1751,7 +1736,7 @@
       <c r="J9" s="44"/>
       <c r="K9" s="54"/>
     </row>
-    <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1774,7 +1759,7 @@
       <c r="J10" s="12"/>
       <c r="K10" s="31"/>
     </row>
-    <row r="11" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
         <v>29</v>
       </c>
@@ -1797,7 +1782,7 @@
       <c r="J11" s="37"/>
       <c r="K11" s="38"/>
     </row>
-    <row r="12" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
         <v>58</v>
       </c>
@@ -1820,7 +1805,7 @@
       <c r="J12" s="42"/>
       <c r="K12" s="43"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="39" t="s">
         <v>58</v>
       </c>
@@ -1841,7 +1826,7 @@
         <v>45946</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -1863,19 +1848,19 @@
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUM(J3:J13)</f>
-        <v>647.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+        <v>673.32999999999993</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D15" s="20"/>
       <c r="I15" s="20"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D16" s="20"/>
       <c r="I16" s="20"/>
     </row>
-    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1894,30 +1879,28 @@
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
     </row>
-    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B18" s="57">
-        <v>520</v>
-      </c>
-      <c r="C18" s="2">
-        <v>30</v>
-      </c>
-      <c r="D18" s="2">
-        <v>60</v>
-      </c>
-      <c r="E18" s="2"/>
+        <v>523</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2">
+        <v>285</v>
+      </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="22"/>
       <c r="J18" s="23">
         <f>SUM(B18:I18)</f>
-        <v>610</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="55"/>
@@ -1926,509 +1909,509 @@
       <c r="H19" s="2"/>
       <c r="I19" s="20"/>
     </row>
-    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D20" s="12"/>
       <c r="H20" s="56" t="s">
         <v>37</v>
       </c>
       <c r="I20" s="25">
         <f>+H14+J14+G14</f>
-        <v>647.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>673.32999999999993</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D21" s="12"/>
       <c r="H21" s="26" t="s">
         <v>38</v>
       </c>
       <c r="I21" s="25">
         <f>+J18-H14-G14</f>
-        <v>610</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D22" s="20"/>
       <c r="H22" s="27" t="s">
         <v>54</v>
       </c>
       <c r="I22" s="25">
         <f>+I21-J14</f>
-        <v>-37.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+        <v>134.67000000000007</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D23" s="12"/>
       <c r="I23" s="20"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D24" s="12"/>
       <c r="I24" s="20"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D25" s="12"/>
       <c r="I25" s="20"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D26" s="12"/>
       <c r="I26" s="20"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D27" s="12"/>
       <c r="I27" s="20"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D28" s="12"/>
       <c r="I28" s="20"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D29" s="12"/>
       <c r="I29" s="20"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D30" s="11"/>
       <c r="I30" s="20"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D31" s="20"/>
       <c r="I31" s="20"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D32" s="11"/>
       <c r="I32" s="20"/>
     </row>
-    <row r="33" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D33" s="11"/>
       <c r="I33" s="20"/>
     </row>
-    <row r="34" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D34" s="11"/>
       <c r="I34" s="20"/>
     </row>
-    <row r="35" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D35" s="11"/>
       <c r="I35" s="20"/>
     </row>
-    <row r="36" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D36" s="11"/>
       <c r="I36" s="20"/>
     </row>
-    <row r="37" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D37" s="11"/>
       <c r="I37" s="20"/>
     </row>
-    <row r="38" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D38" s="11"/>
       <c r="I38" s="20"/>
     </row>
-    <row r="39" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D39" s="11"/>
       <c r="I39" s="20"/>
     </row>
-    <row r="40" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D40" s="11"/>
       <c r="I40" s="20"/>
     </row>
-    <row r="41" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D41" s="20"/>
       <c r="I41" s="20"/>
     </row>
-    <row r="42" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D42" s="12"/>
       <c r="I42" s="20"/>
     </row>
-    <row r="43" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D43" s="12"/>
       <c r="I43" s="20"/>
     </row>
-    <row r="44" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D44" s="20"/>
       <c r="I44" s="20"/>
     </row>
-    <row r="45" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D45" s="20"/>
       <c r="I45" s="20"/>
     </row>
-    <row r="46" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D46" s="20"/>
       <c r="I46" s="20"/>
     </row>
-    <row r="47" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D47" s="20"/>
       <c r="I47" s="20"/>
     </row>
-    <row r="48" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D48" s="20"/>
       <c r="I48" s="20"/>
     </row>
-    <row r="49" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D49" s="20"/>
       <c r="I49" s="20"/>
     </row>
-    <row r="50" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D50" s="20"/>
       <c r="I50" s="20"/>
     </row>
-    <row r="51" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D51" s="20"/>
       <c r="I51" s="20"/>
     </row>
-    <row r="52" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D52" s="20"/>
       <c r="I52" s="20"/>
     </row>
-    <row r="53" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D53" s="20"/>
       <c r="I53" s="20"/>
     </row>
-    <row r="54" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D54" s="20"/>
       <c r="I54" s="20"/>
     </row>
-    <row r="55" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D55" s="20"/>
       <c r="I55" s="20"/>
     </row>
-    <row r="56" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D56" s="20"/>
       <c r="I56" s="20"/>
     </row>
-    <row r="57" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D57" s="20"/>
       <c r="I57" s="20"/>
     </row>
-    <row r="58" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D58" s="20"/>
       <c r="I58" s="20"/>
     </row>
-    <row r="59" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D59" s="20"/>
       <c r="I59" s="20"/>
     </row>
-    <row r="60" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D60" s="20"/>
       <c r="I60" s="20"/>
     </row>
-    <row r="61" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D61" s="20"/>
       <c r="I61" s="20"/>
     </row>
-    <row r="62" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D62" s="20"/>
       <c r="I62" s="20"/>
     </row>
-    <row r="63" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D63" s="20"/>
       <c r="I63" s="20"/>
     </row>
-    <row r="64" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D64" s="20"/>
       <c r="I64" s="20"/>
     </row>
-    <row r="65" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D65" s="20"/>
       <c r="I65" s="20"/>
     </row>
-    <row r="66" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D66" s="20"/>
       <c r="I66" s="20"/>
     </row>
-    <row r="67" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D67" s="20"/>
       <c r="I67" s="20"/>
     </row>
-    <row r="68" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D68" s="20"/>
       <c r="I68" s="20"/>
     </row>
-    <row r="69" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D69" s="20"/>
       <c r="I69" s="20"/>
     </row>
-    <row r="70" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D70" s="20"/>
       <c r="I70" s="20"/>
     </row>
-    <row r="71" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D71" s="20"/>
       <c r="I71" s="20"/>
     </row>
-    <row r="72" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D72" s="20"/>
       <c r="I72" s="20"/>
     </row>
-    <row r="73" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D73" s="20"/>
       <c r="I73" s="20"/>
     </row>
-    <row r="74" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D74" s="20"/>
       <c r="I74" s="20"/>
     </row>
-    <row r="75" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D75" s="20"/>
       <c r="I75" s="20"/>
     </row>
-    <row r="76" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D76" s="20"/>
       <c r="I76" s="20"/>
     </row>
-    <row r="77" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D77" s="20"/>
       <c r="I77" s="20"/>
     </row>
-    <row r="78" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D78" s="20"/>
       <c r="I78" s="20"/>
     </row>
-    <row r="79" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D79" s="20"/>
       <c r="I79" s="20"/>
     </row>
-    <row r="80" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D80" s="20"/>
       <c r="I80" s="20"/>
     </row>
-    <row r="81" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D81" s="20"/>
       <c r="I81" s="20"/>
     </row>
-    <row r="82" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D82" s="20"/>
       <c r="I82" s="20"/>
     </row>
-    <row r="83" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D83" s="20"/>
       <c r="I83" s="20"/>
     </row>
-    <row r="84" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D84" s="20"/>
       <c r="I84" s="20"/>
     </row>
-    <row r="85" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D85" s="20"/>
       <c r="I85" s="20"/>
     </row>
-    <row r="86" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D86" s="20"/>
       <c r="I86" s="20"/>
     </row>
-    <row r="87" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D87" s="20"/>
       <c r="I87" s="20"/>
     </row>
-    <row r="88" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D88" s="20"/>
       <c r="I88" s="20"/>
     </row>
-    <row r="89" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D89" s="20"/>
       <c r="I89" s="20"/>
     </row>
-    <row r="90" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D90" s="20"/>
       <c r="I90" s="20"/>
     </row>
-    <row r="91" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D91" s="20"/>
       <c r="I91" s="20"/>
     </row>
-    <row r="92" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D92" s="20"/>
       <c r="I92" s="20"/>
     </row>
-    <row r="93" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D93" s="20"/>
       <c r="I93" s="20"/>
     </row>
-    <row r="94" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D94" s="20"/>
       <c r="I94" s="20"/>
     </row>
-    <row r="95" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D95" s="20"/>
       <c r="I95" s="20"/>
     </row>
-    <row r="96" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D96" s="20"/>
       <c r="I96" s="20"/>
     </row>
-    <row r="97" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D97" s="20"/>
       <c r="I97" s="20"/>
     </row>
-    <row r="98" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D98" s="20"/>
       <c r="I98" s="20"/>
     </row>
-    <row r="99" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D99" s="20"/>
       <c r="I99" s="20"/>
     </row>
-    <row r="100" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D100" s="20"/>
       <c r="I100" s="20"/>
     </row>
-    <row r="101" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D101" s="20"/>
       <c r="I101" s="20"/>
     </row>
-    <row r="102" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D102" s="20"/>
       <c r="I102" s="20"/>
     </row>
-    <row r="103" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D103" s="20"/>
       <c r="I103" s="20"/>
     </row>
-    <row r="104" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D104" s="20"/>
       <c r="I104" s="20"/>
     </row>
-    <row r="105" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D105" s="20"/>
       <c r="I105" s="20"/>
     </row>
-    <row r="106" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D106" s="20"/>
       <c r="I106" s="20"/>
     </row>
-    <row r="107" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D107" s="20"/>
       <c r="I107" s="20"/>
     </row>
-    <row r="108" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D108" s="20"/>
       <c r="I108" s="20"/>
     </row>
-    <row r="109" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D109" s="20"/>
       <c r="I109" s="20"/>
     </row>
-    <row r="110" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D110" s="20"/>
       <c r="I110" s="20"/>
     </row>
-    <row r="111" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D111" s="20"/>
       <c r="I111" s="20"/>
     </row>
-    <row r="112" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D112" s="20"/>
       <c r="I112" s="20"/>
     </row>
-    <row r="113" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D113" s="20"/>
       <c r="I113" s="20"/>
     </row>
-    <row r="114" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D114" s="20"/>
       <c r="I114" s="20"/>
     </row>
-    <row r="115" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D115" s="20"/>
       <c r="I115" s="20"/>
     </row>
-    <row r="116" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D116" s="20"/>
       <c r="I116" s="20"/>
     </row>
-    <row r="117" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D117" s="20"/>
       <c r="I117" s="20"/>
     </row>
-    <row r="118" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D118" s="20"/>
       <c r="I118" s="20"/>
     </row>
-    <row r="119" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D119" s="20"/>
       <c r="I119" s="20"/>
     </row>
-    <row r="120" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D120" s="20"/>
       <c r="I120" s="20"/>
     </row>
-    <row r="121" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D121" s="20"/>
       <c r="I121" s="20"/>
     </row>
-    <row r="122" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D122" s="20"/>
       <c r="I122" s="20"/>
     </row>
-    <row r="123" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D123" s="20"/>
       <c r="I123" s="20"/>
     </row>
-    <row r="124" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D124" s="20"/>
       <c r="I124" s="20"/>
     </row>
-    <row r="125" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D125" s="20"/>
       <c r="I125" s="20"/>
     </row>
-    <row r="126" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I126" s="20"/>
     </row>
-    <row r="127" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I127" s="20"/>
     </row>
-    <row r="128" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I128" s="20"/>
     </row>
-    <row r="129" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I129" s="20"/>
     </row>
-    <row r="130" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I130" s="20"/>
     </row>
-    <row r="131" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I131" s="20"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D16">
-    <cfRule type="timePeriod" dxfId="13" priority="37" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="24" priority="37" timePeriod="nextMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0+1)),YEAR(D1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="12" priority="38" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="23" priority="38" timePeriod="thisMonth">
       <formula>AND(MONTH(D1)=MONTH(TODAY()),YEAR(D1)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="11" priority="39" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="22" priority="39" timePeriod="lastMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0-1)),YEAR(D1)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D22:D29 D31 D41:D1048576">
-    <cfRule type="timePeriod" dxfId="10" priority="1" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="21" priority="1" timePeriod="nextMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0+1)),YEAR(D22)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="9" priority="2" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="20" priority="2" timePeriod="thisMonth">
       <formula>AND(MONTH(D22)=MONTH(TODAY()),YEAR(D22)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="8" priority="3" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="19" priority="3" timePeriod="lastMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0-1)),YEAR(D22)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="timePeriod" dxfId="7" priority="40" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="18" priority="40" timePeriod="nextMonth">
       <formula>AND(MONTH(I1)=MONTH(EDATE(TODAY(),0+1)),YEAR(I1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="6" priority="41" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="17" priority="41" timePeriod="thisMonth">
       <formula>AND(MONTH(I1)=MONTH(TODAY()),YEAR(I1)=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="cellIs" dxfId="5" priority="45" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="45" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I22">
-    <cfRule type="cellIs" dxfId="4" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="42" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
-    <cfRule type="cellIs" dxfId="3" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="43" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2443,14 +2426,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAE522B-09DD-4490-9CA8-387DE173331A}">
   <dimension ref="A1:G62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
-    <col min="2" max="3" width="11.44140625" style="12"/>
-    <col min="4" max="4" width="11.88671875" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="11.42578125" style="12"/>
+    <col min="4" max="4" width="11.85546875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
         <v>49</v>
       </c>
@@ -2461,20 +2444,18 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="47"/>
       <c r="B2" s="11">
         <v>0</v>
       </c>
-      <c r="C2" s="11">
-        <v>250</v>
-      </c>
+      <c r="C2" s="11"/>
       <c r="D2" t="b">
         <f t="shared" ref="D2:D28" ca="1" si="0">AND(TEXT(A2,"mm-yyyy")=TEXT(TODAY()-DAY(TODAY()-1),"mm-yyyy"), C2&gt;=B2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="47">
         <v>46037</v>
       </c>
@@ -2482,14 +2463,14 @@
         <v>75</v>
       </c>
       <c r="C3" s="11">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="D3" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="47">
         <v>46053</v>
       </c>
@@ -2504,7 +2485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="47">
         <v>46068</v>
       </c>
@@ -2519,7 +2500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="47">
         <v>46081</v>
       </c>
@@ -2534,7 +2515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="47">
         <v>46096</v>
       </c>
@@ -2553,7 +2534,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="47">
         <v>46112</v>
       </c>
@@ -2572,7 +2553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="47">
         <v>46127</v>
       </c>
@@ -2591,7 +2572,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="47">
         <v>46142</v>
       </c>
@@ -2610,7 +2591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="47">
         <v>46157</v>
       </c>
@@ -2629,7 +2610,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="47">
         <v>46173</v>
       </c>
@@ -2648,7 +2629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="47">
         <v>46188</v>
       </c>
@@ -2671,7 +2652,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="47">
         <v>46203</v>
       </c>
@@ -2684,7 +2665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="47">
         <v>46218</v>
       </c>
@@ -2697,7 +2678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="47">
         <v>46234</v>
       </c>
@@ -2710,7 +2691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="47">
         <v>46249</v>
       </c>
@@ -2723,7 +2704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="47">
         <v>46265</v>
       </c>
@@ -2736,7 +2717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="47">
         <v>46280</v>
       </c>
@@ -2749,7 +2730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="47">
         <v>46295</v>
       </c>
@@ -2762,7 +2743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="47">
         <v>46310</v>
       </c>
@@ -2775,7 +2756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="47">
         <v>46326</v>
       </c>
@@ -2788,7 +2769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="47">
         <v>46341</v>
       </c>
@@ -2801,7 +2782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="47">
         <v>46356</v>
       </c>
@@ -2814,7 +2795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="47">
         <v>46371</v>
       </c>
@@ -2827,7 +2808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="46" t="s">
         <v>50</v>
       </c>
@@ -2840,7 +2821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="46" t="s">
         <v>51</v>
       </c>
@@ -2853,7 +2834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="47">
         <v>46387</v>
       </c>
@@ -2866,7 +2847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="47">
         <v>46402</v>
       </c>
@@ -2879,7 +2860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="47">
         <v>46418</v>
       </c>
@@ -2892,7 +2873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="47">
         <v>46433</v>
       </c>
@@ -2905,7 +2886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="47">
         <v>46446</v>
       </c>
@@ -2918,7 +2899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="47">
         <v>46461</v>
       </c>
@@ -2931,7 +2912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="47">
         <v>46477</v>
       </c>
@@ -2944,7 +2925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="47">
         <v>46492</v>
       </c>
@@ -2957,7 +2938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="47">
         <v>46507</v>
       </c>
@@ -2970,7 +2951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="47">
         <v>46522</v>
       </c>
@@ -2983,7 +2964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="47">
         <v>46538</v>
       </c>
@@ -2996,7 +2977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="47">
         <v>46553</v>
       </c>
@@ -3009,7 +2990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="47">
         <v>46568</v>
       </c>
@@ -3022,7 +3003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="47">
         <v>46583</v>
       </c>
@@ -3035,7 +3016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="47">
         <v>46599</v>
       </c>
@@ -3048,7 +3029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="47">
         <v>46614</v>
       </c>
@@ -3061,7 +3042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="47">
         <v>46630</v>
       </c>
@@ -3074,7 +3055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="47">
         <v>46645</v>
       </c>
@@ -3087,7 +3068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="47">
         <v>46660</v>
       </c>
@@ -3100,7 +3081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="47">
         <v>46675</v>
       </c>
@@ -3113,7 +3094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="47">
         <v>46691</v>
       </c>
@@ -3126,7 +3107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="47">
         <v>46706</v>
       </c>
@@ -3139,7 +3120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="47">
         <v>46721</v>
       </c>
@@ -3152,7 +3133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="47">
         <v>46736</v>
       </c>
@@ -3165,7 +3146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="46" t="s">
         <v>50</v>
       </c>
@@ -3178,7 +3159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="46" t="s">
         <v>51</v>
       </c>
@@ -3191,7 +3172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="47">
         <v>46752</v>
       </c>
@@ -3204,44 +3185,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="50">
         <f>SUM(B2:B54)</f>
         <v>4610</v>
       </c>
       <c r="C55" s="51">
         <f>SUM(C2:C54)</f>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
     </row>
-    <row r="57" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="60">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
-        <v>-70</v>
+        <v>-160</v>
       </c>
       <c r="C57" s="61"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B58" s="59"/>
       <c r="C58" s="3"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B59"/>
       <c r="C59" s="3"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
     </row>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D2BAAC-C70D-40E1-AF31-06BC38C4B3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC02230-E1B3-4212-99F3-7D0941DD1F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="2" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -30,9 +30,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -687,6 +684,10 @@
   </cellStyles>
   <dxfs count="29">
     <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -710,68 +711,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="21" formatCode="d\-mmm"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -920,6 +859,64 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="d\-mmm"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -939,7 +936,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="13" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="28" tableBorderDxfId="27">
   <autoFilter ref="A2:K14" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K14">
     <sortCondition ref="D3:D14"/>
@@ -947,15 +944,17 @@
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{4E2F1548-5DA7-4ADC-946F-053ED807460A}" name="Banco"/>
     <tableColumn id="2" xr3:uid="{11D77EA7-239F-47E1-9378-FFBA07ACDD06}" name="Tarjeta"/>
-    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="3" dataCellStyle="Porcentaje"/>
+    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="0">
+      <calculatedColumnFormula>186.68-48</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="19" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1259,16 +1258,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0DE2A9-9218-4E10-883D-DF66D771FC39}">
   <dimension ref="B1:H37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="3.140625" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="3.109375" customWidth="1"/>
+    <col min="6" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1" s="13" t="s">
         <v>14</v>
       </c>
@@ -1280,7 +1279,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1294,7 +1293,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
@@ -1308,7 +1307,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
@@ -1322,7 +1321,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
@@ -1336,7 +1335,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
@@ -1350,7 +1349,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="9" t="s">
         <v>17</v>
       </c>
@@ -1364,7 +1363,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -1375,7 +1374,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -1386,7 +1385,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -1394,7 +1393,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -1405,7 +1404,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>9</v>
       </c>
@@ -1422,7 +1421,7 @@
         <v>8286917</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>10</v>
       </c>
@@ -1430,7 +1429,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>15</v>
       </c>
@@ -1441,7 +1440,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>59</v>
       </c>
@@ -1452,7 +1451,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>11</v>
       </c>
@@ -1466,7 +1465,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="s">
         <v>12</v>
       </c>
@@ -1479,7 +1478,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="5" t="s">
         <v>13</v>
       </c>
@@ -1493,24 +1492,24 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="37" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="30.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>$C$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
       <formula>$C$7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
       <formula>$C$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="equal">
       <formula>$C$2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1522,22 +1521,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B43D18-F407-4702-B159-A2C7E22E2016}">
   <dimension ref="A1:N131"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="19" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="12" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" style="12" customWidth="1"/>
-    <col min="7" max="8" width="16.140625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" style="10" customWidth="1"/>
-    <col min="10" max="10" width="17.42578125" style="12" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" style="19" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" style="12" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" style="12" customWidth="1"/>
+    <col min="7" max="8" width="16.109375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" style="10" customWidth="1"/>
+    <col min="10" max="10" width="17.44140625" style="12" customWidth="1"/>
+    <col min="11" max="11" width="7.109375" style="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
         <v>19</v>
       </c>
@@ -1572,7 +1571,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="39" t="s">
         <v>40</v>
       </c>
@@ -1595,7 +1594,7 @@
       <c r="J3" s="42"/>
       <c r="K3" s="43"/>
     </row>
-    <row r="4" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="34" t="s">
         <v>56</v>
       </c>
@@ -1618,7 +1617,7 @@
       <c r="J4" s="37"/>
       <c r="K4" s="38"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -1635,15 +1634,12 @@
       <c r="I5" s="20">
         <v>46118</v>
       </c>
-      <c r="J5" s="12">
-        <v>612.54</v>
-      </c>
       <c r="K5" s="31">
         <v>0.27900000000000003</v>
       </c>
       <c r="N5" s="4"/>
     </row>
-    <row r="6" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1663,12 +1659,10 @@
       <c r="I6" s="20">
         <v>46118</v>
       </c>
-      <c r="J6" s="12">
-        <v>60.79</v>
-      </c>
+      <c r="J6" s="12"/>
       <c r="K6" s="31"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -1690,7 +1684,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34" t="s">
         <v>39</v>
       </c>
@@ -1713,7 +1707,7 @@
       <c r="J8" s="37"/>
       <c r="K8" s="38"/>
     </row>
-    <row r="9" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="52" t="s">
         <v>29</v>
       </c>
@@ -1736,7 +1730,7 @@
       <c r="J9" s="44"/>
       <c r="K9" s="54"/>
     </row>
-    <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1759,7 +1753,7 @@
       <c r="J10" s="12"/>
       <c r="K10" s="31"/>
     </row>
-    <row r="11" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
         <v>29</v>
       </c>
@@ -1782,7 +1776,7 @@
       <c r="J11" s="37"/>
       <c r="K11" s="38"/>
     </row>
-    <row r="12" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="39" t="s">
         <v>58</v>
       </c>
@@ -1805,7 +1799,7 @@
       <c r="J12" s="42"/>
       <c r="K12" s="43"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="39" t="s">
         <v>58</v>
       </c>
@@ -1816,7 +1810,8 @@
         <v>45798</v>
       </c>
       <c r="E13" s="12">
-        <v>280</v>
+        <f t="shared" ref="E3:E14" si="0">186.68-48</f>
+        <v>138.68</v>
       </c>
       <c r="F13" s="12">
         <v>47.51</v>
@@ -1826,7 +1821,7 @@
         <v>45946</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -1835,32 +1830,35 @@
         <v>14335</v>
       </c>
       <c r="D14" s="20"/>
-      <c r="E14" s="21"/>
+      <c r="E14" s="21">
+        <f>SUBTOTAL(109,E3:E13)</f>
+        <v>138.68</v>
+      </c>
       <c r="F14" s="21"/>
       <c r="G14" s="21">
         <f>SUM(G3:G13)</f>
         <v>0</v>
       </c>
       <c r="H14" s="21">
-        <f>SUM(H3:H13)</f>
+        <f>SUBTOTAL(109,H3:H13)</f>
         <v>0</v>
       </c>
       <c r="I14" s="21"/>
       <c r="J14" s="21">
-        <f>SUM(J3:J13)</f>
-        <v>673.32999999999993</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+        <f>SUBTOTAL(109,J3:J13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D15" s="20"/>
       <c r="I15" s="20"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D16" s="20"/>
       <c r="I16" s="20"/>
     </row>
-    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1879,28 +1877,24 @@
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
     </row>
-    <row r="18" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="57">
-        <v>523</v>
-      </c>
+      <c r="B18" s="57"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="2">
-        <v>285</v>
-      </c>
+      <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="22"/>
       <c r="J18" s="23">
         <f>SUM(B18:I18)</f>
-        <v>808</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="55"/>
@@ -1909,509 +1903,509 @@
       <c r="H19" s="2"/>
       <c r="I19" s="20"/>
     </row>
-    <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D20" s="12"/>
       <c r="H20" s="56" t="s">
         <v>37</v>
       </c>
       <c r="I20" s="25">
         <f>+H14+J14+G14</f>
-        <v>673.32999999999993</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D21" s="12"/>
       <c r="H21" s="26" t="s">
         <v>38</v>
       </c>
       <c r="I21" s="25">
         <f>+J18-H14-G14</f>
-        <v>808</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D22" s="20"/>
       <c r="H22" s="27" t="s">
         <v>54</v>
       </c>
       <c r="I22" s="25">
         <f>+I21-J14</f>
-        <v>134.67000000000007</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D23" s="12"/>
       <c r="I23" s="20"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D24" s="12"/>
       <c r="I24" s="20"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D25" s="12"/>
       <c r="I25" s="20"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D26" s="12"/>
       <c r="I26" s="20"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D27" s="12"/>
       <c r="I27" s="20"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D28" s="12"/>
       <c r="I28" s="20"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D29" s="12"/>
       <c r="I29" s="20"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D30" s="11"/>
       <c r="I30" s="20"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D31" s="20"/>
       <c r="I31" s="20"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D32" s="11"/>
       <c r="I32" s="20"/>
     </row>
-    <row r="33" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D33" s="11"/>
       <c r="I33" s="20"/>
     </row>
-    <row r="34" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D34" s="11"/>
       <c r="I34" s="20"/>
     </row>
-    <row r="35" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D35" s="11"/>
       <c r="I35" s="20"/>
     </row>
-    <row r="36" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D36" s="11"/>
       <c r="I36" s="20"/>
     </row>
-    <row r="37" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D37" s="11"/>
       <c r="I37" s="20"/>
     </row>
-    <row r="38" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D38" s="11"/>
       <c r="I38" s="20"/>
     </row>
-    <row r="39" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D39" s="11"/>
       <c r="I39" s="20"/>
     </row>
-    <row r="40" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D40" s="11"/>
       <c r="I40" s="20"/>
     </row>
-    <row r="41" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D41" s="20"/>
       <c r="I41" s="20"/>
     </row>
-    <row r="42" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D42" s="12"/>
       <c r="I42" s="20"/>
     </row>
-    <row r="43" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D43" s="12"/>
       <c r="I43" s="20"/>
     </row>
-    <row r="44" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D44" s="20"/>
       <c r="I44" s="20"/>
     </row>
-    <row r="45" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D45" s="20"/>
       <c r="I45" s="20"/>
     </row>
-    <row r="46" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D46" s="20"/>
       <c r="I46" s="20"/>
     </row>
-    <row r="47" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D47" s="20"/>
       <c r="I47" s="20"/>
     </row>
-    <row r="48" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D48" s="20"/>
       <c r="I48" s="20"/>
     </row>
-    <row r="49" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D49" s="20"/>
       <c r="I49" s="20"/>
     </row>
-    <row r="50" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D50" s="20"/>
       <c r="I50" s="20"/>
     </row>
-    <row r="51" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D51" s="20"/>
       <c r="I51" s="20"/>
     </row>
-    <row r="52" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D52" s="20"/>
       <c r="I52" s="20"/>
     </row>
-    <row r="53" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D53" s="20"/>
       <c r="I53" s="20"/>
     </row>
-    <row r="54" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D54" s="20"/>
       <c r="I54" s="20"/>
     </row>
-    <row r="55" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D55" s="20"/>
       <c r="I55" s="20"/>
     </row>
-    <row r="56" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D56" s="20"/>
       <c r="I56" s="20"/>
     </row>
-    <row r="57" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D57" s="20"/>
       <c r="I57" s="20"/>
     </row>
-    <row r="58" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D58" s="20"/>
       <c r="I58" s="20"/>
     </row>
-    <row r="59" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D59" s="20"/>
       <c r="I59" s="20"/>
     </row>
-    <row r="60" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D60" s="20"/>
       <c r="I60" s="20"/>
     </row>
-    <row r="61" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D61" s="20"/>
       <c r="I61" s="20"/>
     </row>
-    <row r="62" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D62" s="20"/>
       <c r="I62" s="20"/>
     </row>
-    <row r="63" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D63" s="20"/>
       <c r="I63" s="20"/>
     </row>
-    <row r="64" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D64" s="20"/>
       <c r="I64" s="20"/>
     </row>
-    <row r="65" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D65" s="20"/>
       <c r="I65" s="20"/>
     </row>
-    <row r="66" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D66" s="20"/>
       <c r="I66" s="20"/>
     </row>
-    <row r="67" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D67" s="20"/>
       <c r="I67" s="20"/>
     </row>
-    <row r="68" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D68" s="20"/>
       <c r="I68" s="20"/>
     </row>
-    <row r="69" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D69" s="20"/>
       <c r="I69" s="20"/>
     </row>
-    <row r="70" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D70" s="20"/>
       <c r="I70" s="20"/>
     </row>
-    <row r="71" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D71" s="20"/>
       <c r="I71" s="20"/>
     </row>
-    <row r="72" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D72" s="20"/>
       <c r="I72" s="20"/>
     </row>
-    <row r="73" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D73" s="20"/>
       <c r="I73" s="20"/>
     </row>
-    <row r="74" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D74" s="20"/>
       <c r="I74" s="20"/>
     </row>
-    <row r="75" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D75" s="20"/>
       <c r="I75" s="20"/>
     </row>
-    <row r="76" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D76" s="20"/>
       <c r="I76" s="20"/>
     </row>
-    <row r="77" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D77" s="20"/>
       <c r="I77" s="20"/>
     </row>
-    <row r="78" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D78" s="20"/>
       <c r="I78" s="20"/>
     </row>
-    <row r="79" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D79" s="20"/>
       <c r="I79" s="20"/>
     </row>
-    <row r="80" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D80" s="20"/>
       <c r="I80" s="20"/>
     </row>
-    <row r="81" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D81" s="20"/>
       <c r="I81" s="20"/>
     </row>
-    <row r="82" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D82" s="20"/>
       <c r="I82" s="20"/>
     </row>
-    <row r="83" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D83" s="20"/>
       <c r="I83" s="20"/>
     </row>
-    <row r="84" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D84" s="20"/>
       <c r="I84" s="20"/>
     </row>
-    <row r="85" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D85" s="20"/>
       <c r="I85" s="20"/>
     </row>
-    <row r="86" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D86" s="20"/>
       <c r="I86" s="20"/>
     </row>
-    <row r="87" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D87" s="20"/>
       <c r="I87" s="20"/>
     </row>
-    <row r="88" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D88" s="20"/>
       <c r="I88" s="20"/>
     </row>
-    <row r="89" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D89" s="20"/>
       <c r="I89" s="20"/>
     </row>
-    <row r="90" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D90" s="20"/>
       <c r="I90" s="20"/>
     </row>
-    <row r="91" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D91" s="20"/>
       <c r="I91" s="20"/>
     </row>
-    <row r="92" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D92" s="20"/>
       <c r="I92" s="20"/>
     </row>
-    <row r="93" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D93" s="20"/>
       <c r="I93" s="20"/>
     </row>
-    <row r="94" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D94" s="20"/>
       <c r="I94" s="20"/>
     </row>
-    <row r="95" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D95" s="20"/>
       <c r="I95" s="20"/>
     </row>
-    <row r="96" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D96" s="20"/>
       <c r="I96" s="20"/>
     </row>
-    <row r="97" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D97" s="20"/>
       <c r="I97" s="20"/>
     </row>
-    <row r="98" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D98" s="20"/>
       <c r="I98" s="20"/>
     </row>
-    <row r="99" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D99" s="20"/>
       <c r="I99" s="20"/>
     </row>
-    <row r="100" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D100" s="20"/>
       <c r="I100" s="20"/>
     </row>
-    <row r="101" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D101" s="20"/>
       <c r="I101" s="20"/>
     </row>
-    <row r="102" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D102" s="20"/>
       <c r="I102" s="20"/>
     </row>
-    <row r="103" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D103" s="20"/>
       <c r="I103" s="20"/>
     </row>
-    <row r="104" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D104" s="20"/>
       <c r="I104" s="20"/>
     </row>
-    <row r="105" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D105" s="20"/>
       <c r="I105" s="20"/>
     </row>
-    <row r="106" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D106" s="20"/>
       <c r="I106" s="20"/>
     </row>
-    <row r="107" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D107" s="20"/>
       <c r="I107" s="20"/>
     </row>
-    <row r="108" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D108" s="20"/>
       <c r="I108" s="20"/>
     </row>
-    <row r="109" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D109" s="20"/>
       <c r="I109" s="20"/>
     </row>
-    <row r="110" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D110" s="20"/>
       <c r="I110" s="20"/>
     </row>
-    <row r="111" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D111" s="20"/>
       <c r="I111" s="20"/>
     </row>
-    <row r="112" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D112" s="20"/>
       <c r="I112" s="20"/>
     </row>
-    <row r="113" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D113" s="20"/>
       <c r="I113" s="20"/>
     </row>
-    <row r="114" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D114" s="20"/>
       <c r="I114" s="20"/>
     </row>
-    <row r="115" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D115" s="20"/>
       <c r="I115" s="20"/>
     </row>
-    <row r="116" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D116" s="20"/>
       <c r="I116" s="20"/>
     </row>
-    <row r="117" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D117" s="20"/>
       <c r="I117" s="20"/>
     </row>
-    <row r="118" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D118" s="20"/>
       <c r="I118" s="20"/>
     </row>
-    <row r="119" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D119" s="20"/>
       <c r="I119" s="20"/>
     </row>
-    <row r="120" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D120" s="20"/>
       <c r="I120" s="20"/>
     </row>
-    <row r="121" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D121" s="20"/>
       <c r="I121" s="20"/>
     </row>
-    <row r="122" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D122" s="20"/>
       <c r="I122" s="20"/>
     </row>
-    <row r="123" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D123" s="20"/>
       <c r="I123" s="20"/>
     </row>
-    <row r="124" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D124" s="20"/>
       <c r="I124" s="20"/>
     </row>
-    <row r="125" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D125" s="20"/>
       <c r="I125" s="20"/>
     </row>
-    <row r="126" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I126" s="20"/>
     </row>
-    <row r="127" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I127" s="20"/>
     </row>
-    <row r="128" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I128" s="20"/>
     </row>
-    <row r="129" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I129" s="20"/>
     </row>
-    <row r="130" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I130" s="20"/>
     </row>
-    <row r="131" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I131" s="20"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D16">
-    <cfRule type="timePeriod" dxfId="24" priority="37" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="14" priority="37" timePeriod="nextMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0+1)),YEAR(D1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="23" priority="38" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="13" priority="38" timePeriod="thisMonth">
       <formula>AND(MONTH(D1)=MONTH(TODAY()),YEAR(D1)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="22" priority="39" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="12" priority="39" timePeriod="lastMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0-1)),YEAR(D1)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D22:D29 D31 D41:D1048576">
-    <cfRule type="timePeriod" dxfId="21" priority="1" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="11" priority="1" timePeriod="nextMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0+1)),YEAR(D22)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="20" priority="2" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="10" priority="2" timePeriod="thisMonth">
       <formula>AND(MONTH(D22)=MONTH(TODAY()),YEAR(D22)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="19" priority="3" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="9" priority="3" timePeriod="lastMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0-1)),YEAR(D22)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="timePeriod" dxfId="18" priority="40" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="8" priority="40" timePeriod="nextMonth">
       <formula>AND(MONTH(I1)=MONTH(EDATE(TODAY(),0+1)),YEAR(I1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="17" priority="41" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="7" priority="41" timePeriod="thisMonth">
       <formula>AND(MONTH(I1)=MONTH(TODAY()),YEAR(I1)=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="cellIs" dxfId="16" priority="45" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="45" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I22">
-    <cfRule type="cellIs" dxfId="15" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="42" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
-    <cfRule type="cellIs" dxfId="14" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="43" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2426,14 +2420,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAE522B-09DD-4490-9CA8-387DE173331A}">
   <dimension ref="A1:G62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
-    <col min="2" max="3" width="11.42578125" style="12"/>
-    <col min="4" max="4" width="11.85546875" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="11.44140625" style="12"/>
+    <col min="4" max="4" width="11.88671875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="45" t="s">
         <v>49</v>
       </c>
@@ -2444,7 +2438,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="47"/>
       <c r="B2" s="11">
         <v>0</v>
@@ -2455,7 +2449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="47">
         <v>46037</v>
       </c>
@@ -2463,14 +2457,14 @@
         <v>75</v>
       </c>
       <c r="C3" s="11">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="D3" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="47">
         <v>46053</v>
       </c>
@@ -2485,7 +2479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="47">
         <v>46068</v>
       </c>
@@ -2500,7 +2494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="47">
         <v>46081</v>
       </c>
@@ -2515,7 +2509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="47">
         <v>46096</v>
       </c>
@@ -2534,7 +2528,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="47">
         <v>46112</v>
       </c>
@@ -2553,7 +2547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="47">
         <v>46127</v>
       </c>
@@ -2572,7 +2566,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="47">
         <v>46142</v>
       </c>
@@ -2591,7 +2585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="47">
         <v>46157</v>
       </c>
@@ -2610,7 +2604,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="47">
         <v>46173</v>
       </c>
@@ -2629,7 +2623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="47">
         <v>46188</v>
       </c>
@@ -2652,7 +2646,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="47">
         <v>46203</v>
       </c>
@@ -2665,7 +2659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="47">
         <v>46218</v>
       </c>
@@ -2678,7 +2672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="47">
         <v>46234</v>
       </c>
@@ -2691,7 +2685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="47">
         <v>46249</v>
       </c>
@@ -2704,7 +2698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="47">
         <v>46265</v>
       </c>
@@ -2717,7 +2711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="47">
         <v>46280</v>
       </c>
@@ -2730,7 +2724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="47">
         <v>46295</v>
       </c>
@@ -2743,7 +2737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="47">
         <v>46310</v>
       </c>
@@ -2756,7 +2750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="47">
         <v>46326</v>
       </c>
@@ -2769,7 +2763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="47">
         <v>46341</v>
       </c>
@@ -2782,7 +2776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="47">
         <v>46356</v>
       </c>
@@ -2795,7 +2789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="47">
         <v>46371</v>
       </c>
@@ -2808,7 +2802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="46" t="s">
         <v>50</v>
       </c>
@@ -2821,7 +2815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="46" t="s">
         <v>51</v>
       </c>
@@ -2834,7 +2828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="47">
         <v>46387</v>
       </c>
@@ -2847,7 +2841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="47">
         <v>46402</v>
       </c>
@@ -2860,7 +2854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="47">
         <v>46418</v>
       </c>
@@ -2873,7 +2867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="47">
         <v>46433</v>
       </c>
@@ -2886,7 +2880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="47">
         <v>46446</v>
       </c>
@@ -2899,7 +2893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="47">
         <v>46461</v>
       </c>
@@ -2912,7 +2906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="47">
         <v>46477</v>
       </c>
@@ -2925,7 +2919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="47">
         <v>46492</v>
       </c>
@@ -2938,7 +2932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="47">
         <v>46507</v>
       </c>
@@ -2951,7 +2945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="47">
         <v>46522</v>
       </c>
@@ -2964,7 +2958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="47">
         <v>46538</v>
       </c>
@@ -2977,7 +2971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="47">
         <v>46553</v>
       </c>
@@ -2990,7 +2984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="47">
         <v>46568</v>
       </c>
@@ -3003,7 +2997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="47">
         <v>46583</v>
       </c>
@@ -3016,7 +3010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="47">
         <v>46599</v>
       </c>
@@ -3029,7 +3023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="47">
         <v>46614</v>
       </c>
@@ -3042,7 +3036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="47">
         <v>46630</v>
       </c>
@@ -3055,7 +3049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="47">
         <v>46645</v>
       </c>
@@ -3068,7 +3062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="47">
         <v>46660</v>
       </c>
@@ -3081,7 +3075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="47">
         <v>46675</v>
       </c>
@@ -3094,7 +3088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="47">
         <v>46691</v>
       </c>
@@ -3107,7 +3101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="47">
         <v>46706</v>
       </c>
@@ -3120,7 +3114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="47">
         <v>46721</v>
       </c>
@@ -3133,7 +3127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="47">
         <v>46736</v>
       </c>
@@ -3146,7 +3140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="46" t="s">
         <v>50</v>
       </c>
@@ -3159,7 +3153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="46" t="s">
         <v>51</v>
       </c>
@@ -3172,7 +3166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="47">
         <v>46752</v>
       </c>
@@ -3185,44 +3179,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="50">
         <f>SUM(B2:B54)</f>
         <v>4610</v>
       </c>
       <c r="C55" s="51">
         <f>SUM(C2:C54)</f>
-        <v>130</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
     </row>
-    <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="60">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
-        <v>-160</v>
+        <v>-240</v>
       </c>
       <c r="C57" s="61"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B58" s="59"/>
       <c r="C58" s="3"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B59"/>
       <c r="C59" s="3"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
     </row>
@@ -3231,13 +3225,13 @@
     <mergeCell ref="B57:C57"/>
   </mergeCells>
   <conditionalFormatting sqref="B57:C57">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC02230-E1B3-4212-99F3-7D0941DD1F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F73CD8-6E8E-4062-8809-278410D3EC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="61">
   <si>
     <t>Totales</t>
   </si>
@@ -216,6 +216,9 @@
   </si>
   <si>
     <t>Tasa cero Sillones</t>
+  </si>
+  <si>
+    <t>Bono</t>
   </si>
 </sst>
 </file>
@@ -684,10 +687,6 @@
   </cellStyles>
   <dxfs count="29">
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -897,6 +896,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="166" formatCode="d\-mmm"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -946,15 +949,15 @@
     <tableColumn id="2" xr3:uid="{11D77EA7-239F-47E1-9378-FFBA07ACDD06}" name="Tarjeta"/>
     <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="26"/>
     <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="0">
+    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="24">
       <calculatedColumnFormula>186.68-48</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="24"/>
-    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="19" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="23"/>
+    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="18" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1500,16 +1503,16 @@
     <row r="37" ht="30.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>$C$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
       <formula>$C$7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
       <formula>$C$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
       <formula>$C$2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1634,6 +1637,9 @@
       <c r="I5" s="20">
         <v>46118</v>
       </c>
+      <c r="J5" s="12">
+        <v>32.43</v>
+      </c>
       <c r="K5" s="31">
         <v>0.27900000000000003</v>
       </c>
@@ -1659,7 +1665,9 @@
       <c r="I6" s="20">
         <v>46118</v>
       </c>
-      <c r="J6" s="12"/>
+      <c r="J6" s="12">
+        <v>104.97</v>
+      </c>
       <c r="K6" s="31"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1810,7 +1818,7 @@
         <v>45798</v>
       </c>
       <c r="E13" s="12">
-        <f t="shared" ref="E3:E14" si="0">186.68-48</f>
+        <f t="shared" ref="E13" si="0">186.68-48</f>
         <v>138.68</v>
       </c>
       <c r="F13" s="12">
@@ -1846,7 +1854,7 @@
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>0</v>
+        <v>137.4</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1866,13 +1874,17 @@
         <v>36</v>
       </c>
       <c r="C17" s="24">
-        <v>46096</v>
+        <v>46111</v>
       </c>
       <c r="D17" s="24">
-        <v>46111</v>
-      </c>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
+        <v>46127</v>
+      </c>
+      <c r="E17" s="24">
+        <v>46142</v>
+      </c>
+      <c r="F17" s="24" t="s">
+        <v>60</v>
+      </c>
       <c r="G17" s="24"/>
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
@@ -1881,17 +1893,27 @@
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="57"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
+      <c r="B18" s="57">
+        <v>140</v>
+      </c>
+      <c r="C18" s="2">
+        <v>60</v>
+      </c>
+      <c r="D18" s="2">
+        <v>30</v>
+      </c>
+      <c r="E18" s="2">
+        <v>60</v>
+      </c>
+      <c r="F18" s="2">
+        <v>165</v>
+      </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="22"/>
       <c r="J18" s="23">
         <f>SUM(B18:I18)</f>
-        <v>0</v>
+        <v>455</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1910,7 +1932,7 @@
       </c>
       <c r="I20" s="25">
         <f>+H14+J14+G14</f>
-        <v>0</v>
+        <v>137.4</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1920,7 +1942,7 @@
       </c>
       <c r="I21" s="25">
         <f>+J18-H14-G14</f>
-        <v>0</v>
+        <v>455</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1930,7 +1952,7 @@
       </c>
       <c r="I22" s="25">
         <f>+I21-J14</f>
-        <v>0</v>
+        <v>317.60000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
@@ -2365,47 +2387,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D16">
-    <cfRule type="timePeriod" dxfId="14" priority="37" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="13" priority="37" timePeriod="nextMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0+1)),YEAR(D1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="13" priority="38" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="12" priority="38" timePeriod="thisMonth">
       <formula>AND(MONTH(D1)=MONTH(TODAY()),YEAR(D1)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="12" priority="39" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="11" priority="39" timePeriod="lastMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0-1)),YEAR(D1)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D22:D29 D31 D41:D1048576">
-    <cfRule type="timePeriod" dxfId="11" priority="1" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="10" priority="1" timePeriod="nextMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0+1)),YEAR(D22)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="10" priority="2" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="9" priority="2" timePeriod="thisMonth">
       <formula>AND(MONTH(D22)=MONTH(TODAY()),YEAR(D22)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="9" priority="3" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="8" priority="3" timePeriod="lastMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0-1)),YEAR(D22)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="timePeriod" dxfId="8" priority="40" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="7" priority="40" timePeriod="nextMonth">
       <formula>AND(MONTH(I1)=MONTH(EDATE(TODAY(),0+1)),YEAR(I1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="7" priority="41" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="6" priority="41" timePeriod="thisMonth">
       <formula>AND(MONTH(I1)=MONTH(TODAY()),YEAR(I1)=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="cellIs" dxfId="6" priority="45" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="45" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I22">
-    <cfRule type="cellIs" dxfId="5" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="42" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
-    <cfRule type="cellIs" dxfId="4" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="43" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2419,7 +2441,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAE522B-09DD-4490-9CA8-387DE173331A}">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -2427,7 +2449,7 @@
     <col min="4" max="4" width="11.88671875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="45" t="s">
         <v>49</v>
       </c>
@@ -2438,7 +2460,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="47"/>
       <c r="B2" s="11">
         <v>0</v>
@@ -2449,7 +2471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="47">
         <v>46037</v>
       </c>
@@ -2464,7 +2486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="47">
         <v>46053</v>
       </c>
@@ -2479,7 +2501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="47">
         <v>46068</v>
       </c>
@@ -2494,7 +2516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="47">
         <v>46081</v>
       </c>
@@ -2509,17 +2531,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="47">
         <v>46096</v>
       </c>
       <c r="B7" s="11">
         <v>75</v>
       </c>
-      <c r="C7" s="11"/>
+      <c r="C7" s="11">
+        <v>150</v>
+      </c>
       <c r="D7" t="b">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -2528,7 +2552,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="47">
         <v>46112</v>
       </c>
@@ -2547,7 +2571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="47">
         <v>46127</v>
       </c>
@@ -2566,7 +2590,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="47">
         <v>46142</v>
       </c>
@@ -2585,7 +2609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="47">
         <v>46157</v>
       </c>
@@ -2604,7 +2628,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="47">
         <v>46173</v>
       </c>
@@ -2623,7 +2647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="47">
         <v>46188</v>
       </c>
@@ -2641,12 +2665,8 @@
       <c r="F13">
         <v>50</v>
       </c>
-      <c r="G13">
-        <f>SUM(E7:F15)</f>
-        <v>900</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="47">
         <v>46203</v>
       </c>
@@ -2659,7 +2679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="47">
         <v>46218</v>
       </c>
@@ -2672,7 +2692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="47">
         <v>46234</v>
       </c>
@@ -3186,7 +3206,7 @@
       </c>
       <c r="C55" s="51">
         <f>SUM(C2:C54)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3196,7 +3216,7 @@
     <row r="57" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="60">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
-        <v>-240</v>
+        <v>-165</v>
       </c>
       <c r="C57" s="61"/>
     </row>
@@ -3225,13 +3245,13 @@
     <mergeCell ref="B57:C57"/>
   </mergeCells>
   <conditionalFormatting sqref="B57:C57">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F73CD8-6E8E-4062-8809-278410D3EC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{319911F0-2E5E-4372-966A-6465DA2E0467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
@@ -1638,7 +1638,7 @@
         <v>46118</v>
       </c>
       <c r="J5" s="12">
-        <v>32.43</v>
+        <v>195.36</v>
       </c>
       <c r="K5" s="31">
         <v>0.27900000000000003</v>
@@ -1854,7 +1854,7 @@
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>137.4</v>
+        <v>300.33000000000004</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1894,7 +1894,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="57">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="C18" s="2">
         <v>60</v>
@@ -1906,14 +1906,14 @@
         <v>60</v>
       </c>
       <c r="F18" s="2">
-        <v>165</v>
+        <v>100</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="22"/>
       <c r="J18" s="23">
         <f>SUM(B18:I18)</f>
-        <v>455</v>
+        <v>340</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="I20" s="25">
         <f>+H14+J14+G14</f>
-        <v>137.4</v>
+        <v>300.33000000000004</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="I21" s="25">
         <f>+J18-H14-G14</f>
-        <v>455</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="I22" s="25">
         <f>+I21-J14</f>
-        <v>317.60000000000002</v>
+        <v>39.669999999999959</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{319911F0-2E5E-4372-966A-6465DA2E0467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE53DA18-FD36-4D00-8E2B-A8F16C45E023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="61">
   <si>
     <t>Totales</t>
   </si>
@@ -218,7 +221,7 @@
     <t>Tasa cero Sillones</t>
   </si>
   <si>
-    <t>Bono</t>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -713,6 +716,68 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="21" formatCode="d\-mmm"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -858,68 +923,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="d\-mmm"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -939,7 +942,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="28" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="13" tableBorderDxfId="12">
   <autoFilter ref="A2:K14" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K14">
     <sortCondition ref="D3:D14"/>
@@ -947,17 +950,17 @@
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{4E2F1548-5DA7-4ADC-946F-053ED807460A}" name="Banco"/>
     <tableColumn id="2" xr3:uid="{11D77EA7-239F-47E1-9378-FFBA07ACDD06}" name="Tarjeta"/>
-    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="24">
+    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="9">
       <calculatedColumnFormula>186.68-48</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="23"/>
-    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="18" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="3" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1260,17 +1263,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0DE2A9-9218-4E10-883D-DF66D771FC39}">
-  <dimension ref="B1:H37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:J37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="3.109375" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="3.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
         <v>14</v>
       </c>
@@ -1282,7 +1285,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1296,7 +1299,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
@@ -1309,8 +1312,11 @@
       <c r="F3" s="8">
         <v>50</v>
       </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
@@ -1324,7 +1330,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
@@ -1338,7 +1344,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
@@ -1346,13 +1352,16 @@
         <v>41</v>
       </c>
       <c r="D6" s="8">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F6" s="8">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+      <c r="G6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>17</v>
       </c>
@@ -1365,8 +1374,11 @@
       <c r="F7" s="8">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -1377,7 +1389,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -1385,18 +1397,25 @@
         <v>41</v>
       </c>
       <c r="F9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>16</v>
       </c>
       <c r="C10" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="J10">
+        <f>770-583.32</f>
+        <v>186.67999999999995</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -1406,8 +1425,15 @@
       <c r="F11">
         <v>25</v>
       </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G11" t="s">
+        <v>60</v>
+      </c>
+      <c r="J11">
+        <f>J10/47</f>
+        <v>3.9719148936170203</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>9</v>
       </c>
@@ -1420,11 +1446,14 @@
       <c r="F12">
         <v>5</v>
       </c>
+      <c r="G12" t="s">
+        <v>60</v>
+      </c>
       <c r="H12">
         <v>8286917</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>10</v>
       </c>
@@ -1432,7 +1461,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>15</v>
       </c>
@@ -1442,8 +1471,11 @@
       <c r="F14">
         <v>31</v>
       </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>59</v>
       </c>
@@ -1454,21 +1486,21 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7">
         <f>SUM(D2:D16)</f>
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="F17" s="7">
         <f>SUM(F2:F16)</f>
-        <v>386</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
         <v>12</v>
       </c>
@@ -1481,38 +1513,38 @@
         <v>448</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5">
         <f>D18-D17</f>
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F19" s="5">
         <f>F18-F17</f>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="37" ht="30.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
       <formula>$C$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
       <formula>$C$7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="equal">
       <formula>$C$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="4" operator="equal">
       <formula>$C$2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1524,22 +1556,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B43D18-F407-4702-B159-A2C7E22E2016}">
   <dimension ref="A1:N131"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" style="19" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" style="12" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" style="12" customWidth="1"/>
-    <col min="7" max="8" width="16.109375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" style="10" customWidth="1"/>
-    <col min="10" max="10" width="17.44140625" style="12" customWidth="1"/>
-    <col min="11" max="11" width="7.109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" style="12" customWidth="1"/>
+    <col min="7" max="8" width="16.140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" style="10" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" style="12" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" style="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>19</v>
       </c>
@@ -1574,7 +1606,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
         <v>40</v>
       </c>
@@ -1597,7 +1629,7 @@
       <c r="J3" s="42"/>
       <c r="K3" s="43"/>
     </row>
-    <row r="4" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="34" t="s">
         <v>56</v>
       </c>
@@ -1620,7 +1652,7 @@
       <c r="J4" s="37"/>
       <c r="K4" s="38"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -1638,14 +1670,14 @@
         <v>46118</v>
       </c>
       <c r="J5" s="12">
-        <v>195.36</v>
+        <v>200.36</v>
       </c>
       <c r="K5" s="31">
         <v>0.27900000000000003</v>
       </c>
       <c r="N5" s="4"/>
     </row>
-    <row r="6" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1670,7 +1702,7 @@
       </c>
       <c r="K6" s="31"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -1692,7 +1724,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
         <v>39</v>
       </c>
@@ -1715,7 +1747,7 @@
       <c r="J8" s="37"/>
       <c r="K8" s="38"/>
     </row>
-    <row r="9" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
         <v>29</v>
       </c>
@@ -1738,7 +1770,7 @@
       <c r="J9" s="44"/>
       <c r="K9" s="54"/>
     </row>
-    <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1761,7 +1793,7 @@
       <c r="J10" s="12"/>
       <c r="K10" s="31"/>
     </row>
-    <row r="11" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
         <v>29</v>
       </c>
@@ -1784,7 +1816,7 @@
       <c r="J11" s="37"/>
       <c r="K11" s="38"/>
     </row>
-    <row r="12" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
         <v>58</v>
       </c>
@@ -1807,7 +1839,7 @@
       <c r="J12" s="42"/>
       <c r="K12" s="43"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="39" t="s">
         <v>58</v>
       </c>
@@ -1829,7 +1861,7 @@
         <v>45946</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -1854,69 +1886,65 @@
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>300.33000000000004</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+        <v>305.33000000000004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D15" s="20"/>
       <c r="I15" s="20"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D16" s="20"/>
       <c r="I16" s="20"/>
     </row>
-    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="24">
-        <v>46111</v>
-      </c>
+      <c r="C17" s="24"/>
       <c r="D17" s="24">
         <v>46127</v>
       </c>
       <c r="E17" s="24">
         <v>46142</v>
       </c>
-      <c r="F17" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="G17" s="24"/>
+      <c r="F17" s="24">
+        <v>46157</v>
+      </c>
+      <c r="G17" s="24">
+        <v>46172</v>
+      </c>
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
     </row>
-    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B18" s="57">
-        <v>90</v>
-      </c>
-      <c r="C18" s="2">
-        <v>60</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E18" s="2">
-        <v>60</v>
-      </c>
-      <c r="F18" s="2">
-        <v>100</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="22"/>
       <c r="J18" s="23">
         <f>SUM(B18:I18)</f>
-        <v>340</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="55"/>
@@ -1925,509 +1953,509 @@
       <c r="H19" s="2"/>
       <c r="I19" s="20"/>
     </row>
-    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D20" s="12"/>
       <c r="H20" s="56" t="s">
         <v>37</v>
       </c>
       <c r="I20" s="25">
         <f>+H14+J14+G14</f>
-        <v>300.33000000000004</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>305.33000000000004</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D21" s="12"/>
       <c r="H21" s="26" t="s">
         <v>38</v>
       </c>
       <c r="I21" s="25">
         <f>+J18-H14-G14</f>
-        <v>340</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D22" s="20"/>
       <c r="H22" s="27" t="s">
         <v>54</v>
       </c>
       <c r="I22" s="25">
         <f>+I21-J14</f>
-        <v>39.669999999999959</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+        <v>54.669999999999959</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D23" s="12"/>
       <c r="I23" s="20"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D24" s="12"/>
       <c r="I24" s="20"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D25" s="12"/>
       <c r="I25" s="20"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D26" s="12"/>
       <c r="I26" s="20"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D27" s="12"/>
       <c r="I27" s="20"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D28" s="12"/>
       <c r="I28" s="20"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D29" s="12"/>
       <c r="I29" s="20"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D30" s="11"/>
       <c r="I30" s="20"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D31" s="20"/>
       <c r="I31" s="20"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D32" s="11"/>
       <c r="I32" s="20"/>
     </row>
-    <row r="33" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D33" s="11"/>
       <c r="I33" s="20"/>
     </row>
-    <row r="34" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D34" s="11"/>
       <c r="I34" s="20"/>
     </row>
-    <row r="35" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D35" s="11"/>
       <c r="I35" s="20"/>
     </row>
-    <row r="36" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D36" s="11"/>
       <c r="I36" s="20"/>
     </row>
-    <row r="37" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D37" s="11"/>
       <c r="I37" s="20"/>
     </row>
-    <row r="38" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D38" s="11"/>
       <c r="I38" s="20"/>
     </row>
-    <row r="39" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D39" s="11"/>
       <c r="I39" s="20"/>
     </row>
-    <row r="40" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D40" s="11"/>
       <c r="I40" s="20"/>
     </row>
-    <row r="41" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D41" s="20"/>
       <c r="I41" s="20"/>
     </row>
-    <row r="42" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D42" s="12"/>
       <c r="I42" s="20"/>
     </row>
-    <row r="43" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D43" s="12"/>
       <c r="I43" s="20"/>
     </row>
-    <row r="44" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D44" s="20"/>
       <c r="I44" s="20"/>
     </row>
-    <row r="45" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D45" s="20"/>
       <c r="I45" s="20"/>
     </row>
-    <row r="46" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D46" s="20"/>
       <c r="I46" s="20"/>
     </row>
-    <row r="47" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D47" s="20"/>
       <c r="I47" s="20"/>
     </row>
-    <row r="48" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D48" s="20"/>
       <c r="I48" s="20"/>
     </row>
-    <row r="49" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D49" s="20"/>
       <c r="I49" s="20"/>
     </row>
-    <row r="50" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D50" s="20"/>
       <c r="I50" s="20"/>
     </row>
-    <row r="51" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D51" s="20"/>
       <c r="I51" s="20"/>
     </row>
-    <row r="52" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D52" s="20"/>
       <c r="I52" s="20"/>
     </row>
-    <row r="53" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D53" s="20"/>
       <c r="I53" s="20"/>
     </row>
-    <row r="54" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D54" s="20"/>
       <c r="I54" s="20"/>
     </row>
-    <row r="55" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D55" s="20"/>
       <c r="I55" s="20"/>
     </row>
-    <row r="56" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D56" s="20"/>
       <c r="I56" s="20"/>
     </row>
-    <row r="57" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D57" s="20"/>
       <c r="I57" s="20"/>
     </row>
-    <row r="58" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D58" s="20"/>
       <c r="I58" s="20"/>
     </row>
-    <row r="59" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D59" s="20"/>
       <c r="I59" s="20"/>
     </row>
-    <row r="60" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D60" s="20"/>
       <c r="I60" s="20"/>
     </row>
-    <row r="61" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D61" s="20"/>
       <c r="I61" s="20"/>
     </row>
-    <row r="62" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D62" s="20"/>
       <c r="I62" s="20"/>
     </row>
-    <row r="63" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D63" s="20"/>
       <c r="I63" s="20"/>
     </row>
-    <row r="64" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D64" s="20"/>
       <c r="I64" s="20"/>
     </row>
-    <row r="65" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D65" s="20"/>
       <c r="I65" s="20"/>
     </row>
-    <row r="66" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D66" s="20"/>
       <c r="I66" s="20"/>
     </row>
-    <row r="67" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D67" s="20"/>
       <c r="I67" s="20"/>
     </row>
-    <row r="68" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D68" s="20"/>
       <c r="I68" s="20"/>
     </row>
-    <row r="69" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D69" s="20"/>
       <c r="I69" s="20"/>
     </row>
-    <row r="70" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D70" s="20"/>
       <c r="I70" s="20"/>
     </row>
-    <row r="71" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D71" s="20"/>
       <c r="I71" s="20"/>
     </row>
-    <row r="72" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D72" s="20"/>
       <c r="I72" s="20"/>
     </row>
-    <row r="73" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D73" s="20"/>
       <c r="I73" s="20"/>
     </row>
-    <row r="74" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D74" s="20"/>
       <c r="I74" s="20"/>
     </row>
-    <row r="75" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D75" s="20"/>
       <c r="I75" s="20"/>
     </row>
-    <row r="76" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D76" s="20"/>
       <c r="I76" s="20"/>
     </row>
-    <row r="77" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D77" s="20"/>
       <c r="I77" s="20"/>
     </row>
-    <row r="78" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D78" s="20"/>
       <c r="I78" s="20"/>
     </row>
-    <row r="79" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D79" s="20"/>
       <c r="I79" s="20"/>
     </row>
-    <row r="80" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D80" s="20"/>
       <c r="I80" s="20"/>
     </row>
-    <row r="81" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D81" s="20"/>
       <c r="I81" s="20"/>
     </row>
-    <row r="82" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D82" s="20"/>
       <c r="I82" s="20"/>
     </row>
-    <row r="83" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D83" s="20"/>
       <c r="I83" s="20"/>
     </row>
-    <row r="84" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D84" s="20"/>
       <c r="I84" s="20"/>
     </row>
-    <row r="85" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D85" s="20"/>
       <c r="I85" s="20"/>
     </row>
-    <row r="86" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D86" s="20"/>
       <c r="I86" s="20"/>
     </row>
-    <row r="87" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D87" s="20"/>
       <c r="I87" s="20"/>
     </row>
-    <row r="88" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D88" s="20"/>
       <c r="I88" s="20"/>
     </row>
-    <row r="89" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D89" s="20"/>
       <c r="I89" s="20"/>
     </row>
-    <row r="90" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D90" s="20"/>
       <c r="I90" s="20"/>
     </row>
-    <row r="91" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D91" s="20"/>
       <c r="I91" s="20"/>
     </row>
-    <row r="92" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D92" s="20"/>
       <c r="I92" s="20"/>
     </row>
-    <row r="93" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D93" s="20"/>
       <c r="I93" s="20"/>
     </row>
-    <row r="94" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D94" s="20"/>
       <c r="I94" s="20"/>
     </row>
-    <row r="95" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D95" s="20"/>
       <c r="I95" s="20"/>
     </row>
-    <row r="96" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D96" s="20"/>
       <c r="I96" s="20"/>
     </row>
-    <row r="97" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D97" s="20"/>
       <c r="I97" s="20"/>
     </row>
-    <row r="98" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D98" s="20"/>
       <c r="I98" s="20"/>
     </row>
-    <row r="99" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D99" s="20"/>
       <c r="I99" s="20"/>
     </row>
-    <row r="100" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D100" s="20"/>
       <c r="I100" s="20"/>
     </row>
-    <row r="101" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D101" s="20"/>
       <c r="I101" s="20"/>
     </row>
-    <row r="102" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D102" s="20"/>
       <c r="I102" s="20"/>
     </row>
-    <row r="103" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D103" s="20"/>
       <c r="I103" s="20"/>
     </row>
-    <row r="104" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D104" s="20"/>
       <c r="I104" s="20"/>
     </row>
-    <row r="105" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D105" s="20"/>
       <c r="I105" s="20"/>
     </row>
-    <row r="106" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D106" s="20"/>
       <c r="I106" s="20"/>
     </row>
-    <row r="107" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D107" s="20"/>
       <c r="I107" s="20"/>
     </row>
-    <row r="108" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D108" s="20"/>
       <c r="I108" s="20"/>
     </row>
-    <row r="109" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D109" s="20"/>
       <c r="I109" s="20"/>
     </row>
-    <row r="110" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D110" s="20"/>
       <c r="I110" s="20"/>
     </row>
-    <row r="111" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D111" s="20"/>
       <c r="I111" s="20"/>
     </row>
-    <row r="112" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D112" s="20"/>
       <c r="I112" s="20"/>
     </row>
-    <row r="113" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D113" s="20"/>
       <c r="I113" s="20"/>
     </row>
-    <row r="114" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D114" s="20"/>
       <c r="I114" s="20"/>
     </row>
-    <row r="115" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D115" s="20"/>
       <c r="I115" s="20"/>
     </row>
-    <row r="116" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D116" s="20"/>
       <c r="I116" s="20"/>
     </row>
-    <row r="117" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D117" s="20"/>
       <c r="I117" s="20"/>
     </row>
-    <row r="118" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D118" s="20"/>
       <c r="I118" s="20"/>
     </row>
-    <row r="119" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D119" s="20"/>
       <c r="I119" s="20"/>
     </row>
-    <row r="120" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D120" s="20"/>
       <c r="I120" s="20"/>
     </row>
-    <row r="121" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D121" s="20"/>
       <c r="I121" s="20"/>
     </row>
-    <row r="122" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D122" s="20"/>
       <c r="I122" s="20"/>
     </row>
-    <row r="123" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D123" s="20"/>
       <c r="I123" s="20"/>
     </row>
-    <row r="124" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D124" s="20"/>
       <c r="I124" s="20"/>
     </row>
-    <row r="125" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D125" s="20"/>
       <c r="I125" s="20"/>
     </row>
-    <row r="126" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I126" s="20"/>
     </row>
-    <row r="127" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I127" s="20"/>
     </row>
-    <row r="128" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I128" s="20"/>
     </row>
-    <row r="129" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I129" s="20"/>
     </row>
-    <row r="130" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I130" s="20"/>
     </row>
-    <row r="131" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I131" s="20"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D16">
-    <cfRule type="timePeriod" dxfId="13" priority="37" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="24" priority="37" timePeriod="nextMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0+1)),YEAR(D1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="12" priority="38" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="23" priority="38" timePeriod="thisMonth">
       <formula>AND(MONTH(D1)=MONTH(TODAY()),YEAR(D1)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="11" priority="39" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="22" priority="39" timePeriod="lastMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0-1)),YEAR(D1)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D22:D29 D31 D41:D1048576">
-    <cfRule type="timePeriod" dxfId="10" priority="1" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="21" priority="1" timePeriod="nextMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0+1)),YEAR(D22)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="9" priority="2" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="20" priority="2" timePeriod="thisMonth">
       <formula>AND(MONTH(D22)=MONTH(TODAY()),YEAR(D22)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="8" priority="3" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="19" priority="3" timePeriod="lastMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0-1)),YEAR(D22)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="timePeriod" dxfId="7" priority="40" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="18" priority="40" timePeriod="nextMonth">
       <formula>AND(MONTH(I1)=MONTH(EDATE(TODAY(),0+1)),YEAR(I1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="6" priority="41" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="17" priority="41" timePeriod="thisMonth">
       <formula>AND(MONTH(I1)=MONTH(TODAY()),YEAR(I1)=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="cellIs" dxfId="5" priority="45" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="45" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I22">
-    <cfRule type="cellIs" dxfId="4" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="42" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
-    <cfRule type="cellIs" dxfId="3" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="43" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2441,15 +2469,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAE522B-09DD-4490-9CA8-387DE173331A}">
-  <dimension ref="A1:F62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D62"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
-    <col min="2" max="3" width="11.44140625" style="12"/>
-    <col min="4" max="4" width="11.88671875" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="11.42578125" style="12"/>
+    <col min="4" max="4" width="11.85546875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
         <v>49</v>
       </c>
@@ -2460,7 +2488,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="47"/>
       <c r="B2" s="11">
         <v>0</v>
@@ -2471,7 +2499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="47">
         <v>46037</v>
       </c>
@@ -2486,7 +2514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="47">
         <v>46053</v>
       </c>
@@ -2501,7 +2529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="47">
         <v>46068</v>
       </c>
@@ -2516,7 +2544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="47">
         <v>46081</v>
       </c>
@@ -2531,7 +2559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="47">
         <v>46096</v>
       </c>
@@ -2545,33 +2573,23 @@
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="E7">
-        <v>100</v>
-      </c>
-      <c r="F7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="47">
         <v>46112</v>
       </c>
       <c r="B8" s="11">
         <v>70</v>
       </c>
-      <c r="C8" s="11"/>
+      <c r="C8" s="11">
+        <v>100</v>
+      </c>
       <c r="D8" t="b">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>100</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="47">
         <v>46127</v>
       </c>
@@ -2583,14 +2601,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="E9">
-        <v>100</v>
-      </c>
-      <c r="F9">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="47">
         <v>46142</v>
       </c>
@@ -2602,14 +2614,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="E10">
-        <v>100</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="47">
         <v>46157</v>
       </c>
@@ -2621,14 +2627,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="E11">
-        <v>100</v>
-      </c>
-      <c r="F11">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="47">
         <v>46173</v>
       </c>
@@ -2640,14 +2640,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="E12">
-        <v>100</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="47">
         <v>46188</v>
       </c>
@@ -2659,14 +2653,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="E13">
-        <v>100</v>
-      </c>
-      <c r="F13">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="47">
         <v>46203</v>
       </c>
@@ -2679,7 +2667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="47">
         <v>46218</v>
       </c>
@@ -2692,7 +2680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="47">
         <v>46234</v>
       </c>
@@ -2705,7 +2693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="47">
         <v>46249</v>
       </c>
@@ -2718,7 +2706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="47">
         <v>46265</v>
       </c>
@@ -2731,7 +2719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="47">
         <v>46280</v>
       </c>
@@ -2744,7 +2732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="47">
         <v>46295</v>
       </c>
@@ -2757,7 +2745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="47">
         <v>46310</v>
       </c>
@@ -2770,7 +2758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="47">
         <v>46326</v>
       </c>
@@ -2783,7 +2771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="47">
         <v>46341</v>
       </c>
@@ -2796,7 +2784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="47">
         <v>46356</v>
       </c>
@@ -2809,7 +2797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="47">
         <v>46371</v>
       </c>
@@ -2822,7 +2810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="46" t="s">
         <v>50</v>
       </c>
@@ -2835,7 +2823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="46" t="s">
         <v>51</v>
       </c>
@@ -2848,7 +2836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="47">
         <v>46387</v>
       </c>
@@ -2861,7 +2849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="47">
         <v>46402</v>
       </c>
@@ -2874,7 +2862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="47">
         <v>46418</v>
       </c>
@@ -2887,7 +2875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="47">
         <v>46433</v>
       </c>
@@ -2900,7 +2888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="47">
         <v>46446</v>
       </c>
@@ -2913,7 +2901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="47">
         <v>46461</v>
       </c>
@@ -2926,7 +2914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="47">
         <v>46477</v>
       </c>
@@ -2939,7 +2927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="47">
         <v>46492</v>
       </c>
@@ -2952,7 +2940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="47">
         <v>46507</v>
       </c>
@@ -2965,7 +2953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="47">
         <v>46522</v>
       </c>
@@ -2978,7 +2966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="47">
         <v>46538</v>
       </c>
@@ -2991,7 +2979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="47">
         <v>46553</v>
       </c>
@@ -3004,7 +2992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="47">
         <v>46568</v>
       </c>
@@ -3017,7 +3005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="47">
         <v>46583</v>
       </c>
@@ -3030,7 +3018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="47">
         <v>46599</v>
       </c>
@@ -3043,7 +3031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="47">
         <v>46614</v>
       </c>
@@ -3056,7 +3044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="47">
         <v>46630</v>
       </c>
@@ -3069,7 +3057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="47">
         <v>46645</v>
       </c>
@@ -3082,7 +3070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="47">
         <v>46660</v>
       </c>
@@ -3095,7 +3083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="47">
         <v>46675</v>
       </c>
@@ -3108,7 +3096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="47">
         <v>46691</v>
       </c>
@@ -3121,7 +3109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="47">
         <v>46706</v>
       </c>
@@ -3134,7 +3122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="47">
         <v>46721</v>
       </c>
@@ -3147,7 +3135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="47">
         <v>46736</v>
       </c>
@@ -3160,7 +3148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="46" t="s">
         <v>50</v>
       </c>
@@ -3173,7 +3161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="46" t="s">
         <v>51</v>
       </c>
@@ -3186,7 +3174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="47">
         <v>46752</v>
       </c>
@@ -3199,44 +3187,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="50">
         <f>SUM(B2:B54)</f>
         <v>4610</v>
       </c>
       <c r="C55" s="51">
         <f>SUM(C2:C54)</f>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
     </row>
-    <row r="57" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="60">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
-        <v>-165</v>
+        <v>-135</v>
       </c>
       <c r="C57" s="61"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B58" s="59"/>
       <c r="C58" s="3"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B59"/>
       <c r="C59" s="3"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
     </row>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE53DA18-FD36-4D00-8E2B-A8F16C45E023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038B4F86-B4F7-4F75-83D3-7D6299207D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="2" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
   <si>
     <t>Totales</t>
   </si>
@@ -219,9 +219,6 @@
   </si>
   <si>
     <t>Tasa cero Sillones</t>
-  </si>
-  <si>
-    <t>x</t>
   </si>
 </sst>
 </file>
@@ -1263,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0DE2A9-9218-4E10-883D-DF66D771FC39}">
-  <dimension ref="B1:J37"/>
+  <dimension ref="B1:H37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -1273,7 +1270,7 @@
     <col min="7" max="7" width="3.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
         <v>14</v>
       </c>
@@ -1285,7 +1282,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1299,7 +1296,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
@@ -1312,11 +1309,8 @@
       <c r="F3" s="8">
         <v>50</v>
       </c>
-      <c r="G3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
@@ -1330,7 +1324,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
@@ -1344,7 +1338,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
@@ -1357,11 +1351,8 @@
       <c r="F6" s="8">
         <v>60</v>
       </c>
-      <c r="G6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>17</v>
       </c>
@@ -1374,11 +1365,8 @@
       <c r="F7" s="8">
         <v>100</v>
       </c>
-      <c r="G7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -1389,7 +1377,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -1399,23 +1387,16 @@
       <c r="F9">
         <v>10</v>
       </c>
-      <c r="G9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>16</v>
       </c>
       <c r="C10" t="s">
         <v>42</v>
       </c>
-      <c r="J10">
-        <f>770-583.32</f>
-        <v>186.67999999999995</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -1425,15 +1406,8 @@
       <c r="F11">
         <v>25</v>
       </c>
-      <c r="G11" t="s">
-        <v>60</v>
-      </c>
-      <c r="J11">
-        <f>J10/47</f>
-        <v>3.9719148936170203</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>9</v>
       </c>
@@ -1446,14 +1420,11 @@
       <c r="F12">
         <v>5</v>
       </c>
-      <c r="G12" t="s">
-        <v>60</v>
-      </c>
       <c r="H12">
         <v>8286917</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>10</v>
       </c>
@@ -1461,7 +1432,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>15</v>
       </c>
@@ -1471,11 +1442,8 @@
       <c r="F14">
         <v>31</v>
       </c>
-      <c r="G14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>59</v>
       </c>
@@ -1670,7 +1638,7 @@
         <v>46118</v>
       </c>
       <c r="J5" s="12">
-        <v>200.36</v>
+        <v>269</v>
       </c>
       <c r="K5" s="31">
         <v>0.27900000000000003</v>
@@ -1871,8 +1839,8 @@
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="21">
-        <f>SUBTOTAL(109,E3:E13)</f>
-        <v>138.68</v>
+        <f>SUM(SUBTOTAL(109,E3:E13)+F13)</f>
+        <v>186.19</v>
       </c>
       <c r="F14" s="21"/>
       <c r="G14" s="21">
@@ -1886,7 +1854,7 @@
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>305.33000000000004</v>
+        <v>373.97</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -1926,7 +1894,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="57">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2">
@@ -1941,7 +1909,7 @@
       <c r="I18" s="22"/>
       <c r="J18" s="23">
         <f>SUM(B18:I18)</f>
-        <v>360</v>
+        <v>429</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1960,7 +1928,7 @@
       </c>
       <c r="I20" s="25">
         <f>+H14+J14+G14</f>
-        <v>305.33000000000004</v>
+        <v>373.97</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1970,7 +1938,7 @@
       </c>
       <c r="I21" s="25">
         <f>+J18-H14-G14</f>
-        <v>360</v>
+        <v>429</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1980,7 +1948,7 @@
       </c>
       <c r="I22" s="25">
         <f>+I21-J14</f>
-        <v>54.669999999999959</v>
+        <v>55.029999999999973</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -2469,7 +2437,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAE522B-09DD-4490-9CA8-387DE173331A}">
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -2477,7 +2445,7 @@
     <col min="4" max="4" width="11.85546875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
         <v>49</v>
       </c>
@@ -2488,7 +2456,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="47"/>
       <c r="B2" s="11">
         <v>0</v>
@@ -2499,7 +2467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="47">
         <v>46037</v>
       </c>
@@ -2514,7 +2482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="47">
         <v>46053</v>
       </c>
@@ -2529,7 +2497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="47">
         <v>46068</v>
       </c>
@@ -2544,7 +2512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="47">
         <v>46081</v>
       </c>
@@ -2559,7 +2527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="47">
         <v>46096</v>
       </c>
@@ -2571,10 +2539,10 @@
       </c>
       <c r="D7" t="b">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="47">
         <v>46112</v>
       </c>
@@ -2586,10 +2554,10 @@
       </c>
       <c r="D8" t="b">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="47">
         <v>46127</v>
       </c>
@@ -2601,8 +2569,14 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="47">
         <v>46142</v>
       </c>
@@ -2614,8 +2588,11 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="47">
         <v>46157</v>
       </c>
@@ -2627,8 +2604,14 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11">
+        <v>100</v>
+      </c>
+      <c r="F11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="47">
         <v>46173</v>
       </c>
@@ -2640,8 +2623,11 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="47">
         <v>46188</v>
       </c>
@@ -2653,8 +2639,11 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="47">
         <v>46203</v>
       </c>
@@ -2666,8 +2655,11 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="47">
         <v>46218</v>
       </c>
@@ -2679,8 +2671,11 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="47">
         <v>46234</v>
       </c>
@@ -2692,8 +2687,11 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="47">
         <v>46249</v>
       </c>
@@ -2705,8 +2703,11 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="47">
         <v>46265</v>
       </c>
@@ -2718,8 +2719,11 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="47">
         <v>46280</v>
       </c>
@@ -2731,8 +2735,11 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="47">
         <v>46295</v>
       </c>
@@ -2744,8 +2751,11 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="47">
         <v>46310</v>
       </c>
@@ -2757,8 +2767,11 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="47">
         <v>46326</v>
       </c>
@@ -2770,8 +2783,11 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="47">
         <v>46341</v>
       </c>
@@ -2783,8 +2799,11 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="47">
         <v>46356</v>
       </c>
@@ -2796,8 +2815,11 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="47">
         <v>46371</v>
       </c>
@@ -2809,8 +2831,11 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="46" t="s">
         <v>50</v>
       </c>
@@ -2823,7 +2848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="46" t="s">
         <v>51</v>
       </c>
@@ -2836,7 +2861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="47">
         <v>46387</v>
       </c>
@@ -2848,8 +2873,11 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="47">
         <v>46402</v>
       </c>
@@ -2862,7 +2890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="47">
         <v>46418</v>
       </c>
@@ -2875,7 +2903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="47">
         <v>46433</v>
       </c>
@@ -2888,7 +2916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="47">
         <v>46446</v>
       </c>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038B4F86-B4F7-4F75-83D3-7D6299207D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9E0CB1-A7FE-43FA-9897-7347299446A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="2" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -30,9 +30,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -713,68 +710,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="21" formatCode="d\-mmm"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -920,6 +855,68 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="d\-mmm"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -939,7 +936,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="13" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="28" tableBorderDxfId="27">
   <autoFilter ref="A2:K14" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K14">
     <sortCondition ref="D3:D14"/>
@@ -947,17 +944,17 @@
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{4E2F1548-5DA7-4ADC-946F-053ED807460A}" name="Banco"/>
     <tableColumn id="2" xr3:uid="{11D77EA7-239F-47E1-9378-FFBA07ACDD06}" name="Tarjeta"/>
-    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="9">
+    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="24">
       <calculatedColumnFormula>186.68-48</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="3" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="23"/>
+    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="18" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1261,16 +1258,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0DE2A9-9218-4E10-883D-DF66D771FC39}">
   <dimension ref="B1:H37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="3.140625" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="3.109375" customWidth="1"/>
+    <col min="6" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1" s="13" t="s">
         <v>14</v>
       </c>
@@ -1282,7 +1279,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1296,7 +1293,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
@@ -1310,7 +1307,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
@@ -1324,7 +1321,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
@@ -1338,7 +1335,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
@@ -1352,7 +1349,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="9" t="s">
         <v>17</v>
       </c>
@@ -1366,7 +1363,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -1377,7 +1374,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -1388,7 +1385,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -1396,7 +1393,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -1407,7 +1404,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>9</v>
       </c>
@@ -1424,7 +1421,7 @@
         <v>8286917</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>10</v>
       </c>
@@ -1432,7 +1429,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>15</v>
       </c>
@@ -1443,7 +1440,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>59</v>
       </c>
@@ -1454,7 +1451,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>11</v>
       </c>
@@ -1468,7 +1465,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="s">
         <v>12</v>
       </c>
@@ -1481,7 +1478,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="5" t="s">
         <v>13</v>
       </c>
@@ -1495,24 +1492,24 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="37" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="30.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>$C$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
       <formula>$C$7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
       <formula>$C$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
       <formula>$C$2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1524,22 +1521,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B43D18-F407-4702-B159-A2C7E22E2016}">
   <dimension ref="A1:N131"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="19" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="12" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" style="12" customWidth="1"/>
-    <col min="7" max="8" width="16.140625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" style="10" customWidth="1"/>
-    <col min="10" max="10" width="17.42578125" style="12" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" style="19" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" style="12" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" style="12" customWidth="1"/>
+    <col min="7" max="8" width="16.109375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" style="10" customWidth="1"/>
+    <col min="10" max="10" width="17.44140625" style="12" customWidth="1"/>
+    <col min="11" max="11" width="7.109375" style="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
         <v>19</v>
       </c>
@@ -1574,7 +1571,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="39" t="s">
         <v>40</v>
       </c>
@@ -1582,7 +1579,7 @@
         <v>31</v>
       </c>
       <c r="C3" s="40">
-        <v>1750</v>
+        <v>2100</v>
       </c>
       <c r="D3" s="41">
         <v>45815</v>
@@ -1597,7 +1594,7 @@
       <c r="J3" s="42"/>
       <c r="K3" s="43"/>
     </row>
-    <row r="4" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="34" t="s">
         <v>56</v>
       </c>
@@ -1620,7 +1617,7 @@
       <c r="J4" s="37"/>
       <c r="K4" s="38"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -1645,7 +1642,7 @@
       </c>
       <c r="N5" s="4"/>
     </row>
-    <row r="6" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1670,7 +1667,7 @@
       </c>
       <c r="K6" s="31"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -1692,7 +1689,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34" t="s">
         <v>39</v>
       </c>
@@ -1700,7 +1697,7 @@
         <v>30</v>
       </c>
       <c r="C8" s="35">
-        <v>1350</v>
+        <v>1600</v>
       </c>
       <c r="D8" s="36">
         <v>45822</v>
@@ -1715,7 +1712,7 @@
       <c r="J8" s="37"/>
       <c r="K8" s="38"/>
     </row>
-    <row r="9" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="52" t="s">
         <v>29</v>
       </c>
@@ -1738,7 +1735,7 @@
       <c r="J9" s="44"/>
       <c r="K9" s="54"/>
     </row>
-    <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1761,7 +1758,7 @@
       <c r="J10" s="12"/>
       <c r="K10" s="31"/>
     </row>
-    <row r="11" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
         <v>29</v>
       </c>
@@ -1784,7 +1781,7 @@
       <c r="J11" s="37"/>
       <c r="K11" s="38"/>
     </row>
-    <row r="12" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="39" t="s">
         <v>58</v>
       </c>
@@ -1807,7 +1804,7 @@
       <c r="J12" s="42"/>
       <c r="K12" s="43"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="39" t="s">
         <v>58</v>
       </c>
@@ -1829,13 +1826,13 @@
         <v>45946</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>0</v>
       </c>
       <c r="C14" s="21">
         <f>SUBTOTAL(109,C3:C13)</f>
-        <v>14335</v>
+        <v>14935</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="21">
@@ -1857,16 +1854,16 @@
         <v>373.97</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D15" s="20"/>
       <c r="I15" s="20"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D16" s="20"/>
       <c r="I16" s="20"/>
     </row>
-    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1889,7 +1886,7 @@
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
     </row>
-    <row r="18" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1912,7 +1909,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="55"/>
@@ -1921,7 +1918,7 @@
       <c r="H19" s="2"/>
       <c r="I19" s="20"/>
     </row>
-    <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D20" s="12"/>
       <c r="H20" s="56" t="s">
         <v>37</v>
@@ -1931,7 +1928,7 @@
         <v>373.97</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D21" s="12"/>
       <c r="H21" s="26" t="s">
         <v>38</v>
@@ -1941,7 +1938,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D22" s="20"/>
       <c r="H22" s="27" t="s">
         <v>54</v>
@@ -1951,479 +1948,479 @@
         <v>55.029999999999973</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D23" s="12"/>
       <c r="I23" s="20"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D24" s="12"/>
       <c r="I24" s="20"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D25" s="12"/>
       <c r="I25" s="20"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D26" s="12"/>
       <c r="I26" s="20"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D27" s="12"/>
       <c r="I27" s="20"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D28" s="12"/>
       <c r="I28" s="20"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D29" s="12"/>
       <c r="I29" s="20"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D30" s="11"/>
       <c r="I30" s="20"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D31" s="20"/>
       <c r="I31" s="20"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D32" s="11"/>
       <c r="I32" s="20"/>
     </row>
-    <row r="33" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D33" s="11"/>
       <c r="I33" s="20"/>
     </row>
-    <row r="34" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D34" s="11"/>
       <c r="I34" s="20"/>
     </row>
-    <row r="35" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D35" s="11"/>
       <c r="I35" s="20"/>
     </row>
-    <row r="36" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D36" s="11"/>
       <c r="I36" s="20"/>
     </row>
-    <row r="37" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D37" s="11"/>
       <c r="I37" s="20"/>
     </row>
-    <row r="38" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D38" s="11"/>
       <c r="I38" s="20"/>
     </row>
-    <row r="39" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D39" s="11"/>
       <c r="I39" s="20"/>
     </row>
-    <row r="40" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D40" s="11"/>
       <c r="I40" s="20"/>
     </row>
-    <row r="41" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D41" s="20"/>
       <c r="I41" s="20"/>
     </row>
-    <row r="42" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D42" s="12"/>
       <c r="I42" s="20"/>
     </row>
-    <row r="43" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D43" s="12"/>
       <c r="I43" s="20"/>
     </row>
-    <row r="44" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D44" s="20"/>
       <c r="I44" s="20"/>
     </row>
-    <row r="45" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D45" s="20"/>
       <c r="I45" s="20"/>
     </row>
-    <row r="46" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D46" s="20"/>
       <c r="I46" s="20"/>
     </row>
-    <row r="47" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D47" s="20"/>
       <c r="I47" s="20"/>
     </row>
-    <row r="48" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D48" s="20"/>
       <c r="I48" s="20"/>
     </row>
-    <row r="49" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D49" s="20"/>
       <c r="I49" s="20"/>
     </row>
-    <row r="50" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D50" s="20"/>
       <c r="I50" s="20"/>
     </row>
-    <row r="51" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D51" s="20"/>
       <c r="I51" s="20"/>
     </row>
-    <row r="52" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D52" s="20"/>
       <c r="I52" s="20"/>
     </row>
-    <row r="53" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D53" s="20"/>
       <c r="I53" s="20"/>
     </row>
-    <row r="54" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D54" s="20"/>
       <c r="I54" s="20"/>
     </row>
-    <row r="55" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D55" s="20"/>
       <c r="I55" s="20"/>
     </row>
-    <row r="56" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D56" s="20"/>
       <c r="I56" s="20"/>
     </row>
-    <row r="57" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D57" s="20"/>
       <c r="I57" s="20"/>
     </row>
-    <row r="58" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D58" s="20"/>
       <c r="I58" s="20"/>
     </row>
-    <row r="59" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D59" s="20"/>
       <c r="I59" s="20"/>
     </row>
-    <row r="60" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D60" s="20"/>
       <c r="I60" s="20"/>
     </row>
-    <row r="61" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D61" s="20"/>
       <c r="I61" s="20"/>
     </row>
-    <row r="62" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D62" s="20"/>
       <c r="I62" s="20"/>
     </row>
-    <row r="63" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D63" s="20"/>
       <c r="I63" s="20"/>
     </row>
-    <row r="64" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D64" s="20"/>
       <c r="I64" s="20"/>
     </row>
-    <row r="65" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D65" s="20"/>
       <c r="I65" s="20"/>
     </row>
-    <row r="66" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D66" s="20"/>
       <c r="I66" s="20"/>
     </row>
-    <row r="67" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D67" s="20"/>
       <c r="I67" s="20"/>
     </row>
-    <row r="68" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D68" s="20"/>
       <c r="I68" s="20"/>
     </row>
-    <row r="69" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D69" s="20"/>
       <c r="I69" s="20"/>
     </row>
-    <row r="70" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D70" s="20"/>
       <c r="I70" s="20"/>
     </row>
-    <row r="71" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D71" s="20"/>
       <c r="I71" s="20"/>
     </row>
-    <row r="72" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D72" s="20"/>
       <c r="I72" s="20"/>
     </row>
-    <row r="73" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D73" s="20"/>
       <c r="I73" s="20"/>
     </row>
-    <row r="74" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D74" s="20"/>
       <c r="I74" s="20"/>
     </row>
-    <row r="75" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D75" s="20"/>
       <c r="I75" s="20"/>
     </row>
-    <row r="76" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D76" s="20"/>
       <c r="I76" s="20"/>
     </row>
-    <row r="77" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D77" s="20"/>
       <c r="I77" s="20"/>
     </row>
-    <row r="78" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D78" s="20"/>
       <c r="I78" s="20"/>
     </row>
-    <row r="79" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D79" s="20"/>
       <c r="I79" s="20"/>
     </row>
-    <row r="80" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D80" s="20"/>
       <c r="I80" s="20"/>
     </row>
-    <row r="81" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D81" s="20"/>
       <c r="I81" s="20"/>
     </row>
-    <row r="82" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D82" s="20"/>
       <c r="I82" s="20"/>
     </row>
-    <row r="83" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D83" s="20"/>
       <c r="I83" s="20"/>
     </row>
-    <row r="84" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D84" s="20"/>
       <c r="I84" s="20"/>
     </row>
-    <row r="85" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D85" s="20"/>
       <c r="I85" s="20"/>
     </row>
-    <row r="86" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D86" s="20"/>
       <c r="I86" s="20"/>
     </row>
-    <row r="87" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D87" s="20"/>
       <c r="I87" s="20"/>
     </row>
-    <row r="88" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D88" s="20"/>
       <c r="I88" s="20"/>
     </row>
-    <row r="89" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D89" s="20"/>
       <c r="I89" s="20"/>
     </row>
-    <row r="90" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D90" s="20"/>
       <c r="I90" s="20"/>
     </row>
-    <row r="91" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D91" s="20"/>
       <c r="I91" s="20"/>
     </row>
-    <row r="92" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D92" s="20"/>
       <c r="I92" s="20"/>
     </row>
-    <row r="93" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D93" s="20"/>
       <c r="I93" s="20"/>
     </row>
-    <row r="94" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D94" s="20"/>
       <c r="I94" s="20"/>
     </row>
-    <row r="95" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D95" s="20"/>
       <c r="I95" s="20"/>
     </row>
-    <row r="96" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D96" s="20"/>
       <c r="I96" s="20"/>
     </row>
-    <row r="97" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D97" s="20"/>
       <c r="I97" s="20"/>
     </row>
-    <row r="98" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D98" s="20"/>
       <c r="I98" s="20"/>
     </row>
-    <row r="99" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D99" s="20"/>
       <c r="I99" s="20"/>
     </row>
-    <row r="100" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D100" s="20"/>
       <c r="I100" s="20"/>
     </row>
-    <row r="101" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D101" s="20"/>
       <c r="I101" s="20"/>
     </row>
-    <row r="102" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D102" s="20"/>
       <c r="I102" s="20"/>
     </row>
-    <row r="103" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D103" s="20"/>
       <c r="I103" s="20"/>
     </row>
-    <row r="104" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D104" s="20"/>
       <c r="I104" s="20"/>
     </row>
-    <row r="105" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D105" s="20"/>
       <c r="I105" s="20"/>
     </row>
-    <row r="106" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D106" s="20"/>
       <c r="I106" s="20"/>
     </row>
-    <row r="107" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D107" s="20"/>
       <c r="I107" s="20"/>
     </row>
-    <row r="108" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D108" s="20"/>
       <c r="I108" s="20"/>
     </row>
-    <row r="109" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D109" s="20"/>
       <c r="I109" s="20"/>
     </row>
-    <row r="110" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D110" s="20"/>
       <c r="I110" s="20"/>
     </row>
-    <row r="111" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D111" s="20"/>
       <c r="I111" s="20"/>
     </row>
-    <row r="112" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D112" s="20"/>
       <c r="I112" s="20"/>
     </row>
-    <row r="113" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D113" s="20"/>
       <c r="I113" s="20"/>
     </row>
-    <row r="114" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D114" s="20"/>
       <c r="I114" s="20"/>
     </row>
-    <row r="115" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D115" s="20"/>
       <c r="I115" s="20"/>
     </row>
-    <row r="116" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D116" s="20"/>
       <c r="I116" s="20"/>
     </row>
-    <row r="117" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D117" s="20"/>
       <c r="I117" s="20"/>
     </row>
-    <row r="118" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D118" s="20"/>
       <c r="I118" s="20"/>
     </row>
-    <row r="119" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D119" s="20"/>
       <c r="I119" s="20"/>
     </row>
-    <row r="120" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D120" s="20"/>
       <c r="I120" s="20"/>
     </row>
-    <row r="121" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D121" s="20"/>
       <c r="I121" s="20"/>
     </row>
-    <row r="122" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D122" s="20"/>
       <c r="I122" s="20"/>
     </row>
-    <row r="123" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D123" s="20"/>
       <c r="I123" s="20"/>
     </row>
-    <row r="124" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D124" s="20"/>
       <c r="I124" s="20"/>
     </row>
-    <row r="125" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D125" s="20"/>
       <c r="I125" s="20"/>
     </row>
-    <row r="126" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I126" s="20"/>
     </row>
-    <row r="127" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I127" s="20"/>
     </row>
-    <row r="128" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I128" s="20"/>
     </row>
-    <row r="129" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I129" s="20"/>
     </row>
-    <row r="130" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I130" s="20"/>
     </row>
-    <row r="131" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I131" s="20"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D16">
-    <cfRule type="timePeriod" dxfId="24" priority="37" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="13" priority="37" timePeriod="nextMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0+1)),YEAR(D1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="23" priority="38" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="12" priority="38" timePeriod="thisMonth">
       <formula>AND(MONTH(D1)=MONTH(TODAY()),YEAR(D1)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="22" priority="39" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="11" priority="39" timePeriod="lastMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0-1)),YEAR(D1)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D22:D29 D31 D41:D1048576">
-    <cfRule type="timePeriod" dxfId="21" priority="1" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="10" priority="1" timePeriod="nextMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0+1)),YEAR(D22)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="20" priority="2" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="9" priority="2" timePeriod="thisMonth">
       <formula>AND(MONTH(D22)=MONTH(TODAY()),YEAR(D22)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="19" priority="3" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="8" priority="3" timePeriod="lastMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0-1)),YEAR(D22)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="timePeriod" dxfId="18" priority="40" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="7" priority="40" timePeriod="nextMonth">
       <formula>AND(MONTH(I1)=MONTH(EDATE(TODAY(),0+1)),YEAR(I1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="17" priority="41" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="6" priority="41" timePeriod="thisMonth">
       <formula>AND(MONTH(I1)=MONTH(TODAY()),YEAR(I1)=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="cellIs" dxfId="16" priority="45" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="45" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I22">
-    <cfRule type="cellIs" dxfId="15" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="42" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
-    <cfRule type="cellIs" dxfId="14" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="43" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2438,14 +2435,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAE522B-09DD-4490-9CA8-387DE173331A}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
-    <col min="2" max="3" width="11.42578125" style="12"/>
-    <col min="4" max="4" width="11.85546875" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="11.44140625" style="12"/>
+    <col min="4" max="4" width="11.88671875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="45" t="s">
         <v>49</v>
       </c>
@@ -2456,7 +2453,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="47"/>
       <c r="B2" s="11">
         <v>0</v>
@@ -2467,7 +2464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="47">
         <v>46037</v>
       </c>
@@ -2482,7 +2479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="47">
         <v>46053</v>
       </c>
@@ -2497,7 +2494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="47">
         <v>46068</v>
       </c>
@@ -2512,7 +2509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="47">
         <v>46081</v>
       </c>
@@ -2527,7 +2524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="47">
         <v>46096</v>
       </c>
@@ -2542,7 +2539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="47">
         <v>46112</v>
       </c>
@@ -2557,7 +2554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="47">
         <v>46127</v>
       </c>
@@ -2576,7 +2573,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="47">
         <v>46142</v>
       </c>
@@ -2592,7 +2589,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="47">
         <v>46157</v>
       </c>
@@ -2611,7 +2608,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="47">
         <v>46173</v>
       </c>
@@ -2627,7 +2624,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="47">
         <v>46188</v>
       </c>
@@ -2643,7 +2640,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="47">
         <v>46203</v>
       </c>
@@ -2659,7 +2656,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="47">
         <v>46218</v>
       </c>
@@ -2675,7 +2672,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="47">
         <v>46234</v>
       </c>
@@ -2691,7 +2688,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="47">
         <v>46249</v>
       </c>
@@ -2707,7 +2704,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="47">
         <v>46265</v>
       </c>
@@ -2723,7 +2720,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="47">
         <v>46280</v>
       </c>
@@ -2739,7 +2736,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="47">
         <v>46295</v>
       </c>
@@ -2755,7 +2752,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="47">
         <v>46310</v>
       </c>
@@ -2771,7 +2768,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="47">
         <v>46326</v>
       </c>
@@ -2787,7 +2784,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="47">
         <v>46341</v>
       </c>
@@ -2803,7 +2800,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="47">
         <v>46356</v>
       </c>
@@ -2819,7 +2816,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="47">
         <v>46371</v>
       </c>
@@ -2835,7 +2832,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="46" t="s">
         <v>50</v>
       </c>
@@ -2848,7 +2845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="46" t="s">
         <v>51</v>
       </c>
@@ -2861,7 +2858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="47">
         <v>46387</v>
       </c>
@@ -2877,7 +2874,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="47">
         <v>46402</v>
       </c>
@@ -2890,7 +2887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="47">
         <v>46418</v>
       </c>
@@ -2903,7 +2900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="47">
         <v>46433</v>
       </c>
@@ -2916,7 +2913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="47">
         <v>46446</v>
       </c>
@@ -2929,7 +2926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="47">
         <v>46461</v>
       </c>
@@ -2942,7 +2939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="47">
         <v>46477</v>
       </c>
@@ -2955,7 +2952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="47">
         <v>46492</v>
       </c>
@@ -2968,7 +2965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="47">
         <v>46507</v>
       </c>
@@ -2981,7 +2978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="47">
         <v>46522</v>
       </c>
@@ -2994,7 +2991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="47">
         <v>46538</v>
       </c>
@@ -3007,7 +3004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="47">
         <v>46553</v>
       </c>
@@ -3020,7 +3017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="47">
         <v>46568</v>
       </c>
@@ -3033,7 +3030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="47">
         <v>46583</v>
       </c>
@@ -3046,7 +3043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="47">
         <v>46599</v>
       </c>
@@ -3059,7 +3056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="47">
         <v>46614</v>
       </c>
@@ -3072,7 +3069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="47">
         <v>46630</v>
       </c>
@@ -3085,7 +3082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="47">
         <v>46645</v>
       </c>
@@ -3098,7 +3095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="47">
         <v>46660</v>
       </c>
@@ -3111,7 +3108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="47">
         <v>46675</v>
       </c>
@@ -3124,7 +3121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="47">
         <v>46691</v>
       </c>
@@ -3137,7 +3134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="47">
         <v>46706</v>
       </c>
@@ -3150,7 +3147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="47">
         <v>46721</v>
       </c>
@@ -3163,7 +3160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="47">
         <v>46736</v>
       </c>
@@ -3176,7 +3173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="46" t="s">
         <v>50</v>
       </c>
@@ -3189,7 +3186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="46" t="s">
         <v>51</v>
       </c>
@@ -3202,7 +3199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="47">
         <v>46752</v>
       </c>
@@ -3215,7 +3212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="50">
         <f>SUM(B2:B54)</f>
         <v>4610</v>
@@ -3225,34 +3222,34 @@
         <v>300</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
     </row>
-    <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="60">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
         <v>-135</v>
       </c>
       <c r="C57" s="61"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B58" s="59"/>
       <c r="C58" s="3"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B59"/>
       <c r="C59" s="3"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
     </row>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9E0CB1-A7FE-43FA-9897-7347299446A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B40E0D-5E11-47F6-A76D-F82B458B0319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="61">
   <si>
     <t>Totales</t>
   </si>
@@ -216,6 +219,9 @@
   </si>
   <si>
     <t>Tasa cero Sillones</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -710,6 +716,68 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="21" formatCode="d\-mmm"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -855,68 +923,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="d\-mmm"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -936,7 +942,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="28" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="13" tableBorderDxfId="12">
   <autoFilter ref="A2:K14" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K14">
     <sortCondition ref="D3:D14"/>
@@ -944,17 +950,17 @@
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{4E2F1548-5DA7-4ADC-946F-053ED807460A}" name="Banco"/>
     <tableColumn id="2" xr3:uid="{11D77EA7-239F-47E1-9378-FFBA07ACDD06}" name="Tarjeta"/>
-    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="24">
+    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="9">
       <calculatedColumnFormula>186.68-48</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="23"/>
-    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="18" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="3" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1258,16 +1264,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0DE2A9-9218-4E10-883D-DF66D771FC39}">
   <dimension ref="B1:H37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="3.109375" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="3.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
         <v>14</v>
       </c>
@@ -1279,7 +1285,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1293,7 +1299,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
@@ -1303,11 +1309,14 @@
       <c r="D3" s="8">
         <v>50</v>
       </c>
+      <c r="E3" t="s">
+        <v>60</v>
+      </c>
       <c r="F3" s="8">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
@@ -1317,11 +1326,14 @@
       <c r="D4" s="8">
         <v>10</v>
       </c>
+      <c r="E4" t="s">
+        <v>60</v>
+      </c>
       <c r="F4" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
@@ -1335,7 +1347,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
@@ -1345,11 +1357,14 @@
       <c r="D6" s="8">
         <v>60</v>
       </c>
+      <c r="E6" t="s">
+        <v>60</v>
+      </c>
       <c r="F6" s="8">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>17</v>
       </c>
@@ -1359,11 +1374,14 @@
       <c r="D7" s="8">
         <v>100</v>
       </c>
+      <c r="E7" t="s">
+        <v>60</v>
+      </c>
       <c r="F7" s="8">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -1373,8 +1391,11 @@
       <c r="D8" s="58">
         <v>95</v>
       </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="E8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -1385,7 +1406,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -1393,7 +1414,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -1404,7 +1425,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>9</v>
       </c>
@@ -1414,6 +1435,9 @@
       <c r="D12">
         <v>15</v>
       </c>
+      <c r="E12" t="s">
+        <v>60</v>
+      </c>
       <c r="F12">
         <v>5</v>
       </c>
@@ -1421,7 +1445,7 @@
         <v>8286917</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>10</v>
       </c>
@@ -1429,7 +1453,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>15</v>
       </c>
@@ -1440,7 +1464,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>59</v>
       </c>
@@ -1450,8 +1474,11 @@
       <c r="D15">
         <v>48</v>
       </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="7" t="s">
         <v>11</v>
       </c>
@@ -1465,7 +1492,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
         <v>12</v>
       </c>
@@ -1478,7 +1505,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>13</v>
       </c>
@@ -1492,24 +1519,24 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="37" ht="30.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
       <formula>$C$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
       <formula>$C$7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="equal">
       <formula>$C$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="4" operator="equal">
       <formula>$C$2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1521,22 +1548,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B43D18-F407-4702-B159-A2C7E22E2016}">
   <dimension ref="A1:N131"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" style="19" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" style="12" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" style="12" customWidth="1"/>
-    <col min="7" max="8" width="16.109375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" style="10" customWidth="1"/>
-    <col min="10" max="10" width="17.44140625" style="12" customWidth="1"/>
-    <col min="11" max="11" width="7.109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" style="12" customWidth="1"/>
+    <col min="7" max="8" width="16.140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" style="10" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" style="12" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" style="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>19</v>
       </c>
@@ -1571,7 +1598,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
         <v>40</v>
       </c>
@@ -1594,7 +1621,7 @@
       <c r="J3" s="42"/>
       <c r="K3" s="43"/>
     </row>
-    <row r="4" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="34" t="s">
         <v>56</v>
       </c>
@@ -1617,7 +1644,7 @@
       <c r="J4" s="37"/>
       <c r="K4" s="38"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -1630,19 +1657,21 @@
       <c r="D5" s="20">
         <v>45817</v>
       </c>
-      <c r="H5" s="12"/>
+      <c r="H5" s="12">
+        <v>280.05</v>
+      </c>
       <c r="I5" s="20">
         <v>46118</v>
       </c>
       <c r="J5" s="12">
-        <v>269</v>
+        <v>57.18</v>
       </c>
       <c r="K5" s="31">
         <v>0.27900000000000003</v>
       </c>
       <c r="N5" s="4"/>
     </row>
-    <row r="6" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1658,16 +1687,16 @@
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
-      <c r="H6" s="33"/>
+      <c r="H6" s="33">
+        <v>104.97</v>
+      </c>
       <c r="I6" s="20">
-        <v>46118</v>
-      </c>
-      <c r="J6" s="12">
-        <v>104.97</v>
-      </c>
+        <v>46148</v>
+      </c>
+      <c r="J6" s="12"/>
       <c r="K6" s="31"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -1689,7 +1718,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
         <v>39</v>
       </c>
@@ -1712,7 +1741,7 @@
       <c r="J8" s="37"/>
       <c r="K8" s="38"/>
     </row>
-    <row r="9" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
         <v>29</v>
       </c>
@@ -1735,7 +1764,7 @@
       <c r="J9" s="44"/>
       <c r="K9" s="54"/>
     </row>
-    <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1758,7 +1787,7 @@
       <c r="J10" s="12"/>
       <c r="K10" s="31"/>
     </row>
-    <row r="11" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
         <v>29</v>
       </c>
@@ -1781,7 +1810,7 @@
       <c r="J11" s="37"/>
       <c r="K11" s="38"/>
     </row>
-    <row r="12" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
         <v>58</v>
       </c>
@@ -1804,7 +1833,7 @@
       <c r="J12" s="42"/>
       <c r="K12" s="43"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="39" t="s">
         <v>58</v>
       </c>
@@ -1826,7 +1855,7 @@
         <v>45946</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -1846,24 +1875,24 @@
       </c>
       <c r="H14" s="21">
         <f>SUBTOTAL(109,H3:H13)</f>
-        <v>0</v>
+        <v>385.02</v>
       </c>
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>373.97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+        <v>57.18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D15" s="20"/>
       <c r="I15" s="20"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D16" s="20"/>
       <c r="I16" s="20"/>
     </row>
-    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1871,9 +1900,7 @@
         <v>36</v>
       </c>
       <c r="C17" s="24"/>
-      <c r="D17" s="24">
-        <v>46127</v>
-      </c>
+      <c r="D17" s="24"/>
       <c r="E17" s="24">
         <v>46142</v>
       </c>
@@ -1886,17 +1913,15 @@
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
     </row>
-    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B18" s="57">
-        <v>319</v>
+        <v>406</v>
       </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="2">
-        <v>40</v>
-      </c>
+      <c r="D18" s="2"/>
       <c r="E18" s="2">
         <v>70</v>
       </c>
@@ -1906,10 +1931,10 @@
       <c r="I18" s="22"/>
       <c r="J18" s="23">
         <f>SUM(B18:I18)</f>
-        <v>429</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="55"/>
@@ -1918,509 +1943,509 @@
       <c r="H19" s="2"/>
       <c r="I19" s="20"/>
     </row>
-    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D20" s="12"/>
       <c r="H20" s="56" t="s">
         <v>37</v>
       </c>
       <c r="I20" s="25">
         <f>+H14+J14+G14</f>
-        <v>373.97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>442.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D21" s="12"/>
       <c r="H21" s="26" t="s">
         <v>38</v>
       </c>
       <c r="I21" s="25">
         <f>+J18-H14-G14</f>
-        <v>429</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>90.980000000000018</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D22" s="20"/>
       <c r="H22" s="27" t="s">
         <v>54</v>
       </c>
       <c r="I22" s="25">
         <f>+I21-J14</f>
-        <v>55.029999999999973</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+        <v>33.800000000000018</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D23" s="12"/>
       <c r="I23" s="20"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D24" s="12"/>
       <c r="I24" s="20"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D25" s="12"/>
       <c r="I25" s="20"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D26" s="12"/>
       <c r="I26" s="20"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D27" s="12"/>
       <c r="I27" s="20"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D28" s="12"/>
       <c r="I28" s="20"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D29" s="12"/>
       <c r="I29" s="20"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D30" s="11"/>
       <c r="I30" s="20"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D31" s="20"/>
       <c r="I31" s="20"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D32" s="11"/>
       <c r="I32" s="20"/>
     </row>
-    <row r="33" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D33" s="11"/>
       <c r="I33" s="20"/>
     </row>
-    <row r="34" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D34" s="11"/>
       <c r="I34" s="20"/>
     </row>
-    <row r="35" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D35" s="11"/>
       <c r="I35" s="20"/>
     </row>
-    <row r="36" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D36" s="11"/>
       <c r="I36" s="20"/>
     </row>
-    <row r="37" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D37" s="11"/>
       <c r="I37" s="20"/>
     </row>
-    <row r="38" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D38" s="11"/>
       <c r="I38" s="20"/>
     </row>
-    <row r="39" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D39" s="11"/>
       <c r="I39" s="20"/>
     </row>
-    <row r="40" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D40" s="11"/>
       <c r="I40" s="20"/>
     </row>
-    <row r="41" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D41" s="20"/>
       <c r="I41" s="20"/>
     </row>
-    <row r="42" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D42" s="12"/>
       <c r="I42" s="20"/>
     </row>
-    <row r="43" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D43" s="12"/>
       <c r="I43" s="20"/>
     </row>
-    <row r="44" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D44" s="20"/>
       <c r="I44" s="20"/>
     </row>
-    <row r="45" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D45" s="20"/>
       <c r="I45" s="20"/>
     </row>
-    <row r="46" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D46" s="20"/>
       <c r="I46" s="20"/>
     </row>
-    <row r="47" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D47" s="20"/>
       <c r="I47" s="20"/>
     </row>
-    <row r="48" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D48" s="20"/>
       <c r="I48" s="20"/>
     </row>
-    <row r="49" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D49" s="20"/>
       <c r="I49" s="20"/>
     </row>
-    <row r="50" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D50" s="20"/>
       <c r="I50" s="20"/>
     </row>
-    <row r="51" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D51" s="20"/>
       <c r="I51" s="20"/>
     </row>
-    <row r="52" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D52" s="20"/>
       <c r="I52" s="20"/>
     </row>
-    <row r="53" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D53" s="20"/>
       <c r="I53" s="20"/>
     </row>
-    <row r="54" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D54" s="20"/>
       <c r="I54" s="20"/>
     </row>
-    <row r="55" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D55" s="20"/>
       <c r="I55" s="20"/>
     </row>
-    <row r="56" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D56" s="20"/>
       <c r="I56" s="20"/>
     </row>
-    <row r="57" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D57" s="20"/>
       <c r="I57" s="20"/>
     </row>
-    <row r="58" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D58" s="20"/>
       <c r="I58" s="20"/>
     </row>
-    <row r="59" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D59" s="20"/>
       <c r="I59" s="20"/>
     </row>
-    <row r="60" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D60" s="20"/>
       <c r="I60" s="20"/>
     </row>
-    <row r="61" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D61" s="20"/>
       <c r="I61" s="20"/>
     </row>
-    <row r="62" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D62" s="20"/>
       <c r="I62" s="20"/>
     </row>
-    <row r="63" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D63" s="20"/>
       <c r="I63" s="20"/>
     </row>
-    <row r="64" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D64" s="20"/>
       <c r="I64" s="20"/>
     </row>
-    <row r="65" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D65" s="20"/>
       <c r="I65" s="20"/>
     </row>
-    <row r="66" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D66" s="20"/>
       <c r="I66" s="20"/>
     </row>
-    <row r="67" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D67" s="20"/>
       <c r="I67" s="20"/>
     </row>
-    <row r="68" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D68" s="20"/>
       <c r="I68" s="20"/>
     </row>
-    <row r="69" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D69" s="20"/>
       <c r="I69" s="20"/>
     </row>
-    <row r="70" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D70" s="20"/>
       <c r="I70" s="20"/>
     </row>
-    <row r="71" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D71" s="20"/>
       <c r="I71" s="20"/>
     </row>
-    <row r="72" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D72" s="20"/>
       <c r="I72" s="20"/>
     </row>
-    <row r="73" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D73" s="20"/>
       <c r="I73" s="20"/>
     </row>
-    <row r="74" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D74" s="20"/>
       <c r="I74" s="20"/>
     </row>
-    <row r="75" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D75" s="20"/>
       <c r="I75" s="20"/>
     </row>
-    <row r="76" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D76" s="20"/>
       <c r="I76" s="20"/>
     </row>
-    <row r="77" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D77" s="20"/>
       <c r="I77" s="20"/>
     </row>
-    <row r="78" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D78" s="20"/>
       <c r="I78" s="20"/>
     </row>
-    <row r="79" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D79" s="20"/>
       <c r="I79" s="20"/>
     </row>
-    <row r="80" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D80" s="20"/>
       <c r="I80" s="20"/>
     </row>
-    <row r="81" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D81" s="20"/>
       <c r="I81" s="20"/>
     </row>
-    <row r="82" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D82" s="20"/>
       <c r="I82" s="20"/>
     </row>
-    <row r="83" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D83" s="20"/>
       <c r="I83" s="20"/>
     </row>
-    <row r="84" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D84" s="20"/>
       <c r="I84" s="20"/>
     </row>
-    <row r="85" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D85" s="20"/>
       <c r="I85" s="20"/>
     </row>
-    <row r="86" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D86" s="20"/>
       <c r="I86" s="20"/>
     </row>
-    <row r="87" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D87" s="20"/>
       <c r="I87" s="20"/>
     </row>
-    <row r="88" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D88" s="20"/>
       <c r="I88" s="20"/>
     </row>
-    <row r="89" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D89" s="20"/>
       <c r="I89" s="20"/>
     </row>
-    <row r="90" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D90" s="20"/>
       <c r="I90" s="20"/>
     </row>
-    <row r="91" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D91" s="20"/>
       <c r="I91" s="20"/>
     </row>
-    <row r="92" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D92" s="20"/>
       <c r="I92" s="20"/>
     </row>
-    <row r="93" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D93" s="20"/>
       <c r="I93" s="20"/>
     </row>
-    <row r="94" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D94" s="20"/>
       <c r="I94" s="20"/>
     </row>
-    <row r="95" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D95" s="20"/>
       <c r="I95" s="20"/>
     </row>
-    <row r="96" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D96" s="20"/>
       <c r="I96" s="20"/>
     </row>
-    <row r="97" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D97" s="20"/>
       <c r="I97" s="20"/>
     </row>
-    <row r="98" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D98" s="20"/>
       <c r="I98" s="20"/>
     </row>
-    <row r="99" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D99" s="20"/>
       <c r="I99" s="20"/>
     </row>
-    <row r="100" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D100" s="20"/>
       <c r="I100" s="20"/>
     </row>
-    <row r="101" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D101" s="20"/>
       <c r="I101" s="20"/>
     </row>
-    <row r="102" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D102" s="20"/>
       <c r="I102" s="20"/>
     </row>
-    <row r="103" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D103" s="20"/>
       <c r="I103" s="20"/>
     </row>
-    <row r="104" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D104" s="20"/>
       <c r="I104" s="20"/>
     </row>
-    <row r="105" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D105" s="20"/>
       <c r="I105" s="20"/>
     </row>
-    <row r="106" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D106" s="20"/>
       <c r="I106" s="20"/>
     </row>
-    <row r="107" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D107" s="20"/>
       <c r="I107" s="20"/>
     </row>
-    <row r="108" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D108" s="20"/>
       <c r="I108" s="20"/>
     </row>
-    <row r="109" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D109" s="20"/>
       <c r="I109" s="20"/>
     </row>
-    <row r="110" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D110" s="20"/>
       <c r="I110" s="20"/>
     </row>
-    <row r="111" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D111" s="20"/>
       <c r="I111" s="20"/>
     </row>
-    <row r="112" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D112" s="20"/>
       <c r="I112" s="20"/>
     </row>
-    <row r="113" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D113" s="20"/>
       <c r="I113" s="20"/>
     </row>
-    <row r="114" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D114" s="20"/>
       <c r="I114" s="20"/>
     </row>
-    <row r="115" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D115" s="20"/>
       <c r="I115" s="20"/>
     </row>
-    <row r="116" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D116" s="20"/>
       <c r="I116" s="20"/>
     </row>
-    <row r="117" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D117" s="20"/>
       <c r="I117" s="20"/>
     </row>
-    <row r="118" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D118" s="20"/>
       <c r="I118" s="20"/>
     </row>
-    <row r="119" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D119" s="20"/>
       <c r="I119" s="20"/>
     </row>
-    <row r="120" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D120" s="20"/>
       <c r="I120" s="20"/>
     </row>
-    <row r="121" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D121" s="20"/>
       <c r="I121" s="20"/>
     </row>
-    <row r="122" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D122" s="20"/>
       <c r="I122" s="20"/>
     </row>
-    <row r="123" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D123" s="20"/>
       <c r="I123" s="20"/>
     </row>
-    <row r="124" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D124" s="20"/>
       <c r="I124" s="20"/>
     </row>
-    <row r="125" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D125" s="20"/>
       <c r="I125" s="20"/>
     </row>
-    <row r="126" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I126" s="20"/>
     </row>
-    <row r="127" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I127" s="20"/>
     </row>
-    <row r="128" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I128" s="20"/>
     </row>
-    <row r="129" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I129" s="20"/>
     </row>
-    <row r="130" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I130" s="20"/>
     </row>
-    <row r="131" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I131" s="20"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D16">
-    <cfRule type="timePeriod" dxfId="13" priority="37" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="24" priority="37" timePeriod="nextMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0+1)),YEAR(D1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="12" priority="38" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="23" priority="38" timePeriod="thisMonth">
       <formula>AND(MONTH(D1)=MONTH(TODAY()),YEAR(D1)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="11" priority="39" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="22" priority="39" timePeriod="lastMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0-1)),YEAR(D1)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D22:D29 D31 D41:D1048576">
-    <cfRule type="timePeriod" dxfId="10" priority="1" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="21" priority="1" timePeriod="nextMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0+1)),YEAR(D22)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="9" priority="2" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="20" priority="2" timePeriod="thisMonth">
       <formula>AND(MONTH(D22)=MONTH(TODAY()),YEAR(D22)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="8" priority="3" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="19" priority="3" timePeriod="lastMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0-1)),YEAR(D22)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="timePeriod" dxfId="7" priority="40" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="18" priority="40" timePeriod="nextMonth">
       <formula>AND(MONTH(I1)=MONTH(EDATE(TODAY(),0+1)),YEAR(I1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="6" priority="41" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="17" priority="41" timePeriod="thisMonth">
       <formula>AND(MONTH(I1)=MONTH(TODAY()),YEAR(I1)=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="cellIs" dxfId="5" priority="45" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="45" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I22">
-    <cfRule type="cellIs" dxfId="4" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="42" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
-    <cfRule type="cellIs" dxfId="3" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="43" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2435,14 +2460,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAE522B-09DD-4490-9CA8-387DE173331A}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
-    <col min="2" max="3" width="11.44140625" style="12"/>
-    <col min="4" max="4" width="11.88671875" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="11.42578125" style="12"/>
+    <col min="4" max="4" width="11.85546875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
         <v>49</v>
       </c>
@@ -2453,7 +2478,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="47"/>
       <c r="B2" s="11">
         <v>0</v>
@@ -2464,7 +2489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="47">
         <v>46037</v>
       </c>
@@ -2479,7 +2504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="47">
         <v>46053</v>
       </c>
@@ -2494,7 +2519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="47">
         <v>46068</v>
       </c>
@@ -2509,7 +2534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="47">
         <v>46081</v>
       </c>
@@ -2524,7 +2549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="47">
         <v>46096</v>
       </c>
@@ -2539,7 +2564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="47">
         <v>46112</v>
       </c>
@@ -2554,7 +2579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="47">
         <v>46127</v>
       </c>
@@ -2573,7 +2598,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="47">
         <v>46142</v>
       </c>
@@ -2589,7 +2614,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="47">
         <v>46157</v>
       </c>
@@ -2608,7 +2633,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="47">
         <v>46173</v>
       </c>
@@ -2624,7 +2649,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="47">
         <v>46188</v>
       </c>
@@ -2640,7 +2665,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="47">
         <v>46203</v>
       </c>
@@ -2656,7 +2681,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="47">
         <v>46218</v>
       </c>
@@ -2672,7 +2697,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="47">
         <v>46234</v>
       </c>
@@ -2688,7 +2713,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="47">
         <v>46249</v>
       </c>
@@ -2704,7 +2729,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="47">
         <v>46265</v>
       </c>
@@ -2720,7 +2745,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="47">
         <v>46280</v>
       </c>
@@ -2736,7 +2761,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="47">
         <v>46295</v>
       </c>
@@ -2752,7 +2777,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="47">
         <v>46310</v>
       </c>
@@ -2768,7 +2793,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="47">
         <v>46326</v>
       </c>
@@ -2784,7 +2809,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="47">
         <v>46341</v>
       </c>
@@ -2800,7 +2825,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="47">
         <v>46356</v>
       </c>
@@ -2816,7 +2841,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="47">
         <v>46371</v>
       </c>
@@ -2832,7 +2857,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="46" t="s">
         <v>50</v>
       </c>
@@ -2845,7 +2870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="46" t="s">
         <v>51</v>
       </c>
@@ -2858,7 +2883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="47">
         <v>46387</v>
       </c>
@@ -2874,7 +2899,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="47">
         <v>46402</v>
       </c>
@@ -2887,7 +2912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="47">
         <v>46418</v>
       </c>
@@ -2900,7 +2925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="47">
         <v>46433</v>
       </c>
@@ -2913,7 +2938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="47">
         <v>46446</v>
       </c>
@@ -2926,7 +2951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="47">
         <v>46461</v>
       </c>
@@ -2939,7 +2964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="47">
         <v>46477</v>
       </c>
@@ -2952,7 +2977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="47">
         <v>46492</v>
       </c>
@@ -2965,7 +2990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="47">
         <v>46507</v>
       </c>
@@ -2978,7 +3003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="47">
         <v>46522</v>
       </c>
@@ -2991,7 +3016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="47">
         <v>46538</v>
       </c>
@@ -3004,7 +3029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="47">
         <v>46553</v>
       </c>
@@ -3017,7 +3042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="47">
         <v>46568</v>
       </c>
@@ -3030,7 +3055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="47">
         <v>46583</v>
       </c>
@@ -3043,7 +3068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="47">
         <v>46599</v>
       </c>
@@ -3056,7 +3081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="47">
         <v>46614</v>
       </c>
@@ -3069,7 +3094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="47">
         <v>46630</v>
       </c>
@@ -3082,7 +3107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="47">
         <v>46645</v>
       </c>
@@ -3095,7 +3120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="47">
         <v>46660</v>
       </c>
@@ -3108,7 +3133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="47">
         <v>46675</v>
       </c>
@@ -3121,7 +3146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="47">
         <v>46691</v>
       </c>
@@ -3134,7 +3159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="47">
         <v>46706</v>
       </c>
@@ -3147,7 +3172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="47">
         <v>46721</v>
       </c>
@@ -3160,7 +3185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="47">
         <v>46736</v>
       </c>
@@ -3173,7 +3198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="46" t="s">
         <v>50</v>
       </c>
@@ -3186,7 +3211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="46" t="s">
         <v>51</v>
       </c>
@@ -3199,7 +3224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="47">
         <v>46752</v>
       </c>
@@ -3212,7 +3237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="50">
         <f>SUM(B2:B54)</f>
         <v>4610</v>
@@ -3222,34 +3247,34 @@
         <v>300</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
     </row>
-    <row r="57" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="60">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
-        <v>-135</v>
+        <v>-210</v>
       </c>
       <c r="C57" s="61"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B58" s="59"/>
       <c r="C58" s="3"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B59"/>
       <c r="C59" s="3"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
     </row>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B40E0D-5E11-47F6-A76D-F82B458B0319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1CBF84F-1ECE-4FBF-95E1-16BB7A072C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -31,15 +31,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
   <si>
     <t>Totales</t>
   </si>
@@ -219,9 +216,6 @@
   </si>
   <si>
     <t>Tasa cero Sillones</t>
-  </si>
-  <si>
-    <t>x</t>
   </si>
 </sst>
 </file>
@@ -716,68 +710,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="21" formatCode="d\-mmm"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -923,6 +855,68 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="d\-mmm"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -942,7 +936,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="13" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="28" tableBorderDxfId="27">
   <autoFilter ref="A2:K14" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K14">
     <sortCondition ref="D3:D14"/>
@@ -950,17 +944,17 @@
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{4E2F1548-5DA7-4ADC-946F-053ED807460A}" name="Banco"/>
     <tableColumn id="2" xr3:uid="{11D77EA7-239F-47E1-9378-FFBA07ACDD06}" name="Tarjeta"/>
-    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="9">
+    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="24">
       <calculatedColumnFormula>186.68-48</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="3" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="23"/>
+    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="18" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1264,16 +1258,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0DE2A9-9218-4E10-883D-DF66D771FC39}">
   <dimension ref="B1:H37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="3.140625" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="3.109375" customWidth="1"/>
+    <col min="6" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1" s="13" t="s">
         <v>14</v>
       </c>
@@ -1285,7 +1279,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1299,7 +1293,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
@@ -1309,14 +1303,11 @@
       <c r="D3" s="8">
         <v>50</v>
       </c>
-      <c r="E3" t="s">
-        <v>60</v>
-      </c>
       <c r="F3" s="8">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
@@ -1326,14 +1317,11 @@
       <c r="D4" s="8">
         <v>10</v>
       </c>
-      <c r="E4" t="s">
-        <v>60</v>
-      </c>
       <c r="F4" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
@@ -1347,7 +1335,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
@@ -1357,14 +1345,11 @@
       <c r="D6" s="8">
         <v>60</v>
       </c>
-      <c r="E6" t="s">
-        <v>60</v>
-      </c>
       <c r="F6" s="8">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="9" t="s">
         <v>17</v>
       </c>
@@ -1374,14 +1359,11 @@
       <c r="D7" s="8">
         <v>100</v>
       </c>
-      <c r="E7" t="s">
-        <v>60</v>
-      </c>
       <c r="F7" s="8">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -1391,11 +1373,8 @@
       <c r="D8" s="58">
         <v>95</v>
       </c>
-      <c r="E8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -1406,7 +1385,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -1414,7 +1393,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -1425,7 +1404,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>9</v>
       </c>
@@ -1435,9 +1414,6 @@
       <c r="D12">
         <v>15</v>
       </c>
-      <c r="E12" t="s">
-        <v>60</v>
-      </c>
       <c r="F12">
         <v>5</v>
       </c>
@@ -1445,7 +1421,7 @@
         <v>8286917</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>10</v>
       </c>
@@ -1453,7 +1429,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>15</v>
       </c>
@@ -1464,7 +1440,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>59</v>
       </c>
@@ -1474,11 +1450,8 @@
       <c r="D15">
         <v>48</v>
       </c>
-      <c r="E15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>11</v>
       </c>
@@ -1492,7 +1465,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="s">
         <v>12</v>
       </c>
@@ -1505,7 +1478,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="5" t="s">
         <v>13</v>
       </c>
@@ -1519,24 +1492,24 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="37" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="30.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>$C$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
       <formula>$C$7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
       <formula>$C$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
       <formula>$C$2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1548,22 +1521,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B43D18-F407-4702-B159-A2C7E22E2016}">
   <dimension ref="A1:N131"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="19" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="12" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" style="12" customWidth="1"/>
-    <col min="7" max="8" width="16.140625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" style="10" customWidth="1"/>
-    <col min="10" max="10" width="17.42578125" style="12" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" style="19" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" style="12" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" style="12" customWidth="1"/>
+    <col min="7" max="8" width="16.109375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" style="10" customWidth="1"/>
+    <col min="10" max="10" width="17.44140625" style="12" customWidth="1"/>
+    <col min="11" max="11" width="7.109375" style="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
         <v>19</v>
       </c>
@@ -1598,7 +1571,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="39" t="s">
         <v>40</v>
       </c>
@@ -1621,7 +1594,7 @@
       <c r="J3" s="42"/>
       <c r="K3" s="43"/>
     </row>
-    <row r="4" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="34" t="s">
         <v>56</v>
       </c>
@@ -1644,7 +1617,7 @@
       <c r="J4" s="37"/>
       <c r="K4" s="38"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -1664,14 +1637,14 @@
         <v>46118</v>
       </c>
       <c r="J5" s="12">
-        <v>57.18</v>
+        <v>217.18</v>
       </c>
       <c r="K5" s="31">
         <v>0.27900000000000003</v>
       </c>
       <c r="N5" s="4"/>
     </row>
-    <row r="6" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1693,10 +1666,12 @@
       <c r="I6" s="20">
         <v>46148</v>
       </c>
-      <c r="J6" s="12"/>
+      <c r="J6" s="12">
+        <v>83.28</v>
+      </c>
       <c r="K6" s="31"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -1718,7 +1693,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34" t="s">
         <v>39</v>
       </c>
@@ -1741,7 +1716,7 @@
       <c r="J8" s="37"/>
       <c r="K8" s="38"/>
     </row>
-    <row r="9" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="52" t="s">
         <v>29</v>
       </c>
@@ -1764,7 +1739,7 @@
       <c r="J9" s="44"/>
       <c r="K9" s="54"/>
     </row>
-    <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1787,7 +1762,7 @@
       <c r="J10" s="12"/>
       <c r="K10" s="31"/>
     </row>
-    <row r="11" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
         <v>29</v>
       </c>
@@ -1810,7 +1785,7 @@
       <c r="J11" s="37"/>
       <c r="K11" s="38"/>
     </row>
-    <row r="12" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="39" t="s">
         <v>58</v>
       </c>
@@ -1833,7 +1808,7 @@
       <c r="J12" s="42"/>
       <c r="K12" s="43"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="39" t="s">
         <v>58</v>
       </c>
@@ -1855,7 +1830,7 @@
         <v>45946</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -1880,19 +1855,19 @@
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>57.18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+        <v>300.46000000000004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D15" s="20"/>
       <c r="I15" s="20"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D16" s="20"/>
       <c r="I16" s="20"/>
     </row>
-    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1913,28 +1888,36 @@
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
     </row>
-    <row r="18" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B18" s="57">
-        <v>406</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="C18" s="2">
+        <v>100</v>
+      </c>
+      <c r="D18" s="2">
+        <v>50</v>
+      </c>
       <c r="E18" s="2">
         <v>70</v>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
+      <c r="F18" s="2">
+        <v>40</v>
+      </c>
+      <c r="G18" s="2">
+        <v>70</v>
+      </c>
       <c r="H18" s="2"/>
       <c r="I18" s="22"/>
       <c r="J18" s="23">
         <f>SUM(B18:I18)</f>
-        <v>476</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="55"/>
@@ -1943,509 +1926,509 @@
       <c r="H19" s="2"/>
       <c r="I19" s="20"/>
     </row>
-    <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D20" s="12"/>
       <c r="H20" s="56" t="s">
         <v>37</v>
       </c>
       <c r="I20" s="25">
         <f>+H14+J14+G14</f>
-        <v>442.2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>685.48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D21" s="12"/>
       <c r="H21" s="26" t="s">
         <v>38</v>
       </c>
       <c r="I21" s="25">
         <f>+J18-H14-G14</f>
-        <v>90.980000000000018</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>289.98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D22" s="20"/>
       <c r="H22" s="27" t="s">
         <v>54</v>
       </c>
       <c r="I22" s="25">
         <f>+I21-J14</f>
-        <v>33.800000000000018</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-10.480000000000018</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D23" s="12"/>
       <c r="I23" s="20"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D24" s="12"/>
       <c r="I24" s="20"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D25" s="12"/>
       <c r="I25" s="20"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D26" s="12"/>
       <c r="I26" s="20"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D27" s="12"/>
       <c r="I27" s="20"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D28" s="12"/>
       <c r="I28" s="20"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D29" s="12"/>
       <c r="I29" s="20"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D30" s="11"/>
       <c r="I30" s="20"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D31" s="20"/>
       <c r="I31" s="20"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D32" s="11"/>
       <c r="I32" s="20"/>
     </row>
-    <row r="33" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D33" s="11"/>
       <c r="I33" s="20"/>
     </row>
-    <row r="34" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D34" s="11"/>
       <c r="I34" s="20"/>
     </row>
-    <row r="35" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D35" s="11"/>
       <c r="I35" s="20"/>
     </row>
-    <row r="36" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D36" s="11"/>
       <c r="I36" s="20"/>
     </row>
-    <row r="37" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D37" s="11"/>
       <c r="I37" s="20"/>
     </row>
-    <row r="38" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D38" s="11"/>
       <c r="I38" s="20"/>
     </row>
-    <row r="39" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D39" s="11"/>
       <c r="I39" s="20"/>
     </row>
-    <row r="40" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D40" s="11"/>
       <c r="I40" s="20"/>
     </row>
-    <row r="41" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D41" s="20"/>
       <c r="I41" s="20"/>
     </row>
-    <row r="42" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D42" s="12"/>
       <c r="I42" s="20"/>
     </row>
-    <row r="43" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D43" s="12"/>
       <c r="I43" s="20"/>
     </row>
-    <row r="44" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D44" s="20"/>
       <c r="I44" s="20"/>
     </row>
-    <row r="45" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D45" s="20"/>
       <c r="I45" s="20"/>
     </row>
-    <row r="46" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D46" s="20"/>
       <c r="I46" s="20"/>
     </row>
-    <row r="47" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D47" s="20"/>
       <c r="I47" s="20"/>
     </row>
-    <row r="48" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D48" s="20"/>
       <c r="I48" s="20"/>
     </row>
-    <row r="49" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D49" s="20"/>
       <c r="I49" s="20"/>
     </row>
-    <row r="50" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D50" s="20"/>
       <c r="I50" s="20"/>
     </row>
-    <row r="51" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D51" s="20"/>
       <c r="I51" s="20"/>
     </row>
-    <row r="52" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D52" s="20"/>
       <c r="I52" s="20"/>
     </row>
-    <row r="53" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D53" s="20"/>
       <c r="I53" s="20"/>
     </row>
-    <row r="54" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D54" s="20"/>
       <c r="I54" s="20"/>
     </row>
-    <row r="55" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D55" s="20"/>
       <c r="I55" s="20"/>
     </row>
-    <row r="56" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D56" s="20"/>
       <c r="I56" s="20"/>
     </row>
-    <row r="57" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D57" s="20"/>
       <c r="I57" s="20"/>
     </row>
-    <row r="58" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D58" s="20"/>
       <c r="I58" s="20"/>
     </row>
-    <row r="59" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D59" s="20"/>
       <c r="I59" s="20"/>
     </row>
-    <row r="60" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D60" s="20"/>
       <c r="I60" s="20"/>
     </row>
-    <row r="61" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D61" s="20"/>
       <c r="I61" s="20"/>
     </row>
-    <row r="62" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D62" s="20"/>
       <c r="I62" s="20"/>
     </row>
-    <row r="63" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D63" s="20"/>
       <c r="I63" s="20"/>
     </row>
-    <row r="64" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D64" s="20"/>
       <c r="I64" s="20"/>
     </row>
-    <row r="65" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D65" s="20"/>
       <c r="I65" s="20"/>
     </row>
-    <row r="66" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D66" s="20"/>
       <c r="I66" s="20"/>
     </row>
-    <row r="67" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D67" s="20"/>
       <c r="I67" s="20"/>
     </row>
-    <row r="68" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D68" s="20"/>
       <c r="I68" s="20"/>
     </row>
-    <row r="69" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D69" s="20"/>
       <c r="I69" s="20"/>
     </row>
-    <row r="70" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D70" s="20"/>
       <c r="I70" s="20"/>
     </row>
-    <row r="71" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D71" s="20"/>
       <c r="I71" s="20"/>
     </row>
-    <row r="72" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D72" s="20"/>
       <c r="I72" s="20"/>
     </row>
-    <row r="73" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D73" s="20"/>
       <c r="I73" s="20"/>
     </row>
-    <row r="74" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D74" s="20"/>
       <c r="I74" s="20"/>
     </row>
-    <row r="75" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D75" s="20"/>
       <c r="I75" s="20"/>
     </row>
-    <row r="76" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D76" s="20"/>
       <c r="I76" s="20"/>
     </row>
-    <row r="77" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D77" s="20"/>
       <c r="I77" s="20"/>
     </row>
-    <row r="78" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D78" s="20"/>
       <c r="I78" s="20"/>
     </row>
-    <row r="79" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D79" s="20"/>
       <c r="I79" s="20"/>
     </row>
-    <row r="80" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D80" s="20"/>
       <c r="I80" s="20"/>
     </row>
-    <row r="81" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D81" s="20"/>
       <c r="I81" s="20"/>
     </row>
-    <row r="82" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D82" s="20"/>
       <c r="I82" s="20"/>
     </row>
-    <row r="83" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D83" s="20"/>
       <c r="I83" s="20"/>
     </row>
-    <row r="84" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D84" s="20"/>
       <c r="I84" s="20"/>
     </row>
-    <row r="85" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D85" s="20"/>
       <c r="I85" s="20"/>
     </row>
-    <row r="86" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D86" s="20"/>
       <c r="I86" s="20"/>
     </row>
-    <row r="87" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D87" s="20"/>
       <c r="I87" s="20"/>
     </row>
-    <row r="88" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D88" s="20"/>
       <c r="I88" s="20"/>
     </row>
-    <row r="89" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D89" s="20"/>
       <c r="I89" s="20"/>
     </row>
-    <row r="90" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D90" s="20"/>
       <c r="I90" s="20"/>
     </row>
-    <row r="91" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D91" s="20"/>
       <c r="I91" s="20"/>
     </row>
-    <row r="92" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D92" s="20"/>
       <c r="I92" s="20"/>
     </row>
-    <row r="93" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D93" s="20"/>
       <c r="I93" s="20"/>
     </row>
-    <row r="94" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D94" s="20"/>
       <c r="I94" s="20"/>
     </row>
-    <row r="95" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D95" s="20"/>
       <c r="I95" s="20"/>
     </row>
-    <row r="96" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D96" s="20"/>
       <c r="I96" s="20"/>
     </row>
-    <row r="97" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D97" s="20"/>
       <c r="I97" s="20"/>
     </row>
-    <row r="98" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D98" s="20"/>
       <c r="I98" s="20"/>
     </row>
-    <row r="99" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D99" s="20"/>
       <c r="I99" s="20"/>
     </row>
-    <row r="100" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D100" s="20"/>
       <c r="I100" s="20"/>
     </row>
-    <row r="101" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D101" s="20"/>
       <c r="I101" s="20"/>
     </row>
-    <row r="102" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D102" s="20"/>
       <c r="I102" s="20"/>
     </row>
-    <row r="103" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D103" s="20"/>
       <c r="I103" s="20"/>
     </row>
-    <row r="104" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D104" s="20"/>
       <c r="I104" s="20"/>
     </row>
-    <row r="105" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D105" s="20"/>
       <c r="I105" s="20"/>
     </row>
-    <row r="106" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D106" s="20"/>
       <c r="I106" s="20"/>
     </row>
-    <row r="107" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D107" s="20"/>
       <c r="I107" s="20"/>
     </row>
-    <row r="108" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D108" s="20"/>
       <c r="I108" s="20"/>
     </row>
-    <row r="109" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D109" s="20"/>
       <c r="I109" s="20"/>
     </row>
-    <row r="110" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D110" s="20"/>
       <c r="I110" s="20"/>
     </row>
-    <row r="111" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D111" s="20"/>
       <c r="I111" s="20"/>
     </row>
-    <row r="112" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D112" s="20"/>
       <c r="I112" s="20"/>
     </row>
-    <row r="113" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D113" s="20"/>
       <c r="I113" s="20"/>
     </row>
-    <row r="114" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D114" s="20"/>
       <c r="I114" s="20"/>
     </row>
-    <row r="115" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D115" s="20"/>
       <c r="I115" s="20"/>
     </row>
-    <row r="116" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D116" s="20"/>
       <c r="I116" s="20"/>
     </row>
-    <row r="117" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D117" s="20"/>
       <c r="I117" s="20"/>
     </row>
-    <row r="118" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D118" s="20"/>
       <c r="I118" s="20"/>
     </row>
-    <row r="119" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D119" s="20"/>
       <c r="I119" s="20"/>
     </row>
-    <row r="120" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D120" s="20"/>
       <c r="I120" s="20"/>
     </row>
-    <row r="121" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D121" s="20"/>
       <c r="I121" s="20"/>
     </row>
-    <row r="122" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D122" s="20"/>
       <c r="I122" s="20"/>
     </row>
-    <row r="123" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D123" s="20"/>
       <c r="I123" s="20"/>
     </row>
-    <row r="124" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D124" s="20"/>
       <c r="I124" s="20"/>
     </row>
-    <row r="125" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D125" s="20"/>
       <c r="I125" s="20"/>
     </row>
-    <row r="126" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I126" s="20"/>
     </row>
-    <row r="127" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I127" s="20"/>
     </row>
-    <row r="128" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I128" s="20"/>
     </row>
-    <row r="129" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I129" s="20"/>
     </row>
-    <row r="130" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I130" s="20"/>
     </row>
-    <row r="131" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I131" s="20"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D16">
-    <cfRule type="timePeriod" dxfId="24" priority="37" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="13" priority="37" timePeriod="nextMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0+1)),YEAR(D1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="23" priority="38" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="12" priority="38" timePeriod="thisMonth">
       <formula>AND(MONTH(D1)=MONTH(TODAY()),YEAR(D1)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="22" priority="39" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="11" priority="39" timePeriod="lastMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0-1)),YEAR(D1)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D22:D29 D31 D41:D1048576">
-    <cfRule type="timePeriod" dxfId="21" priority="1" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="10" priority="1" timePeriod="nextMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0+1)),YEAR(D22)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="20" priority="2" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="9" priority="2" timePeriod="thisMonth">
       <formula>AND(MONTH(D22)=MONTH(TODAY()),YEAR(D22)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="19" priority="3" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="8" priority="3" timePeriod="lastMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0-1)),YEAR(D22)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="timePeriod" dxfId="18" priority="40" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="7" priority="40" timePeriod="nextMonth">
       <formula>AND(MONTH(I1)=MONTH(EDATE(TODAY(),0+1)),YEAR(I1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="17" priority="41" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="6" priority="41" timePeriod="thisMonth">
       <formula>AND(MONTH(I1)=MONTH(TODAY()),YEAR(I1)=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="cellIs" dxfId="16" priority="45" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="45" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I22">
-    <cfRule type="cellIs" dxfId="15" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="42" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
-    <cfRule type="cellIs" dxfId="14" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="43" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2460,14 +2443,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAE522B-09DD-4490-9CA8-387DE173331A}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
-    <col min="2" max="3" width="11.42578125" style="12"/>
-    <col min="4" max="4" width="11.85546875" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="11.44140625" style="12"/>
+    <col min="4" max="4" width="11.88671875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="45" t="s">
         <v>49</v>
       </c>
@@ -2478,7 +2461,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="47"/>
       <c r="B2" s="11">
         <v>0</v>
@@ -2489,7 +2472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="47">
         <v>46037</v>
       </c>
@@ -2504,7 +2487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="47">
         <v>46053</v>
       </c>
@@ -2519,7 +2502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="47">
         <v>46068</v>
       </c>
@@ -2534,7 +2517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="47">
         <v>46081</v>
       </c>
@@ -2549,7 +2532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="47">
         <v>46096</v>
       </c>
@@ -2564,7 +2547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="47">
         <v>46112</v>
       </c>
@@ -2579,7 +2562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="47">
         <v>46127</v>
       </c>
@@ -2598,7 +2581,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="47">
         <v>46142</v>
       </c>
@@ -2614,7 +2597,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="47">
         <v>46157</v>
       </c>
@@ -2633,7 +2616,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="47">
         <v>46173</v>
       </c>
@@ -2649,7 +2632,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="47">
         <v>46188</v>
       </c>
@@ -2665,7 +2648,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="47">
         <v>46203</v>
       </c>
@@ -2681,7 +2664,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="47">
         <v>46218</v>
       </c>
@@ -2697,7 +2680,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="47">
         <v>46234</v>
       </c>
@@ -2713,7 +2696,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="47">
         <v>46249</v>
       </c>
@@ -2729,7 +2712,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="47">
         <v>46265</v>
       </c>
@@ -2745,7 +2728,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="47">
         <v>46280</v>
       </c>
@@ -2761,7 +2744,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="47">
         <v>46295</v>
       </c>
@@ -2777,7 +2760,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="47">
         <v>46310</v>
       </c>
@@ -2793,7 +2776,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="47">
         <v>46326</v>
       </c>
@@ -2809,7 +2792,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="47">
         <v>46341</v>
       </c>
@@ -2825,7 +2808,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="47">
         <v>46356</v>
       </c>
@@ -2841,7 +2824,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="47">
         <v>46371</v>
       </c>
@@ -2857,7 +2840,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="46" t="s">
         <v>50</v>
       </c>
@@ -2870,7 +2853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="46" t="s">
         <v>51</v>
       </c>
@@ -2883,7 +2866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="47">
         <v>46387</v>
       </c>
@@ -2899,7 +2882,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="47">
         <v>46402</v>
       </c>
@@ -2912,7 +2895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="47">
         <v>46418</v>
       </c>
@@ -2925,7 +2908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="47">
         <v>46433</v>
       </c>
@@ -2938,7 +2921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="47">
         <v>46446</v>
       </c>
@@ -2951,7 +2934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="47">
         <v>46461</v>
       </c>
@@ -2964,7 +2947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="47">
         <v>46477</v>
       </c>
@@ -2977,7 +2960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="47">
         <v>46492</v>
       </c>
@@ -2990,7 +2973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="47">
         <v>46507</v>
       </c>
@@ -3003,7 +2986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="47">
         <v>46522</v>
       </c>
@@ -3016,7 +2999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="47">
         <v>46538</v>
       </c>
@@ -3029,7 +3012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="47">
         <v>46553</v>
       </c>
@@ -3042,7 +3025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="47">
         <v>46568</v>
       </c>
@@ -3055,7 +3038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="47">
         <v>46583</v>
       </c>
@@ -3068,7 +3051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="47">
         <v>46599</v>
       </c>
@@ -3081,7 +3064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="47">
         <v>46614</v>
       </c>
@@ -3094,7 +3077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="47">
         <v>46630</v>
       </c>
@@ -3107,7 +3090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="47">
         <v>46645</v>
       </c>
@@ -3120,7 +3103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="47">
         <v>46660</v>
       </c>
@@ -3133,7 +3116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="47">
         <v>46675</v>
       </c>
@@ -3146,7 +3129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="47">
         <v>46691</v>
       </c>
@@ -3159,7 +3142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="47">
         <v>46706</v>
       </c>
@@ -3172,7 +3155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="47">
         <v>46721</v>
       </c>
@@ -3185,7 +3168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="47">
         <v>46736</v>
       </c>
@@ -3198,7 +3181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="46" t="s">
         <v>50</v>
       </c>
@@ -3211,7 +3194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="46" t="s">
         <v>51</v>
       </c>
@@ -3224,7 +3207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="47">
         <v>46752</v>
       </c>
@@ -3237,7 +3220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="50">
         <f>SUM(B2:B54)</f>
         <v>4610</v>
@@ -3247,34 +3230,34 @@
         <v>300</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
     </row>
-    <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="60">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
         <v>-210</v>
       </c>
       <c r="C57" s="61"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B58" s="59"/>
       <c r="C58" s="3"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B59"/>
       <c r="C59" s="3"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
     </row>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1CBF84F-1ECE-4FBF-95E1-16BB7A072C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6EB3D0D-15A3-434D-993D-87F9FB1EB391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
@@ -1630,9 +1630,7 @@
       <c r="D5" s="20">
         <v>45817</v>
       </c>
-      <c r="H5" s="12">
-        <v>280.05</v>
-      </c>
+      <c r="H5" s="12"/>
       <c r="I5" s="20">
         <v>46118</v>
       </c>
@@ -1850,7 +1848,7 @@
       </c>
       <c r="H14" s="21">
         <f>SUBTOTAL(109,H3:H13)</f>
-        <v>385.02</v>
+        <v>104.97</v>
       </c>
       <c r="I14" s="21"/>
       <c r="J14" s="21">
@@ -1893,28 +1891,24 @@
         <v>35</v>
       </c>
       <c r="B18" s="57">
-        <v>345</v>
+        <v>65</v>
       </c>
       <c r="C18" s="2">
+        <v>70</v>
+      </c>
+      <c r="D18" s="2">
         <v>100</v>
-      </c>
-      <c r="D18" s="2">
-        <v>50</v>
       </c>
       <c r="E18" s="2">
         <v>70</v>
       </c>
-      <c r="F18" s="2">
-        <v>40</v>
-      </c>
-      <c r="G18" s="2">
-        <v>70</v>
-      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="22"/>
       <c r="J18" s="23">
         <f>SUM(B18:I18)</f>
-        <v>675</v>
+        <v>305</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1933,7 +1927,7 @@
       </c>
       <c r="I20" s="25">
         <f>+H14+J14+G14</f>
-        <v>685.48</v>
+        <v>405.43000000000006</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1943,7 +1937,7 @@
       </c>
       <c r="I21" s="25">
         <f>+J18-H14-G14</f>
-        <v>289.98</v>
+        <v>200.03</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1953,7 +1947,7 @@
       </c>
       <c r="I22" s="25">
         <f>+I21-J14</f>
-        <v>-10.480000000000018</v>
+        <v>-100.43000000000004</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
@@ -2569,10 +2563,12 @@
       <c r="B9" s="11">
         <v>75</v>
       </c>
-      <c r="C9" s="11"/>
+      <c r="C9" s="11">
+        <v>100</v>
+      </c>
       <c r="D9" t="b">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -3227,7 +3223,7 @@
       </c>
       <c r="C55" s="51">
         <f>SUM(C2:C54)</f>
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3237,7 +3233,7 @@
     <row r="57" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="60">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
-        <v>-210</v>
+        <v>-110</v>
       </c>
       <c r="C57" s="61"/>
     </row>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6EB3D0D-15A3-434D-993D-87F9FB1EB391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08998907-B233-4CFF-A3DE-6CF713A6513C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -1635,7 +1635,7 @@
         <v>46118</v>
       </c>
       <c r="J5" s="12">
-        <v>217.18</v>
+        <v>240.82</v>
       </c>
       <c r="K5" s="31">
         <v>0.27900000000000003</v>
@@ -1658,14 +1658,12 @@
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
-      <c r="H6" s="33">
-        <v>104.97</v>
-      </c>
+      <c r="H6" s="33"/>
       <c r="I6" s="20">
         <v>46148</v>
       </c>
       <c r="J6" s="12">
-        <v>83.28</v>
+        <v>94.06</v>
       </c>
       <c r="K6" s="31"/>
     </row>
@@ -1848,12 +1846,12 @@
       </c>
       <c r="H14" s="21">
         <f>SUBTOTAL(109,H3:H13)</f>
-        <v>104.97</v>
+        <v>0</v>
       </c>
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>300.46000000000004</v>
+        <v>334.88</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1872,17 +1870,15 @@
       <c r="B17" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24">
-        <v>46142</v>
-      </c>
-      <c r="F17" s="24">
+      <c r="C17" s="24">
         <v>46157</v>
       </c>
-      <c r="G17" s="24">
+      <c r="D17" s="24">
         <v>46172</v>
       </c>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
     </row>
@@ -1891,24 +1887,28 @@
         <v>35</v>
       </c>
       <c r="B18" s="57">
-        <v>65</v>
+        <v>219</v>
       </c>
       <c r="C18" s="2">
+        <v>40</v>
+      </c>
+      <c r="D18" s="2">
         <v>70</v>
       </c>
-      <c r="D18" s="2">
-        <v>100</v>
-      </c>
       <c r="E18" s="2">
-        <v>70</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
+        <v>-50</v>
+      </c>
+      <c r="F18" s="2">
+        <v>-60</v>
+      </c>
+      <c r="G18" s="2">
+        <v>-20</v>
+      </c>
       <c r="H18" s="2"/>
       <c r="I18" s="22"/>
       <c r="J18" s="23">
         <f>SUM(B18:I18)</f>
-        <v>305</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="I20" s="25">
         <f>+H14+J14+G14</f>
-        <v>405.43000000000006</v>
+        <v>334.88</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="I21" s="25">
         <f>+J18-H14-G14</f>
-        <v>200.03</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="I22" s="25">
         <f>+I21-J14</f>
-        <v>-100.43000000000004</v>
+        <v>-135.88</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="D9" t="b">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -3233,7 +3233,7 @@
     <row r="57" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="60">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
-        <v>-110</v>
+        <v>-180</v>
       </c>
       <c r="C57" s="61"/>
     </row>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08998907-B233-4CFF-A3DE-6CF713A6513C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2038722-EB46-4446-90CD-D1EC681CF739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -552,7 +555,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -677,6 +680,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -707,6 +711,68 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="21" formatCode="d\-mmm"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -855,68 +921,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="d\-mmm"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -936,7 +940,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="28" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="13" tableBorderDxfId="12">
   <autoFilter ref="A2:K14" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K14">
     <sortCondition ref="D3:D14"/>
@@ -944,17 +948,17 @@
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{4E2F1548-5DA7-4ADC-946F-053ED807460A}" name="Banco"/>
     <tableColumn id="2" xr3:uid="{11D77EA7-239F-47E1-9378-FFBA07ACDD06}" name="Tarjeta"/>
-    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="24">
+    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="9">
       <calculatedColumnFormula>186.68-48</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="23"/>
-    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="18" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="3" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1258,16 +1262,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0DE2A9-9218-4E10-883D-DF66D771FC39}">
   <dimension ref="B1:H37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="3.109375" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="3.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
         <v>14</v>
       </c>
@@ -1279,7 +1283,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1293,7 +1297,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
@@ -1307,7 +1311,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
@@ -1321,7 +1325,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
@@ -1335,7 +1339,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
@@ -1349,7 +1353,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>17</v>
       </c>
@@ -1363,7 +1367,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -1374,7 +1378,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -1385,7 +1389,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -1393,7 +1397,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -1404,7 +1408,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>9</v>
       </c>
@@ -1421,7 +1425,7 @@
         <v>8286917</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>10</v>
       </c>
@@ -1429,7 +1433,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>15</v>
       </c>
@@ -1440,7 +1444,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>59</v>
       </c>
@@ -1451,7 +1455,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="7" t="s">
         <v>11</v>
       </c>
@@ -1465,7 +1469,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
         <v>12</v>
       </c>
@@ -1478,7 +1482,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>13</v>
       </c>
@@ -1492,24 +1496,24 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="37" ht="30.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
       <formula>$C$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
       <formula>$C$7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="equal">
       <formula>$C$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="4" operator="equal">
       <formula>$C$2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1521,22 +1525,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B43D18-F407-4702-B159-A2C7E22E2016}">
   <dimension ref="A1:N131"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" style="19" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" style="12" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" style="12" customWidth="1"/>
-    <col min="7" max="8" width="16.109375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" style="10" customWidth="1"/>
-    <col min="10" max="10" width="17.44140625" style="12" customWidth="1"/>
-    <col min="11" max="11" width="7.109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" style="12" customWidth="1"/>
+    <col min="7" max="8" width="16.140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" style="10" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" style="12" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" style="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>19</v>
       </c>
@@ -1571,7 +1575,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
         <v>40</v>
       </c>
@@ -1594,7 +1598,7 @@
       <c r="J3" s="42"/>
       <c r="K3" s="43"/>
     </row>
-    <row r="4" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="34" t="s">
         <v>56</v>
       </c>
@@ -1617,7 +1621,7 @@
       <c r="J4" s="37"/>
       <c r="K4" s="38"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -1635,14 +1639,14 @@
         <v>46118</v>
       </c>
       <c r="J5" s="12">
-        <v>240.82</v>
+        <v>250</v>
       </c>
       <c r="K5" s="31">
         <v>0.27900000000000003</v>
       </c>
       <c r="N5" s="4"/>
     </row>
-    <row r="6" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1667,7 +1671,7 @@
       </c>
       <c r="K6" s="31"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -1689,7 +1693,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
         <v>39</v>
       </c>
@@ -1712,7 +1716,7 @@
       <c r="J8" s="37"/>
       <c r="K8" s="38"/>
     </row>
-    <row r="9" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
         <v>29</v>
       </c>
@@ -1735,7 +1739,7 @@
       <c r="J9" s="44"/>
       <c r="K9" s="54"/>
     </row>
-    <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1758,7 +1762,7 @@
       <c r="J10" s="12"/>
       <c r="K10" s="31"/>
     </row>
-    <row r="11" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
         <v>29</v>
       </c>
@@ -1781,7 +1785,7 @@
       <c r="J11" s="37"/>
       <c r="K11" s="38"/>
     </row>
-    <row r="12" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
         <v>58</v>
       </c>
@@ -1804,7 +1808,7 @@
       <c r="J12" s="42"/>
       <c r="K12" s="43"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="39" t="s">
         <v>58</v>
       </c>
@@ -1826,7 +1830,7 @@
         <v>45946</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -1851,19 +1855,19 @@
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>334.88</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+        <v>344.06</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D15" s="20"/>
       <c r="I15" s="20"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D16" s="20"/>
       <c r="I16" s="20"/>
     </row>
-    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1882,7 +1886,7 @@
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
     </row>
-    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1895,23 +1899,21 @@
       <c r="D18" s="2">
         <v>70</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="62">
         <v>-50</v>
       </c>
       <c r="F18" s="2">
         <v>-60</v>
       </c>
-      <c r="G18" s="2">
-        <v>-20</v>
-      </c>
+      <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="22"/>
       <c r="J18" s="23">
         <f>SUM(B18:I18)</f>
-        <v>199</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="55"/>
@@ -1920,509 +1922,509 @@
       <c r="H19" s="2"/>
       <c r="I19" s="20"/>
     </row>
-    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D20" s="12"/>
       <c r="H20" s="56" t="s">
         <v>37</v>
       </c>
       <c r="I20" s="25">
         <f>+H14+J14+G14</f>
-        <v>334.88</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>344.06</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D21" s="12"/>
       <c r="H21" s="26" t="s">
         <v>38</v>
       </c>
       <c r="I21" s="25">
         <f>+J18-H14-G14</f>
-        <v>199</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D22" s="20"/>
       <c r="H22" s="27" t="s">
         <v>54</v>
       </c>
       <c r="I22" s="25">
         <f>+I21-J14</f>
-        <v>-135.88</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+        <v>-125.06</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D23" s="12"/>
       <c r="I23" s="20"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D24" s="12"/>
       <c r="I24" s="20"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D25" s="12"/>
       <c r="I25" s="20"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D26" s="12"/>
       <c r="I26" s="20"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D27" s="12"/>
       <c r="I27" s="20"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D28" s="12"/>
       <c r="I28" s="20"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D29" s="12"/>
       <c r="I29" s="20"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D30" s="11"/>
       <c r="I30" s="20"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D31" s="20"/>
       <c r="I31" s="20"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D32" s="11"/>
       <c r="I32" s="20"/>
     </row>
-    <row r="33" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D33" s="11"/>
       <c r="I33" s="20"/>
     </row>
-    <row r="34" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D34" s="11"/>
       <c r="I34" s="20"/>
     </row>
-    <row r="35" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D35" s="11"/>
       <c r="I35" s="20"/>
     </row>
-    <row r="36" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D36" s="11"/>
       <c r="I36" s="20"/>
     </row>
-    <row r="37" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D37" s="11"/>
       <c r="I37" s="20"/>
     </row>
-    <row r="38" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D38" s="11"/>
       <c r="I38" s="20"/>
     </row>
-    <row r="39" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D39" s="11"/>
       <c r="I39" s="20"/>
     </row>
-    <row r="40" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D40" s="11"/>
       <c r="I40" s="20"/>
     </row>
-    <row r="41" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D41" s="20"/>
       <c r="I41" s="20"/>
     </row>
-    <row r="42" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D42" s="12"/>
       <c r="I42" s="20"/>
     </row>
-    <row r="43" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D43" s="12"/>
       <c r="I43" s="20"/>
     </row>
-    <row r="44" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D44" s="20"/>
       <c r="I44" s="20"/>
     </row>
-    <row r="45" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D45" s="20"/>
       <c r="I45" s="20"/>
     </row>
-    <row r="46" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D46" s="20"/>
       <c r="I46" s="20"/>
     </row>
-    <row r="47" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D47" s="20"/>
       <c r="I47" s="20"/>
     </row>
-    <row r="48" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D48" s="20"/>
       <c r="I48" s="20"/>
     </row>
-    <row r="49" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D49" s="20"/>
       <c r="I49" s="20"/>
     </row>
-    <row r="50" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D50" s="20"/>
       <c r="I50" s="20"/>
     </row>
-    <row r="51" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D51" s="20"/>
       <c r="I51" s="20"/>
     </row>
-    <row r="52" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D52" s="20"/>
       <c r="I52" s="20"/>
     </row>
-    <row r="53" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D53" s="20"/>
       <c r="I53" s="20"/>
     </row>
-    <row r="54" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D54" s="20"/>
       <c r="I54" s="20"/>
     </row>
-    <row r="55" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D55" s="20"/>
       <c r="I55" s="20"/>
     </row>
-    <row r="56" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D56" s="20"/>
       <c r="I56" s="20"/>
     </row>
-    <row r="57" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D57" s="20"/>
       <c r="I57" s="20"/>
     </row>
-    <row r="58" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D58" s="20"/>
       <c r="I58" s="20"/>
     </row>
-    <row r="59" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D59" s="20"/>
       <c r="I59" s="20"/>
     </row>
-    <row r="60" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D60" s="20"/>
       <c r="I60" s="20"/>
     </row>
-    <row r="61" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D61" s="20"/>
       <c r="I61" s="20"/>
     </row>
-    <row r="62" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D62" s="20"/>
       <c r="I62" s="20"/>
     </row>
-    <row r="63" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D63" s="20"/>
       <c r="I63" s="20"/>
     </row>
-    <row r="64" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D64" s="20"/>
       <c r="I64" s="20"/>
     </row>
-    <row r="65" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D65" s="20"/>
       <c r="I65" s="20"/>
     </row>
-    <row r="66" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D66" s="20"/>
       <c r="I66" s="20"/>
     </row>
-    <row r="67" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D67" s="20"/>
       <c r="I67" s="20"/>
     </row>
-    <row r="68" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D68" s="20"/>
       <c r="I68" s="20"/>
     </row>
-    <row r="69" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D69" s="20"/>
       <c r="I69" s="20"/>
     </row>
-    <row r="70" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D70" s="20"/>
       <c r="I70" s="20"/>
     </row>
-    <row r="71" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D71" s="20"/>
       <c r="I71" s="20"/>
     </row>
-    <row r="72" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D72" s="20"/>
       <c r="I72" s="20"/>
     </row>
-    <row r="73" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D73" s="20"/>
       <c r="I73" s="20"/>
     </row>
-    <row r="74" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D74" s="20"/>
       <c r="I74" s="20"/>
     </row>
-    <row r="75" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D75" s="20"/>
       <c r="I75" s="20"/>
     </row>
-    <row r="76" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D76" s="20"/>
       <c r="I76" s="20"/>
     </row>
-    <row r="77" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D77" s="20"/>
       <c r="I77" s="20"/>
     </row>
-    <row r="78" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D78" s="20"/>
       <c r="I78" s="20"/>
     </row>
-    <row r="79" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D79" s="20"/>
       <c r="I79" s="20"/>
     </row>
-    <row r="80" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D80" s="20"/>
       <c r="I80" s="20"/>
     </row>
-    <row r="81" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D81" s="20"/>
       <c r="I81" s="20"/>
     </row>
-    <row r="82" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D82" s="20"/>
       <c r="I82" s="20"/>
     </row>
-    <row r="83" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D83" s="20"/>
       <c r="I83" s="20"/>
     </row>
-    <row r="84" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D84" s="20"/>
       <c r="I84" s="20"/>
     </row>
-    <row r="85" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D85" s="20"/>
       <c r="I85" s="20"/>
     </row>
-    <row r="86" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D86" s="20"/>
       <c r="I86" s="20"/>
     </row>
-    <row r="87" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D87" s="20"/>
       <c r="I87" s="20"/>
     </row>
-    <row r="88" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D88" s="20"/>
       <c r="I88" s="20"/>
     </row>
-    <row r="89" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D89" s="20"/>
       <c r="I89" s="20"/>
     </row>
-    <row r="90" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D90" s="20"/>
       <c r="I90" s="20"/>
     </row>
-    <row r="91" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D91" s="20"/>
       <c r="I91" s="20"/>
     </row>
-    <row r="92" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D92" s="20"/>
       <c r="I92" s="20"/>
     </row>
-    <row r="93" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D93" s="20"/>
       <c r="I93" s="20"/>
     </row>
-    <row r="94" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D94" s="20"/>
       <c r="I94" s="20"/>
     </row>
-    <row r="95" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D95" s="20"/>
       <c r="I95" s="20"/>
     </row>
-    <row r="96" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D96" s="20"/>
       <c r="I96" s="20"/>
     </row>
-    <row r="97" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D97" s="20"/>
       <c r="I97" s="20"/>
     </row>
-    <row r="98" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D98" s="20"/>
       <c r="I98" s="20"/>
     </row>
-    <row r="99" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D99" s="20"/>
       <c r="I99" s="20"/>
     </row>
-    <row r="100" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D100" s="20"/>
       <c r="I100" s="20"/>
     </row>
-    <row r="101" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D101" s="20"/>
       <c r="I101" s="20"/>
     </row>
-    <row r="102" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D102" s="20"/>
       <c r="I102" s="20"/>
     </row>
-    <row r="103" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D103" s="20"/>
       <c r="I103" s="20"/>
     </row>
-    <row r="104" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D104" s="20"/>
       <c r="I104" s="20"/>
     </row>
-    <row r="105" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D105" s="20"/>
       <c r="I105" s="20"/>
     </row>
-    <row r="106" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D106" s="20"/>
       <c r="I106" s="20"/>
     </row>
-    <row r="107" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D107" s="20"/>
       <c r="I107" s="20"/>
     </row>
-    <row r="108" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D108" s="20"/>
       <c r="I108" s="20"/>
     </row>
-    <row r="109" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D109" s="20"/>
       <c r="I109" s="20"/>
     </row>
-    <row r="110" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D110" s="20"/>
       <c r="I110" s="20"/>
     </row>
-    <row r="111" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D111" s="20"/>
       <c r="I111" s="20"/>
     </row>
-    <row r="112" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D112" s="20"/>
       <c r="I112" s="20"/>
     </row>
-    <row r="113" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D113" s="20"/>
       <c r="I113" s="20"/>
     </row>
-    <row r="114" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D114" s="20"/>
       <c r="I114" s="20"/>
     </row>
-    <row r="115" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D115" s="20"/>
       <c r="I115" s="20"/>
     </row>
-    <row r="116" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D116" s="20"/>
       <c r="I116" s="20"/>
     </row>
-    <row r="117" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D117" s="20"/>
       <c r="I117" s="20"/>
     </row>
-    <row r="118" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D118" s="20"/>
       <c r="I118" s="20"/>
     </row>
-    <row r="119" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D119" s="20"/>
       <c r="I119" s="20"/>
     </row>
-    <row r="120" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D120" s="20"/>
       <c r="I120" s="20"/>
     </row>
-    <row r="121" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D121" s="20"/>
       <c r="I121" s="20"/>
     </row>
-    <row r="122" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D122" s="20"/>
       <c r="I122" s="20"/>
     </row>
-    <row r="123" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D123" s="20"/>
       <c r="I123" s="20"/>
     </row>
-    <row r="124" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D124" s="20"/>
       <c r="I124" s="20"/>
     </row>
-    <row r="125" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D125" s="20"/>
       <c r="I125" s="20"/>
     </row>
-    <row r="126" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I126" s="20"/>
     </row>
-    <row r="127" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I127" s="20"/>
     </row>
-    <row r="128" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I128" s="20"/>
     </row>
-    <row r="129" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I129" s="20"/>
     </row>
-    <row r="130" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I130" s="20"/>
     </row>
-    <row r="131" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I131" s="20"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D16">
-    <cfRule type="timePeriod" dxfId="13" priority="37" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="24" priority="37" timePeriod="nextMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0+1)),YEAR(D1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="12" priority="38" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="23" priority="38" timePeriod="thisMonth">
       <formula>AND(MONTH(D1)=MONTH(TODAY()),YEAR(D1)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="11" priority="39" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="22" priority="39" timePeriod="lastMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0-1)),YEAR(D1)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D22:D29 D31 D41:D1048576">
-    <cfRule type="timePeriod" dxfId="10" priority="1" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="21" priority="1" timePeriod="nextMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0+1)),YEAR(D22)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="9" priority="2" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="20" priority="2" timePeriod="thisMonth">
       <formula>AND(MONTH(D22)=MONTH(TODAY()),YEAR(D22)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="8" priority="3" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="19" priority="3" timePeriod="lastMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0-1)),YEAR(D22)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="timePeriod" dxfId="7" priority="40" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="18" priority="40" timePeriod="nextMonth">
       <formula>AND(MONTH(I1)=MONTH(EDATE(TODAY(),0+1)),YEAR(I1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="6" priority="41" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="17" priority="41" timePeriod="thisMonth">
       <formula>AND(MONTH(I1)=MONTH(TODAY()),YEAR(I1)=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="cellIs" dxfId="5" priority="45" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="45" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I22">
-    <cfRule type="cellIs" dxfId="4" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="42" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
-    <cfRule type="cellIs" dxfId="3" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="43" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2437,14 +2439,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAE522B-09DD-4490-9CA8-387DE173331A}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
-    <col min="2" max="3" width="11.44140625" style="12"/>
-    <col min="4" max="4" width="11.88671875" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="11.42578125" style="12"/>
+    <col min="4" max="4" width="11.85546875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
         <v>49</v>
       </c>
@@ -2455,7 +2457,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="47"/>
       <c r="B2" s="11">
         <v>0</v>
@@ -2466,7 +2468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="47">
         <v>46037</v>
       </c>
@@ -2481,7 +2483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="47">
         <v>46053</v>
       </c>
@@ -2496,7 +2498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="47">
         <v>46068</v>
       </c>
@@ -2511,7 +2513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="47">
         <v>46081</v>
       </c>
@@ -2526,7 +2528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="47">
         <v>46096</v>
       </c>
@@ -2541,7 +2543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="47">
         <v>46112</v>
       </c>
@@ -2556,7 +2558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="47">
         <v>46127</v>
       </c>
@@ -2577,7 +2579,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="47">
         <v>46142</v>
       </c>
@@ -2593,7 +2595,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="47">
         <v>46157</v>
       </c>
@@ -2612,7 +2614,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="47">
         <v>46173</v>
       </c>
@@ -2628,7 +2630,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="47">
         <v>46188</v>
       </c>
@@ -2644,7 +2646,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="47">
         <v>46203</v>
       </c>
@@ -2660,7 +2662,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="47">
         <v>46218</v>
       </c>
@@ -2676,7 +2678,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="47">
         <v>46234</v>
       </c>
@@ -2692,7 +2694,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="47">
         <v>46249</v>
       </c>
@@ -2708,7 +2710,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="47">
         <v>46265</v>
       </c>
@@ -2724,7 +2726,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="47">
         <v>46280</v>
       </c>
@@ -2740,7 +2742,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="47">
         <v>46295</v>
       </c>
@@ -2756,7 +2758,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="47">
         <v>46310</v>
       </c>
@@ -2772,7 +2774,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="47">
         <v>46326</v>
       </c>
@@ -2788,7 +2790,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="47">
         <v>46341</v>
       </c>
@@ -2804,7 +2806,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="47">
         <v>46356</v>
       </c>
@@ -2820,7 +2822,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="47">
         <v>46371</v>
       </c>
@@ -2836,7 +2838,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="46" t="s">
         <v>50</v>
       </c>
@@ -2849,7 +2851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="46" t="s">
         <v>51</v>
       </c>
@@ -2862,7 +2864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="47">
         <v>46387</v>
       </c>
@@ -2878,7 +2880,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="47">
         <v>46402</v>
       </c>
@@ -2891,7 +2893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="47">
         <v>46418</v>
       </c>
@@ -2904,7 +2906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="47">
         <v>46433</v>
       </c>
@@ -2917,7 +2919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="47">
         <v>46446</v>
       </c>
@@ -2930,7 +2932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="47">
         <v>46461</v>
       </c>
@@ -2943,7 +2945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="47">
         <v>46477</v>
       </c>
@@ -2956,7 +2958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="47">
         <v>46492</v>
       </c>
@@ -2969,7 +2971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="47">
         <v>46507</v>
       </c>
@@ -2982,7 +2984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="47">
         <v>46522</v>
       </c>
@@ -2995,7 +2997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="47">
         <v>46538</v>
       </c>
@@ -3008,7 +3010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="47">
         <v>46553</v>
       </c>
@@ -3021,7 +3023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="47">
         <v>46568</v>
       </c>
@@ -3034,7 +3036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="47">
         <v>46583</v>
       </c>
@@ -3047,7 +3049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="47">
         <v>46599</v>
       </c>
@@ -3060,7 +3062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="47">
         <v>46614</v>
       </c>
@@ -3073,7 +3075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="47">
         <v>46630</v>
       </c>
@@ -3086,7 +3088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="47">
         <v>46645</v>
       </c>
@@ -3099,7 +3101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="47">
         <v>46660</v>
       </c>
@@ -3112,7 +3114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="47">
         <v>46675</v>
       </c>
@@ -3125,7 +3127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="47">
         <v>46691</v>
       </c>
@@ -3138,7 +3140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="47">
         <v>46706</v>
       </c>
@@ -3151,7 +3153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="47">
         <v>46721</v>
       </c>
@@ -3164,7 +3166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="47">
         <v>46736</v>
       </c>
@@ -3177,7 +3179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="46" t="s">
         <v>50</v>
       </c>
@@ -3190,7 +3192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="46" t="s">
         <v>51</v>
       </c>
@@ -3203,7 +3205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="47">
         <v>46752</v>
       </c>
@@ -3216,7 +3218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="50">
         <f>SUM(B2:B54)</f>
         <v>4610</v>
@@ -3226,34 +3228,34 @@
         <v>400</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
     </row>
-    <row r="57" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="60">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
         <v>-180</v>
       </c>
       <c r="C57" s="61"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B58" s="59"/>
       <c r="C58" s="3"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B59"/>
       <c r="C59" s="3"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
     </row>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2038722-EB46-4446-90CD-D1EC681CF739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{934104BB-04A5-4DD3-8251-F708FF598E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -674,13 +674,13 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1634,12 +1634,14 @@
       <c r="D5" s="20">
         <v>45817</v>
       </c>
-      <c r="H5" s="12"/>
+      <c r="H5" s="12">
+        <v>251</v>
+      </c>
       <c r="I5" s="20">
         <v>46118</v>
       </c>
       <c r="J5" s="12">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="K5" s="31">
         <v>0.27900000000000003</v>
@@ -1662,13 +1664,13 @@
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
-      <c r="H6" s="33"/>
+      <c r="H6" s="33">
+        <v>94.06</v>
+      </c>
       <c r="I6" s="20">
         <v>46148</v>
       </c>
-      <c r="J6" s="12">
-        <v>94.06</v>
-      </c>
+      <c r="J6" s="12"/>
       <c r="K6" s="31"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1850,12 +1852,12 @@
       </c>
       <c r="H14" s="21">
         <f>SUBTOTAL(109,H3:H13)</f>
-        <v>0</v>
+        <v>345.06</v>
       </c>
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>344.06</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -1891,7 +1893,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="57">
-        <v>219</v>
+        <v>165</v>
       </c>
       <c r="C18" s="2">
         <v>40</v>
@@ -1899,18 +1901,16 @@
       <c r="D18" s="2">
         <v>70</v>
       </c>
-      <c r="E18" s="62">
-        <v>-50</v>
-      </c>
-      <c r="F18" s="2">
-        <v>-60</v>
-      </c>
+      <c r="E18" s="60">
+        <v>50</v>
+      </c>
+      <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="22"/>
       <c r="J18" s="23">
         <f>SUM(B18:I18)</f>
-        <v>219</v>
+        <v>325</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="I20" s="25">
         <f>+H14+J14+G14</f>
-        <v>344.06</v>
+        <v>365.06</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="I21" s="25">
         <f>+J18-H14-G14</f>
-        <v>219</v>
+        <v>-20.060000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I22" s="25">
         <f>+I21-J14</f>
-        <v>-125.06</v>
+        <v>-40.06</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -2438,7 +2438,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAE522B-09DD-4490-9CA8-387DE173331A}">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -2446,7 +2446,7 @@
     <col min="4" max="4" width="11.85546875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
         <v>49</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="47"/>
       <c r="B2" s="11">
         <v>0</v>
@@ -2468,7 +2468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="47">
         <v>46037</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="47">
         <v>46053</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="47">
         <v>46068</v>
       </c>
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="47">
         <v>46081</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="47">
         <v>46096</v>
       </c>
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="47">
         <v>46112</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="47">
         <v>46127</v>
       </c>
@@ -2572,65 +2572,53 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="E9">
-        <v>100</v>
-      </c>
-      <c r="F9">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="47">
         <v>46142</v>
       </c>
       <c r="B10" s="11">
         <v>70</v>
       </c>
-      <c r="C10" s="11"/>
+      <c r="C10" s="11">
+        <v>0</v>
+      </c>
       <c r="D10" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="E10">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="47">
         <v>46157</v>
       </c>
       <c r="B11" s="11">
         <v>75</v>
       </c>
-      <c r="C11" s="11"/>
+      <c r="C11" s="11">
+        <v>50</v>
+      </c>
       <c r="D11" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="E11">
-        <v>100</v>
-      </c>
-      <c r="F11">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="47">
         <v>46173</v>
       </c>
       <c r="B12" s="11">
         <v>70</v>
       </c>
-      <c r="C12" s="11"/>
+      <c r="C12" s="11">
+        <v>100</v>
+      </c>
       <c r="D12" t="b">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="47">
         <v>46188</v>
       </c>
@@ -2642,11 +2630,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="E13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="47">
         <v>46203</v>
       </c>
@@ -2658,11 +2643,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="E14">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="47">
         <v>46218</v>
       </c>
@@ -2674,11 +2656,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="E15">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="47">
         <v>46234</v>
       </c>
@@ -2690,11 +2669,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="E16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="47">
         <v>46249</v>
       </c>
@@ -2706,11 +2682,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="E17">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="47">
         <v>46265</v>
       </c>
@@ -2722,11 +2695,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="E18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="47">
         <v>46280</v>
       </c>
@@ -2738,11 +2708,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="E19">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="47">
         <v>46295</v>
       </c>
@@ -2754,11 +2721,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="E20">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="47">
         <v>46310</v>
       </c>
@@ -2770,11 +2734,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="E21">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="47">
         <v>46326</v>
       </c>
@@ -2786,11 +2747,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="E22">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="47">
         <v>46341</v>
       </c>
@@ -2802,11 +2760,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="E23">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="47">
         <v>46356</v>
       </c>
@@ -2818,11 +2773,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="E24">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="47">
         <v>46371</v>
       </c>
@@ -2834,11 +2786,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="E25">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="46" t="s">
         <v>50</v>
       </c>
@@ -2851,7 +2800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="46" t="s">
         <v>51</v>
       </c>
@@ -2864,7 +2813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="47">
         <v>46387</v>
       </c>
@@ -2876,11 +2825,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="47">
         <v>46402</v>
       </c>
@@ -2893,7 +2839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="47">
         <v>46418</v>
       </c>
@@ -2906,7 +2852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="47">
         <v>46433</v>
       </c>
@@ -2919,7 +2865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="47">
         <v>46446</v>
       </c>
@@ -3225,7 +3171,7 @@
       </c>
       <c r="C55" s="51">
         <f>SUM(C2:C54)</f>
-        <v>400</v>
+        <v>550</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3233,11 +3179,11 @@
       <c r="C56" s="3"/>
     </row>
     <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="60">
+      <c r="B57" s="61">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
         <v>-180</v>
       </c>
-      <c r="C57" s="61"/>
+      <c r="C57" s="62"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B58" s="59"/>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{934104BB-04A5-4DD3-8251-F708FF598E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5322C1-E241-44A7-97C2-A736E2112449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -31,15 +31,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="61">
   <si>
     <t>Totales</t>
   </si>
@@ -219,6 +216,9 @@
   </si>
   <si>
     <t>Tasa cero Sillones</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -714,68 +714,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="21" formatCode="d\-mmm"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -921,6 +859,68 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="d\-mmm"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -940,7 +940,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="13" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="28" tableBorderDxfId="27">
   <autoFilter ref="A2:K14" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K14">
     <sortCondition ref="D3:D14"/>
@@ -948,17 +948,17 @@
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{4E2F1548-5DA7-4ADC-946F-053ED807460A}" name="Banco"/>
     <tableColumn id="2" xr3:uid="{11D77EA7-239F-47E1-9378-FFBA07ACDD06}" name="Tarjeta"/>
-    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="9">
+    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="24">
       <calculatedColumnFormula>186.68-48</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="3" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="23"/>
+    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="18" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1261,17 +1261,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0DE2A9-9218-4E10-883D-DF66D771FC39}">
-  <dimension ref="B1:H37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:J37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="3.140625" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="3.109375" customWidth="1"/>
+    <col min="6" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B1" s="13" t="s">
         <v>14</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1293,11 +1293,14 @@
       <c r="D2" s="8">
         <v>60</v>
       </c>
+      <c r="E2" t="s">
+        <v>60</v>
+      </c>
       <c r="F2" s="8">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
@@ -1310,8 +1313,12 @@
       <c r="F3" s="8">
         <v>50</v>
       </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="J3">
+        <f>482-95-110</f>
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
@@ -1321,11 +1328,14 @@
       <c r="D4" s="8">
         <v>10</v>
       </c>
+      <c r="E4" t="s">
+        <v>60</v>
+      </c>
       <c r="F4" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
@@ -1339,7 +1349,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
@@ -1353,7 +1363,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="9" t="s">
         <v>17</v>
       </c>
@@ -1367,7 +1377,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -1378,7 +1388,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -1389,7 +1399,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -1397,7 +1407,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -1408,7 +1418,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>9</v>
       </c>
@@ -1418,6 +1428,9 @@
       <c r="D12">
         <v>15</v>
       </c>
+      <c r="E12" t="s">
+        <v>60</v>
+      </c>
       <c r="F12">
         <v>5</v>
       </c>
@@ -1425,7 +1438,7 @@
         <v>8286917</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>10</v>
       </c>
@@ -1433,7 +1446,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>15</v>
       </c>
@@ -1444,7 +1457,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>59</v>
       </c>
@@ -1454,8 +1467,11 @@
       <c r="D15">
         <v>48</v>
       </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>11</v>
       </c>
@@ -1469,7 +1485,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="s">
         <v>12</v>
       </c>
@@ -1482,7 +1498,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="5" t="s">
         <v>13</v>
       </c>
@@ -1496,24 +1512,24 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="37" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="30.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>$C$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
       <formula>$C$7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
       <formula>$C$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
       <formula>$C$2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1525,22 +1541,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B43D18-F407-4702-B159-A2C7E22E2016}">
   <dimension ref="A1:N131"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="19" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="12" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" style="12" customWidth="1"/>
-    <col min="7" max="8" width="16.140625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" style="10" customWidth="1"/>
-    <col min="10" max="10" width="17.42578125" style="12" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" style="19" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" style="12" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" style="12" customWidth="1"/>
+    <col min="7" max="8" width="16.109375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" style="10" customWidth="1"/>
+    <col min="10" max="10" width="17.44140625" style="12" customWidth="1"/>
+    <col min="11" max="11" width="7.109375" style="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
         <v>19</v>
       </c>
@@ -1575,7 +1591,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="39" t="s">
         <v>40</v>
       </c>
@@ -1598,7 +1614,7 @@
       <c r="J3" s="42"/>
       <c r="K3" s="43"/>
     </row>
-    <row r="4" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="34" t="s">
         <v>56</v>
       </c>
@@ -1621,7 +1637,7 @@
       <c r="J4" s="37"/>
       <c r="K4" s="38"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -1638,17 +1654,17 @@
         <v>251</v>
       </c>
       <c r="I5" s="20">
-        <v>46118</v>
+        <v>46179</v>
       </c>
       <c r="J5" s="12">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K5" s="31">
         <v>0.27900000000000003</v>
       </c>
       <c r="N5" s="4"/>
     </row>
-    <row r="6" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1665,15 +1681,17 @@
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
       <c r="H6" s="33">
-        <v>94.06</v>
+        <v>95</v>
       </c>
       <c r="I6" s="20">
-        <v>46148</v>
-      </c>
-      <c r="J6" s="12"/>
+        <v>46179</v>
+      </c>
+      <c r="J6" s="12">
+        <v>80</v>
+      </c>
       <c r="K6" s="31"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -1695,7 +1713,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34" t="s">
         <v>39</v>
       </c>
@@ -1718,7 +1736,7 @@
       <c r="J8" s="37"/>
       <c r="K8" s="38"/>
     </row>
-    <row r="9" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="52" t="s">
         <v>29</v>
       </c>
@@ -1741,7 +1759,7 @@
       <c r="J9" s="44"/>
       <c r="K9" s="54"/>
     </row>
-    <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1764,7 +1782,7 @@
       <c r="J10" s="12"/>
       <c r="K10" s="31"/>
     </row>
-    <row r="11" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
         <v>29</v>
       </c>
@@ -1787,7 +1805,7 @@
       <c r="J11" s="37"/>
       <c r="K11" s="38"/>
     </row>
-    <row r="12" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="39" t="s">
         <v>58</v>
       </c>
@@ -1810,7 +1828,7 @@
       <c r="J12" s="42"/>
       <c r="K12" s="43"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="39" t="s">
         <v>58</v>
       </c>
@@ -1832,7 +1850,7 @@
         <v>45946</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -1852,24 +1870,24 @@
       </c>
       <c r="H14" s="21">
         <f>SUBTOTAL(109,H3:H13)</f>
-        <v>345.06</v>
+        <v>346</v>
       </c>
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D15" s="20"/>
       <c r="I15" s="20"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D16" s="20"/>
       <c r="I16" s="20"/>
     </row>
-    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1877,32 +1895,34 @@
         <v>36</v>
       </c>
       <c r="C17" s="24">
-        <v>46157</v>
+        <v>46172</v>
       </c>
       <c r="D17" s="24">
-        <v>46172</v>
-      </c>
-      <c r="E17" s="24"/>
+        <v>46188</v>
+      </c>
+      <c r="E17" s="24">
+        <v>46203</v>
+      </c>
       <c r="F17" s="24"/>
       <c r="G17" s="24"/>
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
     </row>
-    <row r="18" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B18" s="57">
-        <v>165</v>
+        <v>435</v>
       </c>
       <c r="C18" s="2">
+        <v>70</v>
+      </c>
+      <c r="D18" s="2">
         <v>40</v>
       </c>
-      <c r="D18" s="2">
+      <c r="E18" s="60">
         <v>70</v>
-      </c>
-      <c r="E18" s="60">
-        <v>50</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -1910,10 +1930,10 @@
       <c r="I18" s="22"/>
       <c r="J18" s="23">
         <f>SUM(B18:I18)</f>
-        <v>325</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="55"/>
@@ -1922,509 +1942,509 @@
       <c r="H19" s="2"/>
       <c r="I19" s="20"/>
     </row>
-    <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D20" s="12"/>
       <c r="H20" s="56" t="s">
         <v>37</v>
       </c>
       <c r="I20" s="25">
         <f>+H14+J14+G14</f>
-        <v>365.06</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D21" s="12"/>
       <c r="H21" s="26" t="s">
         <v>38</v>
       </c>
       <c r="I21" s="25">
         <f>+J18-H14-G14</f>
-        <v>-20.060000000000002</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D22" s="20"/>
       <c r="H22" s="27" t="s">
         <v>54</v>
       </c>
       <c r="I22" s="25">
         <f>+I21-J14</f>
-        <v>-40.06</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D23" s="12"/>
       <c r="I23" s="20"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D24" s="12"/>
       <c r="I24" s="20"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D25" s="12"/>
       <c r="I25" s="20"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D26" s="12"/>
       <c r="I26" s="20"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D27" s="12"/>
       <c r="I27" s="20"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D28" s="12"/>
       <c r="I28" s="20"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D29" s="12"/>
       <c r="I29" s="20"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D30" s="11"/>
       <c r="I30" s="20"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D31" s="20"/>
       <c r="I31" s="20"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D32" s="11"/>
       <c r="I32" s="20"/>
     </row>
-    <row r="33" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D33" s="11"/>
       <c r="I33" s="20"/>
     </row>
-    <row r="34" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D34" s="11"/>
       <c r="I34" s="20"/>
     </row>
-    <row r="35" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D35" s="11"/>
       <c r="I35" s="20"/>
     </row>
-    <row r="36" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D36" s="11"/>
       <c r="I36" s="20"/>
     </row>
-    <row r="37" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D37" s="11"/>
       <c r="I37" s="20"/>
     </row>
-    <row r="38" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D38" s="11"/>
       <c r="I38" s="20"/>
     </row>
-    <row r="39" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D39" s="11"/>
       <c r="I39" s="20"/>
     </row>
-    <row r="40" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D40" s="11"/>
       <c r="I40" s="20"/>
     </row>
-    <row r="41" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D41" s="20"/>
       <c r="I41" s="20"/>
     </row>
-    <row r="42" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D42" s="12"/>
       <c r="I42" s="20"/>
     </row>
-    <row r="43" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D43" s="12"/>
       <c r="I43" s="20"/>
     </row>
-    <row r="44" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D44" s="20"/>
       <c r="I44" s="20"/>
     </row>
-    <row r="45" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D45" s="20"/>
       <c r="I45" s="20"/>
     </row>
-    <row r="46" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D46" s="20"/>
       <c r="I46" s="20"/>
     </row>
-    <row r="47" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D47" s="20"/>
       <c r="I47" s="20"/>
     </row>
-    <row r="48" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D48" s="20"/>
       <c r="I48" s="20"/>
     </row>
-    <row r="49" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D49" s="20"/>
       <c r="I49" s="20"/>
     </row>
-    <row r="50" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D50" s="20"/>
       <c r="I50" s="20"/>
     </row>
-    <row r="51" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D51" s="20"/>
       <c r="I51" s="20"/>
     </row>
-    <row r="52" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D52" s="20"/>
       <c r="I52" s="20"/>
     </row>
-    <row r="53" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D53" s="20"/>
       <c r="I53" s="20"/>
     </row>
-    <row r="54" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D54" s="20"/>
       <c r="I54" s="20"/>
     </row>
-    <row r="55" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D55" s="20"/>
       <c r="I55" s="20"/>
     </row>
-    <row r="56" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D56" s="20"/>
       <c r="I56" s="20"/>
     </row>
-    <row r="57" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D57" s="20"/>
       <c r="I57" s="20"/>
     </row>
-    <row r="58" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D58" s="20"/>
       <c r="I58" s="20"/>
     </row>
-    <row r="59" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D59" s="20"/>
       <c r="I59" s="20"/>
     </row>
-    <row r="60" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D60" s="20"/>
       <c r="I60" s="20"/>
     </row>
-    <row r="61" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D61" s="20"/>
       <c r="I61" s="20"/>
     </row>
-    <row r="62" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D62" s="20"/>
       <c r="I62" s="20"/>
     </row>
-    <row r="63" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D63" s="20"/>
       <c r="I63" s="20"/>
     </row>
-    <row r="64" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D64" s="20"/>
       <c r="I64" s="20"/>
     </row>
-    <row r="65" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D65" s="20"/>
       <c r="I65" s="20"/>
     </row>
-    <row r="66" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D66" s="20"/>
       <c r="I66" s="20"/>
     </row>
-    <row r="67" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D67" s="20"/>
       <c r="I67" s="20"/>
     </row>
-    <row r="68" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D68" s="20"/>
       <c r="I68" s="20"/>
     </row>
-    <row r="69" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D69" s="20"/>
       <c r="I69" s="20"/>
     </row>
-    <row r="70" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D70" s="20"/>
       <c r="I70" s="20"/>
     </row>
-    <row r="71" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D71" s="20"/>
       <c r="I71" s="20"/>
     </row>
-    <row r="72" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D72" s="20"/>
       <c r="I72" s="20"/>
     </row>
-    <row r="73" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D73" s="20"/>
       <c r="I73" s="20"/>
     </row>
-    <row r="74" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D74" s="20"/>
       <c r="I74" s="20"/>
     </row>
-    <row r="75" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D75" s="20"/>
       <c r="I75" s="20"/>
     </row>
-    <row r="76" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D76" s="20"/>
       <c r="I76" s="20"/>
     </row>
-    <row r="77" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D77" s="20"/>
       <c r="I77" s="20"/>
     </row>
-    <row r="78" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D78" s="20"/>
       <c r="I78" s="20"/>
     </row>
-    <row r="79" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D79" s="20"/>
       <c r="I79" s="20"/>
     </row>
-    <row r="80" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D80" s="20"/>
       <c r="I80" s="20"/>
     </row>
-    <row r="81" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D81" s="20"/>
       <c r="I81" s="20"/>
     </row>
-    <row r="82" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D82" s="20"/>
       <c r="I82" s="20"/>
     </row>
-    <row r="83" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D83" s="20"/>
       <c r="I83" s="20"/>
     </row>
-    <row r="84" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D84" s="20"/>
       <c r="I84" s="20"/>
     </row>
-    <row r="85" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D85" s="20"/>
       <c r="I85" s="20"/>
     </row>
-    <row r="86" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D86" s="20"/>
       <c r="I86" s="20"/>
     </row>
-    <row r="87" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D87" s="20"/>
       <c r="I87" s="20"/>
     </row>
-    <row r="88" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D88" s="20"/>
       <c r="I88" s="20"/>
     </row>
-    <row r="89" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D89" s="20"/>
       <c r="I89" s="20"/>
     </row>
-    <row r="90" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D90" s="20"/>
       <c r="I90" s="20"/>
     </row>
-    <row r="91" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D91" s="20"/>
       <c r="I91" s="20"/>
     </row>
-    <row r="92" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D92" s="20"/>
       <c r="I92" s="20"/>
     </row>
-    <row r="93" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D93" s="20"/>
       <c r="I93" s="20"/>
     </row>
-    <row r="94" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D94" s="20"/>
       <c r="I94" s="20"/>
     </row>
-    <row r="95" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D95" s="20"/>
       <c r="I95" s="20"/>
     </row>
-    <row r="96" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D96" s="20"/>
       <c r="I96" s="20"/>
     </row>
-    <row r="97" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D97" s="20"/>
       <c r="I97" s="20"/>
     </row>
-    <row r="98" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D98" s="20"/>
       <c r="I98" s="20"/>
     </row>
-    <row r="99" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D99" s="20"/>
       <c r="I99" s="20"/>
     </row>
-    <row r="100" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D100" s="20"/>
       <c r="I100" s="20"/>
     </row>
-    <row r="101" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D101" s="20"/>
       <c r="I101" s="20"/>
     </row>
-    <row r="102" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D102" s="20"/>
       <c r="I102" s="20"/>
     </row>
-    <row r="103" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D103" s="20"/>
       <c r="I103" s="20"/>
     </row>
-    <row r="104" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D104" s="20"/>
       <c r="I104" s="20"/>
     </row>
-    <row r="105" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D105" s="20"/>
       <c r="I105" s="20"/>
     </row>
-    <row r="106" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D106" s="20"/>
       <c r="I106" s="20"/>
     </row>
-    <row r="107" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D107" s="20"/>
       <c r="I107" s="20"/>
     </row>
-    <row r="108" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D108" s="20"/>
       <c r="I108" s="20"/>
     </row>
-    <row r="109" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D109" s="20"/>
       <c r="I109" s="20"/>
     </row>
-    <row r="110" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D110" s="20"/>
       <c r="I110" s="20"/>
     </row>
-    <row r="111" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D111" s="20"/>
       <c r="I111" s="20"/>
     </row>
-    <row r="112" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D112" s="20"/>
       <c r="I112" s="20"/>
     </row>
-    <row r="113" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D113" s="20"/>
       <c r="I113" s="20"/>
     </row>
-    <row r="114" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D114" s="20"/>
       <c r="I114" s="20"/>
     </row>
-    <row r="115" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D115" s="20"/>
       <c r="I115" s="20"/>
     </row>
-    <row r="116" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D116" s="20"/>
       <c r="I116" s="20"/>
     </row>
-    <row r="117" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D117" s="20"/>
       <c r="I117" s="20"/>
     </row>
-    <row r="118" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D118" s="20"/>
       <c r="I118" s="20"/>
     </row>
-    <row r="119" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D119" s="20"/>
       <c r="I119" s="20"/>
     </row>
-    <row r="120" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D120" s="20"/>
       <c r="I120" s="20"/>
     </row>
-    <row r="121" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D121" s="20"/>
       <c r="I121" s="20"/>
     </row>
-    <row r="122" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D122" s="20"/>
       <c r="I122" s="20"/>
     </row>
-    <row r="123" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D123" s="20"/>
       <c r="I123" s="20"/>
     </row>
-    <row r="124" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D124" s="20"/>
       <c r="I124" s="20"/>
     </row>
-    <row r="125" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D125" s="20"/>
       <c r="I125" s="20"/>
     </row>
-    <row r="126" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I126" s="20"/>
     </row>
-    <row r="127" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I127" s="20"/>
     </row>
-    <row r="128" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I128" s="20"/>
     </row>
-    <row r="129" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I129" s="20"/>
     </row>
-    <row r="130" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I130" s="20"/>
     </row>
-    <row r="131" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I131" s="20"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D16">
-    <cfRule type="timePeriod" dxfId="24" priority="37" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="13" priority="37" timePeriod="nextMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0+1)),YEAR(D1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="23" priority="38" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="12" priority="38" timePeriod="thisMonth">
       <formula>AND(MONTH(D1)=MONTH(TODAY()),YEAR(D1)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="22" priority="39" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="11" priority="39" timePeriod="lastMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0-1)),YEAR(D1)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D22:D29 D31 D41:D1048576">
-    <cfRule type="timePeriod" dxfId="21" priority="1" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="10" priority="1" timePeriod="nextMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0+1)),YEAR(D22)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="20" priority="2" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="9" priority="2" timePeriod="thisMonth">
       <formula>AND(MONTH(D22)=MONTH(TODAY()),YEAR(D22)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="19" priority="3" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="8" priority="3" timePeriod="lastMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0-1)),YEAR(D22)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="timePeriod" dxfId="18" priority="40" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="7" priority="40" timePeriod="nextMonth">
       <formula>AND(MONTH(I1)=MONTH(EDATE(TODAY(),0+1)),YEAR(I1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="17" priority="41" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="6" priority="41" timePeriod="thisMonth">
       <formula>AND(MONTH(I1)=MONTH(TODAY()),YEAR(I1)=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="cellIs" dxfId="16" priority="45" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="45" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I22">
-    <cfRule type="cellIs" dxfId="15" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="42" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
-    <cfRule type="cellIs" dxfId="14" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="43" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2439,14 +2459,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAE522B-09DD-4490-9CA8-387DE173331A}">
   <dimension ref="A1:D62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
-    <col min="2" max="3" width="11.42578125" style="12"/>
-    <col min="4" max="4" width="11.85546875" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="11.44140625" style="12"/>
+    <col min="4" max="4" width="11.88671875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="45" t="s">
         <v>49</v>
       </c>
@@ -2457,7 +2477,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="47"/>
       <c r="B2" s="11">
         <v>0</v>
@@ -2468,7 +2488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="47">
         <v>46037</v>
       </c>
@@ -2483,7 +2503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="47">
         <v>46053</v>
       </c>
@@ -2498,7 +2518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="47">
         <v>46068</v>
       </c>
@@ -2513,7 +2533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="47">
         <v>46081</v>
       </c>
@@ -2528,7 +2548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="47">
         <v>46096</v>
       </c>
@@ -2543,7 +2563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="47">
         <v>46112</v>
       </c>
@@ -2558,7 +2578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="47">
         <v>46127</v>
       </c>
@@ -2573,7 +2593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="47">
         <v>46142</v>
       </c>
@@ -2588,7 +2608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="47">
         <v>46157</v>
       </c>
@@ -2603,7 +2623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="47">
         <v>46173</v>
       </c>
@@ -2618,7 +2638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="47">
         <v>46188</v>
       </c>
@@ -2631,7 +2651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="47">
         <v>46203</v>
       </c>
@@ -2644,7 +2664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="47">
         <v>46218</v>
       </c>
@@ -2657,7 +2677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="47">
         <v>46234</v>
       </c>
@@ -2670,7 +2690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="47">
         <v>46249</v>
       </c>
@@ -2683,7 +2703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="47">
         <v>46265</v>
       </c>
@@ -2696,7 +2716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="47">
         <v>46280</v>
       </c>
@@ -2709,7 +2729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="47">
         <v>46295</v>
       </c>
@@ -2722,7 +2742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="47">
         <v>46310</v>
       </c>
@@ -2735,7 +2755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="47">
         <v>46326</v>
       </c>
@@ -2748,7 +2768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="47">
         <v>46341</v>
       </c>
@@ -2761,7 +2781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="47">
         <v>46356</v>
       </c>
@@ -2774,7 +2794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="47">
         <v>46371</v>
       </c>
@@ -2787,7 +2807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="46" t="s">
         <v>50</v>
       </c>
@@ -2800,7 +2820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="46" t="s">
         <v>51</v>
       </c>
@@ -2813,7 +2833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="47">
         <v>46387</v>
       </c>
@@ -2826,7 +2846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="47">
         <v>46402</v>
       </c>
@@ -2839,7 +2859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="47">
         <v>46418</v>
       </c>
@@ -2852,7 +2872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="47">
         <v>46433</v>
       </c>
@@ -2865,7 +2885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="47">
         <v>46446</v>
       </c>
@@ -2878,7 +2898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="47">
         <v>46461</v>
       </c>
@@ -2891,7 +2911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="47">
         <v>46477</v>
       </c>
@@ -2904,7 +2924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="47">
         <v>46492</v>
       </c>
@@ -2917,7 +2937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="47">
         <v>46507</v>
       </c>
@@ -2930,7 +2950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="47">
         <v>46522</v>
       </c>
@@ -2943,7 +2963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="47">
         <v>46538</v>
       </c>
@@ -2956,7 +2976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="47">
         <v>46553</v>
       </c>
@@ -2969,7 +2989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="47">
         <v>46568</v>
       </c>
@@ -2982,7 +3002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="47">
         <v>46583</v>
       </c>
@@ -2995,7 +3015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="47">
         <v>46599</v>
       </c>
@@ -3008,7 +3028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="47">
         <v>46614</v>
       </c>
@@ -3021,7 +3041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="47">
         <v>46630</v>
       </c>
@@ -3034,7 +3054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="47">
         <v>46645</v>
       </c>
@@ -3047,7 +3067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="47">
         <v>46660</v>
       </c>
@@ -3060,7 +3080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="47">
         <v>46675</v>
       </c>
@@ -3073,7 +3093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="47">
         <v>46691</v>
       </c>
@@ -3086,7 +3106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="47">
         <v>46706</v>
       </c>
@@ -3099,7 +3119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="47">
         <v>46721</v>
       </c>
@@ -3112,7 +3132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="47">
         <v>46736</v>
       </c>
@@ -3125,7 +3145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="46" t="s">
         <v>50</v>
       </c>
@@ -3138,7 +3158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="46" t="s">
         <v>51</v>
       </c>
@@ -3151,7 +3171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="47">
         <v>46752</v>
       </c>
@@ -3164,7 +3184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="50">
         <f>SUM(B2:B54)</f>
         <v>4610</v>
@@ -3174,34 +3194,34 @@
         <v>550</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
     </row>
-    <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="61">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
-        <v>-180</v>
+        <v>-205</v>
       </c>
       <c r="C57" s="62"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B58" s="59"/>
       <c r="C58" s="3"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B59"/>
       <c r="C59" s="3"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
     </row>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5322C1-E241-44A7-97C2-A736E2112449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5683051E-7897-43DB-A825-42B18935446B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -714,6 +717,68 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="21" formatCode="d\-mmm"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -859,68 +924,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="d\-mmm"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -940,7 +943,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="28" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="13" tableBorderDxfId="12">
   <autoFilter ref="A2:K14" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K14">
     <sortCondition ref="D3:D14"/>
@@ -948,17 +951,17 @@
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{4E2F1548-5DA7-4ADC-946F-053ED807460A}" name="Banco"/>
     <tableColumn id="2" xr3:uid="{11D77EA7-239F-47E1-9378-FFBA07ACDD06}" name="Tarjeta"/>
-    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="24">
+    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="9">
       <calculatedColumnFormula>186.68-48</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="23"/>
-    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="18" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="3" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1262,16 +1265,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0DE2A9-9218-4E10-883D-DF66D771FC39}">
   <dimension ref="B1:J37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="3.109375" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="3.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
         <v>14</v>
       </c>
@@ -1283,7 +1286,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1300,7 +1303,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
@@ -1318,7 +1321,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
@@ -1335,7 +1338,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
@@ -1349,7 +1352,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
@@ -1363,7 +1366,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>17</v>
       </c>
@@ -1377,7 +1380,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -1388,7 +1391,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -1399,7 +1402,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -1407,7 +1410,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -1418,7 +1421,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>9</v>
       </c>
@@ -1438,7 +1441,7 @@
         <v>8286917</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>10</v>
       </c>
@@ -1446,7 +1449,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>15</v>
       </c>
@@ -1457,7 +1460,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>59</v>
       </c>
@@ -1471,7 +1474,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="7" t="s">
         <v>11</v>
       </c>
@@ -1485,7 +1488,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
         <v>12</v>
       </c>
@@ -1498,7 +1501,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>13</v>
       </c>
@@ -1512,24 +1515,24 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="37" ht="30.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
       <formula>$C$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
       <formula>$C$7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="equal">
       <formula>$C$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="4" operator="equal">
       <formula>$C$2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1541,22 +1544,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B43D18-F407-4702-B159-A2C7E22E2016}">
   <dimension ref="A1:N131"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" style="19" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" style="12" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" style="12" customWidth="1"/>
-    <col min="7" max="8" width="16.109375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" style="10" customWidth="1"/>
-    <col min="10" max="10" width="17.44140625" style="12" customWidth="1"/>
-    <col min="11" max="11" width="7.109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" style="12" customWidth="1"/>
+    <col min="7" max="8" width="16.140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" style="10" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" style="12" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" style="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>19</v>
       </c>
@@ -1591,7 +1594,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
         <v>40</v>
       </c>
@@ -1614,7 +1617,7 @@
       <c r="J3" s="42"/>
       <c r="K3" s="43"/>
     </row>
-    <row r="4" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="34" t="s">
         <v>56</v>
       </c>
@@ -1637,7 +1640,7 @@
       <c r="J4" s="37"/>
       <c r="K4" s="38"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -1657,14 +1660,14 @@
         <v>46179</v>
       </c>
       <c r="J5" s="12">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="K5" s="31">
         <v>0.27900000000000003</v>
       </c>
       <c r="N5" s="4"/>
     </row>
-    <row r="6" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1691,7 +1694,7 @@
       </c>
       <c r="K6" s="31"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -1713,7 +1716,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
         <v>39</v>
       </c>
@@ -1736,7 +1739,7 @@
       <c r="J8" s="37"/>
       <c r="K8" s="38"/>
     </row>
-    <row r="9" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
         <v>29</v>
       </c>
@@ -1759,7 +1762,7 @@
       <c r="J9" s="44"/>
       <c r="K9" s="54"/>
     </row>
-    <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1782,7 +1785,7 @@
       <c r="J10" s="12"/>
       <c r="K10" s="31"/>
     </row>
-    <row r="11" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
         <v>29</v>
       </c>
@@ -1805,7 +1808,7 @@
       <c r="J11" s="37"/>
       <c r="K11" s="38"/>
     </row>
-    <row r="12" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
         <v>58</v>
       </c>
@@ -1828,7 +1831,7 @@
       <c r="J12" s="42"/>
       <c r="K12" s="43"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="39" t="s">
         <v>58</v>
       </c>
@@ -1839,18 +1842,17 @@
         <v>45798</v>
       </c>
       <c r="E13" s="12">
-        <f t="shared" ref="E13" si="0">186.68-48</f>
-        <v>138.68</v>
+        <v>46.7</v>
       </c>
       <c r="F13" s="12">
-        <v>47.51</v>
+        <v>46.32</v>
       </c>
       <c r="G13" s="12"/>
       <c r="I13" s="20">
         <v>45946</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -1861,7 +1863,7 @@
       <c r="D14" s="20"/>
       <c r="E14" s="21">
         <f>SUM(SUBTOTAL(109,E3:E13)+F13)</f>
-        <v>186.19</v>
+        <v>93.02000000000001</v>
       </c>
       <c r="F14" s="21"/>
       <c r="G14" s="21">
@@ -1875,19 +1877,19 @@
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>106</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D15" s="20"/>
       <c r="I15" s="20"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D16" s="20"/>
       <c r="I16" s="20"/>
     </row>
-    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1908,12 +1910,12 @@
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
     </row>
-    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B18" s="57">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="C18" s="2">
         <v>70</v>
@@ -1921,19 +1923,17 @@
       <c r="D18" s="2">
         <v>40</v>
       </c>
-      <c r="E18" s="60">
-        <v>70</v>
-      </c>
+      <c r="E18" s="60"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="22"/>
       <c r="J18" s="23">
         <f>SUM(B18:I18)</f>
-        <v>615</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="55"/>
@@ -1942,509 +1942,509 @@
       <c r="H19" s="2"/>
       <c r="I19" s="20"/>
     </row>
-    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D20" s="12"/>
       <c r="H20" s="56" t="s">
         <v>37</v>
       </c>
       <c r="I20" s="25">
         <f>+H14+J14+G14</f>
-        <v>452</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D21" s="12"/>
       <c r="H21" s="26" t="s">
         <v>38</v>
       </c>
       <c r="I21" s="25">
         <f>+J18-H14-G14</f>
-        <v>269</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D22" s="20"/>
       <c r="H22" s="27" t="s">
         <v>54</v>
       </c>
       <c r="I22" s="25">
         <f>+I21-J14</f>
-        <v>163</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D23" s="12"/>
       <c r="I23" s="20"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D24" s="12"/>
       <c r="I24" s="20"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D25" s="12"/>
       <c r="I25" s="20"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D26" s="12"/>
       <c r="I26" s="20"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D27" s="12"/>
       <c r="I27" s="20"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D28" s="12"/>
       <c r="I28" s="20"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D29" s="12"/>
       <c r="I29" s="20"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D30" s="11"/>
       <c r="I30" s="20"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D31" s="20"/>
       <c r="I31" s="20"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D32" s="11"/>
       <c r="I32" s="20"/>
     </row>
-    <row r="33" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D33" s="11"/>
       <c r="I33" s="20"/>
     </row>
-    <row r="34" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D34" s="11"/>
       <c r="I34" s="20"/>
     </row>
-    <row r="35" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D35" s="11"/>
       <c r="I35" s="20"/>
     </row>
-    <row r="36" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D36" s="11"/>
       <c r="I36" s="20"/>
     </row>
-    <row r="37" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D37" s="11"/>
       <c r="I37" s="20"/>
     </row>
-    <row r="38" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D38" s="11"/>
       <c r="I38" s="20"/>
     </row>
-    <row r="39" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D39" s="11"/>
       <c r="I39" s="20"/>
     </row>
-    <row r="40" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D40" s="11"/>
       <c r="I40" s="20"/>
     </row>
-    <row r="41" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D41" s="20"/>
       <c r="I41" s="20"/>
     </row>
-    <row r="42" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D42" s="12"/>
       <c r="I42" s="20"/>
     </row>
-    <row r="43" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D43" s="12"/>
       <c r="I43" s="20"/>
     </row>
-    <row r="44" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D44" s="20"/>
       <c r="I44" s="20"/>
     </row>
-    <row r="45" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D45" s="20"/>
       <c r="I45" s="20"/>
     </row>
-    <row r="46" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D46" s="20"/>
       <c r="I46" s="20"/>
     </row>
-    <row r="47" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D47" s="20"/>
       <c r="I47" s="20"/>
     </row>
-    <row r="48" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D48" s="20"/>
       <c r="I48" s="20"/>
     </row>
-    <row r="49" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D49" s="20"/>
       <c r="I49" s="20"/>
     </row>
-    <row r="50" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D50" s="20"/>
       <c r="I50" s="20"/>
     </row>
-    <row r="51" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D51" s="20"/>
       <c r="I51" s="20"/>
     </row>
-    <row r="52" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D52" s="20"/>
       <c r="I52" s="20"/>
     </row>
-    <row r="53" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D53" s="20"/>
       <c r="I53" s="20"/>
     </row>
-    <row r="54" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D54" s="20"/>
       <c r="I54" s="20"/>
     </row>
-    <row r="55" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D55" s="20"/>
       <c r="I55" s="20"/>
     </row>
-    <row r="56" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D56" s="20"/>
       <c r="I56" s="20"/>
     </row>
-    <row r="57" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D57" s="20"/>
       <c r="I57" s="20"/>
     </row>
-    <row r="58" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D58" s="20"/>
       <c r="I58" s="20"/>
     </row>
-    <row r="59" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D59" s="20"/>
       <c r="I59" s="20"/>
     </row>
-    <row r="60" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D60" s="20"/>
       <c r="I60" s="20"/>
     </row>
-    <row r="61" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D61" s="20"/>
       <c r="I61" s="20"/>
     </row>
-    <row r="62" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D62" s="20"/>
       <c r="I62" s="20"/>
     </row>
-    <row r="63" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D63" s="20"/>
       <c r="I63" s="20"/>
     </row>
-    <row r="64" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D64" s="20"/>
       <c r="I64" s="20"/>
     </row>
-    <row r="65" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D65" s="20"/>
       <c r="I65" s="20"/>
     </row>
-    <row r="66" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D66" s="20"/>
       <c r="I66" s="20"/>
     </row>
-    <row r="67" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D67" s="20"/>
       <c r="I67" s="20"/>
     </row>
-    <row r="68" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D68" s="20"/>
       <c r="I68" s="20"/>
     </row>
-    <row r="69" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D69" s="20"/>
       <c r="I69" s="20"/>
     </row>
-    <row r="70" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D70" s="20"/>
       <c r="I70" s="20"/>
     </row>
-    <row r="71" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D71" s="20"/>
       <c r="I71" s="20"/>
     </row>
-    <row r="72" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D72" s="20"/>
       <c r="I72" s="20"/>
     </row>
-    <row r="73" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D73" s="20"/>
       <c r="I73" s="20"/>
     </row>
-    <row r="74" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D74" s="20"/>
       <c r="I74" s="20"/>
     </row>
-    <row r="75" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D75" s="20"/>
       <c r="I75" s="20"/>
     </row>
-    <row r="76" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D76" s="20"/>
       <c r="I76" s="20"/>
     </row>
-    <row r="77" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D77" s="20"/>
       <c r="I77" s="20"/>
     </row>
-    <row r="78" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D78" s="20"/>
       <c r="I78" s="20"/>
     </row>
-    <row r="79" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D79" s="20"/>
       <c r="I79" s="20"/>
     </row>
-    <row r="80" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D80" s="20"/>
       <c r="I80" s="20"/>
     </row>
-    <row r="81" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D81" s="20"/>
       <c r="I81" s="20"/>
     </row>
-    <row r="82" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D82" s="20"/>
       <c r="I82" s="20"/>
     </row>
-    <row r="83" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D83" s="20"/>
       <c r="I83" s="20"/>
     </row>
-    <row r="84" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D84" s="20"/>
       <c r="I84" s="20"/>
     </row>
-    <row r="85" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D85" s="20"/>
       <c r="I85" s="20"/>
     </row>
-    <row r="86" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D86" s="20"/>
       <c r="I86" s="20"/>
     </row>
-    <row r="87" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D87" s="20"/>
       <c r="I87" s="20"/>
     </row>
-    <row r="88" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D88" s="20"/>
       <c r="I88" s="20"/>
     </row>
-    <row r="89" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D89" s="20"/>
       <c r="I89" s="20"/>
     </row>
-    <row r="90" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D90" s="20"/>
       <c r="I90" s="20"/>
     </row>
-    <row r="91" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D91" s="20"/>
       <c r="I91" s="20"/>
     </row>
-    <row r="92" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D92" s="20"/>
       <c r="I92" s="20"/>
     </row>
-    <row r="93" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D93" s="20"/>
       <c r="I93" s="20"/>
     </row>
-    <row r="94" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D94" s="20"/>
       <c r="I94" s="20"/>
     </row>
-    <row r="95" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D95" s="20"/>
       <c r="I95" s="20"/>
     </row>
-    <row r="96" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D96" s="20"/>
       <c r="I96" s="20"/>
     </row>
-    <row r="97" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D97" s="20"/>
       <c r="I97" s="20"/>
     </row>
-    <row r="98" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D98" s="20"/>
       <c r="I98" s="20"/>
     </row>
-    <row r="99" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D99" s="20"/>
       <c r="I99" s="20"/>
     </row>
-    <row r="100" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D100" s="20"/>
       <c r="I100" s="20"/>
     </row>
-    <row r="101" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D101" s="20"/>
       <c r="I101" s="20"/>
     </row>
-    <row r="102" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D102" s="20"/>
       <c r="I102" s="20"/>
     </row>
-    <row r="103" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D103" s="20"/>
       <c r="I103" s="20"/>
     </row>
-    <row r="104" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D104" s="20"/>
       <c r="I104" s="20"/>
     </row>
-    <row r="105" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D105" s="20"/>
       <c r="I105" s="20"/>
     </row>
-    <row r="106" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D106" s="20"/>
       <c r="I106" s="20"/>
     </row>
-    <row r="107" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D107" s="20"/>
       <c r="I107" s="20"/>
     </row>
-    <row r="108" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D108" s="20"/>
       <c r="I108" s="20"/>
     </row>
-    <row r="109" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D109" s="20"/>
       <c r="I109" s="20"/>
     </row>
-    <row r="110" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D110" s="20"/>
       <c r="I110" s="20"/>
     </row>
-    <row r="111" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D111" s="20"/>
       <c r="I111" s="20"/>
     </row>
-    <row r="112" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D112" s="20"/>
       <c r="I112" s="20"/>
     </row>
-    <row r="113" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D113" s="20"/>
       <c r="I113" s="20"/>
     </row>
-    <row r="114" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D114" s="20"/>
       <c r="I114" s="20"/>
     </row>
-    <row r="115" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D115" s="20"/>
       <c r="I115" s="20"/>
     </row>
-    <row r="116" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D116" s="20"/>
       <c r="I116" s="20"/>
     </row>
-    <row r="117" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D117" s="20"/>
       <c r="I117" s="20"/>
     </row>
-    <row r="118" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D118" s="20"/>
       <c r="I118" s="20"/>
     </row>
-    <row r="119" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D119" s="20"/>
       <c r="I119" s="20"/>
     </row>
-    <row r="120" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D120" s="20"/>
       <c r="I120" s="20"/>
     </row>
-    <row r="121" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D121" s="20"/>
       <c r="I121" s="20"/>
     </row>
-    <row r="122" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D122" s="20"/>
       <c r="I122" s="20"/>
     </row>
-    <row r="123" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D123" s="20"/>
       <c r="I123" s="20"/>
     </row>
-    <row r="124" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D124" s="20"/>
       <c r="I124" s="20"/>
     </row>
-    <row r="125" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D125" s="20"/>
       <c r="I125" s="20"/>
     </row>
-    <row r="126" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I126" s="20"/>
     </row>
-    <row r="127" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I127" s="20"/>
     </row>
-    <row r="128" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I128" s="20"/>
     </row>
-    <row r="129" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I129" s="20"/>
     </row>
-    <row r="130" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I130" s="20"/>
     </row>
-    <row r="131" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I131" s="20"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D16">
-    <cfRule type="timePeriod" dxfId="13" priority="37" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="24" priority="37" timePeriod="nextMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0+1)),YEAR(D1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="12" priority="38" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="23" priority="38" timePeriod="thisMonth">
       <formula>AND(MONTH(D1)=MONTH(TODAY()),YEAR(D1)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="11" priority="39" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="22" priority="39" timePeriod="lastMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0-1)),YEAR(D1)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D22:D29 D31 D41:D1048576">
-    <cfRule type="timePeriod" dxfId="10" priority="1" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="21" priority="1" timePeriod="nextMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0+1)),YEAR(D22)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="9" priority="2" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="20" priority="2" timePeriod="thisMonth">
       <formula>AND(MONTH(D22)=MONTH(TODAY()),YEAR(D22)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="8" priority="3" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="19" priority="3" timePeriod="lastMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0-1)),YEAR(D22)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="timePeriod" dxfId="7" priority="40" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="18" priority="40" timePeriod="nextMonth">
       <formula>AND(MONTH(I1)=MONTH(EDATE(TODAY(),0+1)),YEAR(I1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="6" priority="41" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="17" priority="41" timePeriod="thisMonth">
       <formula>AND(MONTH(I1)=MONTH(TODAY()),YEAR(I1)=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="cellIs" dxfId="5" priority="45" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="45" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I22">
-    <cfRule type="cellIs" dxfId="4" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="42" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
-    <cfRule type="cellIs" dxfId="3" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="43" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2459,14 +2459,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAE522B-09DD-4490-9CA8-387DE173331A}">
   <dimension ref="A1:D62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
-    <col min="2" max="3" width="11.44140625" style="12"/>
-    <col min="4" max="4" width="11.88671875" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="11.42578125" style="12"/>
+    <col min="4" max="4" width="11.85546875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
         <v>49</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="47"/>
       <c r="B2" s="11">
         <v>0</v>
@@ -2488,7 +2488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="47">
         <v>46037</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="47">
         <v>46053</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="47">
         <v>46068</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="47">
         <v>46081</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="47">
         <v>46096</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="47">
         <v>46112</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="47">
         <v>46127</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="47">
         <v>46142</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="47">
         <v>46157</v>
       </c>
@@ -2623,7 +2623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="47">
         <v>46173</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="47">
         <v>46188</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="47">
         <v>46203</v>
       </c>
@@ -2664,7 +2664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="47">
         <v>46218</v>
       </c>
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="47">
         <v>46234</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="47">
         <v>46249</v>
       </c>
@@ -2703,7 +2703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="47">
         <v>46265</v>
       </c>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="47">
         <v>46280</v>
       </c>
@@ -2729,7 +2729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="47">
         <v>46295</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="47">
         <v>46310</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="47">
         <v>46326</v>
       </c>
@@ -2768,7 +2768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="47">
         <v>46341</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="47">
         <v>46356</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="47">
         <v>46371</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="46" t="s">
         <v>50</v>
       </c>
@@ -2820,7 +2820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="46" t="s">
         <v>51</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="47">
         <v>46387</v>
       </c>
@@ -2846,7 +2846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="47">
         <v>46402</v>
       </c>
@@ -2859,7 +2859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="47">
         <v>46418</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="47">
         <v>46433</v>
       </c>
@@ -2885,7 +2885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="47">
         <v>46446</v>
       </c>
@@ -2898,7 +2898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="47">
         <v>46461</v>
       </c>
@@ -2911,7 +2911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="47">
         <v>46477</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="47">
         <v>46492</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="47">
         <v>46507</v>
       </c>
@@ -2950,7 +2950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="47">
         <v>46522</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="47">
         <v>46538</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="47">
         <v>46553</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="47">
         <v>46568</v>
       </c>
@@ -3002,7 +3002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="47">
         <v>46583</v>
       </c>
@@ -3015,7 +3015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="47">
         <v>46599</v>
       </c>
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="47">
         <v>46614</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="47">
         <v>46630</v>
       </c>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="47">
         <v>46645</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="47">
         <v>46660</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="47">
         <v>46675</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="47">
         <v>46691</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="47">
         <v>46706</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="47">
         <v>46721</v>
       </c>
@@ -3132,7 +3132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="47">
         <v>46736</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="46" t="s">
         <v>50</v>
       </c>
@@ -3158,7 +3158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="46" t="s">
         <v>51</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="47">
         <v>46752</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="50">
         <f>SUM(B2:B54)</f>
         <v>4610</v>
@@ -3194,34 +3194,34 @@
         <v>550</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
     </row>
-    <row r="57" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="61">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
         <v>-205</v>
       </c>
       <c r="C57" s="62"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B58" s="59"/>
       <c r="C58" s="3"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B59"/>
       <c r="C59" s="3"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
     </row>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5683051E-7897-43DB-A825-42B18935446B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37E486F-157E-4B28-B58A-33CEC352672A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -31,15 +31,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="61">
   <si>
     <t>Totales</t>
   </si>
@@ -717,68 +714,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="21" formatCode="d\-mmm"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -924,6 +859,68 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="d\-mmm"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -943,7 +940,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="13" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="28" tableBorderDxfId="27">
   <autoFilter ref="A2:K14" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K14">
     <sortCondition ref="D3:D14"/>
@@ -951,17 +948,17 @@
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{4E2F1548-5DA7-4ADC-946F-053ED807460A}" name="Banco"/>
     <tableColumn id="2" xr3:uid="{11D77EA7-239F-47E1-9378-FFBA07ACDD06}" name="Tarjeta"/>
-    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="9">
+    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="24">
       <calculatedColumnFormula>186.68-48</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="3" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="23"/>
+    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="18" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1264,7 +1261,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0DE2A9-9218-4E10-883D-DF66D771FC39}">
-  <dimension ref="B1:J37"/>
+  <dimension ref="B1:H37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -1274,7 +1271,7 @@
     <col min="7" max="7" width="3.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
         <v>14</v>
       </c>
@@ -1286,7 +1283,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1296,14 +1293,11 @@
       <c r="D2" s="8">
         <v>60</v>
       </c>
-      <c r="E2" t="s">
-        <v>60</v>
-      </c>
       <c r="F2" s="8">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
@@ -1316,12 +1310,11 @@
       <c r="F3" s="8">
         <v>50</v>
       </c>
-      <c r="J3">
-        <f>482-95-110</f>
-        <v>277</v>
-      </c>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
@@ -1331,14 +1324,11 @@
       <c r="D4" s="8">
         <v>10</v>
       </c>
-      <c r="E4" t="s">
-        <v>60</v>
-      </c>
       <c r="F4" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
@@ -1352,7 +1342,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
@@ -1365,8 +1355,11 @@
       <c r="F6" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>17</v>
       </c>
@@ -1380,7 +1373,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -1391,7 +1384,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -1401,8 +1394,11 @@
       <c r="F9">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -1410,7 +1406,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -1420,8 +1416,11 @@
       <c r="F11">
         <v>25</v>
       </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>9</v>
       </c>
@@ -1431,17 +1430,17 @@
       <c r="D12">
         <v>15</v>
       </c>
-      <c r="E12" t="s">
-        <v>60</v>
-      </c>
       <c r="F12">
         <v>5</v>
       </c>
+      <c r="G12" t="s">
+        <v>60</v>
+      </c>
       <c r="H12">
         <v>8286917</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>10</v>
       </c>
@@ -1449,7 +1448,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>15</v>
       </c>
@@ -1459,8 +1458,11 @@
       <c r="F14">
         <v>31</v>
       </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>59</v>
       </c>
@@ -1469,9 +1471,6 @@
       </c>
       <c r="D15">
         <v>48</v>
-      </c>
-      <c r="E15" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
@@ -1523,16 +1522,16 @@
     <row r="37" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>$C$10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
       <formula>$C$7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
       <formula>$C$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
       <formula>$C$2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1653,14 +1652,12 @@
       <c r="D5" s="20">
         <v>45817</v>
       </c>
-      <c r="H5" s="12">
-        <v>251</v>
-      </c>
+      <c r="H5" s="12"/>
       <c r="I5" s="20">
         <v>46179</v>
       </c>
       <c r="J5" s="12">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="K5" s="31">
         <v>0.27900000000000003</v>
@@ -1683,9 +1680,7 @@
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
-      <c r="H6" s="33">
-        <v>95</v>
-      </c>
+      <c r="H6" s="33"/>
       <c r="I6" s="20">
         <v>46179</v>
       </c>
@@ -1872,12 +1867,12 @@
       </c>
       <c r="H14" s="21">
         <f>SUBTOTAL(109,H3:H13)</f>
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>164</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -1949,7 +1944,7 @@
       </c>
       <c r="I20" s="25">
         <f>+H14+J14+G14</f>
-        <v>510</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1959,7 +1954,7 @@
       </c>
       <c r="I21" s="25">
         <f>+J18-H14-G14</f>
-        <v>192</v>
+        <v>538</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1969,7 +1964,7 @@
       </c>
       <c r="I22" s="25">
         <f>+I21-J14</f>
-        <v>28</v>
+        <v>353</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -2404,47 +2399,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D16">
-    <cfRule type="timePeriod" dxfId="24" priority="37" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="13" priority="37" timePeriod="nextMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0+1)),YEAR(D1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="23" priority="38" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="12" priority="38" timePeriod="thisMonth">
       <formula>AND(MONTH(D1)=MONTH(TODAY()),YEAR(D1)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="22" priority="39" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="11" priority="39" timePeriod="lastMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0-1)),YEAR(D1)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D22:D29 D31 D41:D1048576">
-    <cfRule type="timePeriod" dxfId="21" priority="1" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="10" priority="1" timePeriod="nextMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0+1)),YEAR(D22)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="20" priority="2" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="9" priority="2" timePeriod="thisMonth">
       <formula>AND(MONTH(D22)=MONTH(TODAY()),YEAR(D22)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="19" priority="3" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="8" priority="3" timePeriod="lastMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0-1)),YEAR(D22)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="timePeriod" dxfId="18" priority="40" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="7" priority="40" timePeriod="nextMonth">
       <formula>AND(MONTH(I1)=MONTH(EDATE(TODAY(),0+1)),YEAR(I1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="17" priority="41" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="6" priority="41" timePeriod="thisMonth">
       <formula>AND(MONTH(I1)=MONTH(TODAY()),YEAR(I1)=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="cellIs" dxfId="16" priority="45" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="45" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I22">
-    <cfRule type="cellIs" dxfId="15" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="42" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
-    <cfRule type="cellIs" dxfId="14" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="43" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37E486F-157E-4B28-B58A-33CEC352672A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C2B0160-F323-4599-83F7-783850170140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
   <si>
     <t>Totales</t>
   </si>
@@ -216,9 +216,6 @@
   </si>
   <si>
     <t>Tasa cero Sillones</t>
-  </si>
-  <si>
-    <t>x</t>
   </si>
 </sst>
 </file>
@@ -1310,9 +1307,6 @@
       <c r="F3" s="8">
         <v>50</v>
       </c>
-      <c r="G3" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
@@ -1355,9 +1349,6 @@
       <c r="F6" s="8">
         <v>60</v>
       </c>
-      <c r="G6" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
@@ -1394,9 +1385,6 @@
       <c r="F9">
         <v>10</v>
       </c>
-      <c r="G9" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
@@ -1416,9 +1404,6 @@
       <c r="F11">
         <v>25</v>
       </c>
-      <c r="G11" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
@@ -1433,9 +1418,6 @@
       <c r="F12">
         <v>5</v>
       </c>
-      <c r="G12" t="s">
-        <v>60</v>
-      </c>
       <c r="H12">
         <v>8286917</v>
       </c>
@@ -1457,9 +1439,6 @@
       </c>
       <c r="F14">
         <v>31</v>
-      </c>
-      <c r="G14" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
@@ -1593,28 +1572,30 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="39" t="s">
+    <row r="3" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="40">
+      <c r="C3" s="33">
         <v>2100</v>
       </c>
-      <c r="D3" s="41">
+      <c r="D3" s="53">
         <v>45815</v>
       </c>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="41">
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="53">
         <v>45871</v>
       </c>
-      <c r="J3" s="42"/>
-      <c r="K3" s="43"/>
+      <c r="J3" s="44">
+        <v>51.16</v>
+      </c>
+      <c r="K3" s="54"/>
     </row>
     <row r="4" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="34" t="s">
@@ -1657,7 +1638,7 @@
         <v>46179</v>
       </c>
       <c r="J5" s="12">
-        <v>105</v>
+        <v>233.39</v>
       </c>
       <c r="K5" s="31">
         <v>0.27900000000000003</v>
@@ -1685,7 +1666,7 @@
         <v>46179</v>
       </c>
       <c r="J6" s="12">
-        <v>80</v>
+        <v>74.92</v>
       </c>
       <c r="K6" s="31"/>
     </row>
@@ -1777,7 +1758,9 @@
       <c r="I10" s="20">
         <v>45943</v>
       </c>
-      <c r="J10" s="12"/>
+      <c r="J10" s="12">
+        <v>60</v>
+      </c>
       <c r="K10" s="31"/>
     </row>
     <row r="11" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
@@ -1800,7 +1783,9 @@
       <c r="I11" s="36">
         <v>45885</v>
       </c>
-      <c r="J11" s="37"/>
+      <c r="J11" s="37">
+        <v>40</v>
+      </c>
       <c r="K11" s="38"/>
     </row>
     <row r="12" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
@@ -1872,8 +1857,9 @@
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>185</v>
-      </c>
+        <v>459.46999999999997</v>
+      </c>
+      <c r="N14" s="3"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D15" s="20"/>
@@ -1891,9 +1877,7 @@
       <c r="B17" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="24">
-        <v>46172</v>
-      </c>
+      <c r="C17" s="24"/>
       <c r="D17" s="24">
         <v>46188</v>
       </c>
@@ -1910,22 +1894,22 @@
         <v>35</v>
       </c>
       <c r="B18" s="57">
-        <v>428</v>
-      </c>
-      <c r="C18" s="2">
-        <v>70</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" s="2">
         <v>40</v>
       </c>
-      <c r="E18" s="60"/>
+      <c r="E18" s="60">
+        <v>75</v>
+      </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="22"/>
       <c r="J18" s="23">
         <f>SUM(B18:I18)</f>
-        <v>538</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1944,7 +1928,7 @@
       </c>
       <c r="I20" s="25">
         <f>+H14+J14+G14</f>
-        <v>185</v>
+        <v>459.46999999999997</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1954,7 +1938,7 @@
       </c>
       <c r="I21" s="25">
         <f>+J18-H14-G14</f>
-        <v>538</v>
+        <v>295</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1964,7 +1948,7 @@
       </c>
       <c r="I22" s="25">
         <f>+I21-J14</f>
-        <v>353</v>
+        <v>-164.46999999999997</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -1988,63 +1972,63 @@
       <c r="I27" s="20"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D28" s="12"/>
+      <c r="D28" s="3"/>
       <c r="I28" s="20"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D29" s="12"/>
+      <c r="D29" s="3"/>
       <c r="I29" s="20"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D30" s="11"/>
+      <c r="D30" s="3"/>
       <c r="I30" s="20"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D31" s="20"/>
+      <c r="D31" s="3"/>
       <c r="I31" s="20"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D32" s="11"/>
+      <c r="D32" s="3"/>
       <c r="I32" s="20"/>
     </row>
     <row r="33" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D33" s="11"/>
+      <c r="D33" s="3"/>
       <c r="I33" s="20"/>
     </row>
     <row r="34" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D34" s="11"/>
+      <c r="D34" s="3"/>
       <c r="I34" s="20"/>
     </row>
     <row r="35" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D35" s="11"/>
+      <c r="D35" s="3"/>
       <c r="I35" s="20"/>
     </row>
     <row r="36" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D36" s="11"/>
+      <c r="D36" s="3"/>
       <c r="I36" s="20"/>
     </row>
     <row r="37" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D37" s="11"/>
+      <c r="D37" s="3"/>
       <c r="I37" s="20"/>
     </row>
     <row r="38" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D38" s="11"/>
+      <c r="D38" s="3"/>
       <c r="I38" s="20"/>
     </row>
     <row r="39" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D39" s="11"/>
+      <c r="D39" s="3"/>
       <c r="I39" s="20"/>
     </row>
     <row r="40" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D40" s="11"/>
+      <c r="D40" s="3"/>
       <c r="I40" s="20"/>
     </row>
     <row r="41" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D41" s="20"/>
+      <c r="D41" s="3"/>
       <c r="I41" s="20"/>
     </row>
     <row r="42" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D42" s="12"/>
+      <c r="D42" s="3"/>
       <c r="I42" s="20"/>
     </row>
     <row r="43" spans="4:9" x14ac:dyDescent="0.25">
@@ -2409,7 +2393,7 @@
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0-1)),YEAR(D1)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D22:D29 D31 D41:D1048576">
+  <conditionalFormatting sqref="D22:D27 D43:D1048576">
     <cfRule type="timePeriod" dxfId="10" priority="1" timePeriod="nextMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0+1)),YEAR(D22)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
@@ -3196,7 +3180,7 @@
     <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="61">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
-        <v>-205</v>
+        <v>-175</v>
       </c>
       <c r="C57" s="62"/>
     </row>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C2B0160-F323-4599-83F7-783850170140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A473E8F-F9B1-4678-9A48-243EA6EB8E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
@@ -1437,9 +1437,6 @@
       <c r="C14" t="s">
         <v>43</v>
       </c>
-      <c r="F14">
-        <v>31</v>
-      </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
@@ -1463,7 +1460,7 @@
       </c>
       <c r="F17" s="7">
         <f>SUM(F2:F16)</f>
-        <v>371</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
@@ -1490,7 +1487,7 @@
       </c>
       <c r="F19" s="5">
         <f>F18-F17</f>
-        <v>77</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
@@ -1638,7 +1635,7 @@
         <v>46179</v>
       </c>
       <c r="J5" s="12">
-        <v>233.39</v>
+        <v>270</v>
       </c>
       <c r="K5" s="31">
         <v>0.27900000000000003</v>
@@ -1666,7 +1663,7 @@
         <v>46179</v>
       </c>
       <c r="J6" s="12">
-        <v>74.92</v>
+        <v>140.72</v>
       </c>
       <c r="K6" s="31"/>
     </row>
@@ -1735,7 +1732,9 @@
       <c r="I9" s="53">
         <v>45943</v>
       </c>
-      <c r="J9" s="44"/>
+      <c r="J9" s="44">
+        <v>20</v>
+      </c>
       <c r="K9" s="54"/>
     </row>
     <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
@@ -1758,9 +1757,7 @@
       <c r="I10" s="20">
         <v>45943</v>
       </c>
-      <c r="J10" s="12">
-        <v>60</v>
-      </c>
+      <c r="J10" s="12"/>
       <c r="K10" s="31"/>
     </row>
     <row r="11" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
@@ -1783,9 +1780,7 @@
       <c r="I11" s="36">
         <v>45885</v>
       </c>
-      <c r="J11" s="37">
-        <v>40</v>
-      </c>
+      <c r="J11" s="37"/>
       <c r="K11" s="38"/>
     </row>
     <row r="12" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
@@ -1857,7 +1852,7 @@
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>459.46999999999997</v>
+        <v>481.88</v>
       </c>
       <c r="N14" s="3"/>
     </row>
@@ -1894,14 +1889,14 @@
         <v>35</v>
       </c>
       <c r="B18" s="57">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2">
         <v>40</v>
       </c>
       <c r="E18" s="60">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -1909,7 +1904,7 @@
       <c r="I18" s="22"/>
       <c r="J18" s="23">
         <f>SUM(B18:I18)</f>
-        <v>295</v>
+        <v>330</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1928,7 +1923,7 @@
       </c>
       <c r="I20" s="25">
         <f>+H14+J14+G14</f>
-        <v>459.46999999999997</v>
+        <v>481.88</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1938,7 +1933,7 @@
       </c>
       <c r="I21" s="25">
         <f>+J18-H14-G14</f>
-        <v>295</v>
+        <v>330</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1948,7 +1943,7 @@
       </c>
       <c r="I22" s="25">
         <f>+I21-J14</f>
-        <v>-164.46999999999997</v>
+        <v>-151.88</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -2610,11 +2605,11 @@
         <v>70</v>
       </c>
       <c r="C12" s="11">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D12" t="b">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -3170,7 +3165,7 @@
       </c>
       <c r="C55" s="51">
         <f>SUM(C2:C54)</f>
-        <v>550</v>
+        <v>500</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3180,7 +3175,7 @@
     <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="61">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
-        <v>-175</v>
+        <v>-225</v>
       </c>
       <c r="C57" s="62"/>
     </row>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A473E8F-F9B1-4678-9A48-243EA6EB8E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4FB98D-48EF-4D1C-845F-A610CAC800E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="62">
   <si>
     <t>Totales</t>
   </si>
@@ -216,6 +216,12 @@
   </si>
   <si>
     <t>Tasa cero Sillones</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>com jun</t>
   </si>
 </sst>
 </file>
@@ -1258,7 +1264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0DE2A9-9218-4E10-883D-DF66D771FC39}">
-  <dimension ref="B1:H37"/>
+  <dimension ref="B1:N37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -1268,7 +1274,7 @@
     <col min="7" max="7" width="3.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
         <v>14</v>
       </c>
@@ -1280,7 +1286,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1294,7 +1300,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
@@ -1308,7 +1314,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
@@ -1322,7 +1328,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
@@ -1336,7 +1342,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
@@ -1350,7 +1356,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>17</v>
       </c>
@@ -1360,11 +1366,14 @@
       <c r="D7" s="8">
         <v>100</v>
       </c>
+      <c r="E7" t="s">
+        <v>60</v>
+      </c>
       <c r="F7" s="8">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -1374,8 +1383,11 @@
       <c r="D8" s="58">
         <v>95</v>
       </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -1386,7 +1398,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -1394,7 +1406,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -1405,7 +1417,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>9</v>
       </c>
@@ -1415,6 +1427,9 @@
       <c r="D12">
         <v>15</v>
       </c>
+      <c r="E12" t="s">
+        <v>60</v>
+      </c>
       <c r="F12">
         <v>5</v>
       </c>
@@ -1422,23 +1437,35 @@
         <v>8286917</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>10</v>
       </c>
       <c r="C13" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="L13">
+        <v>95</v>
+      </c>
+      <c r="N13">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="L14">
+        <v>-20</v>
+      </c>
+      <c r="N14">
+        <v>-95</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>59</v>
       </c>
@@ -1447,6 +1474,17 @@
       </c>
       <c r="D15">
         <v>48</v>
+      </c>
+      <c r="E15" t="s">
+        <v>60</v>
+      </c>
+      <c r="L15">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="L16">
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
@@ -1585,13 +1623,13 @@
       <c r="E3" s="44"/>
       <c r="F3" s="44"/>
       <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
+      <c r="H3" s="44">
+        <v>51.16</v>
+      </c>
       <c r="I3" s="53">
-        <v>45871</v>
-      </c>
-      <c r="J3" s="44">
-        <v>51.16</v>
-      </c>
+        <v>46204</v>
+      </c>
+      <c r="J3" s="44"/>
       <c r="K3" s="54"/>
     </row>
     <row r="4" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
@@ -1630,12 +1668,14 @@
       <c r="D5" s="20">
         <v>45817</v>
       </c>
-      <c r="H5" s="12"/>
+      <c r="H5" s="12">
+        <v>280</v>
+      </c>
       <c r="I5" s="20">
-        <v>46179</v>
+        <v>46207</v>
       </c>
       <c r="J5" s="12">
-        <v>270</v>
+        <v>155</v>
       </c>
       <c r="K5" s="31">
         <v>0.27900000000000003</v>
@@ -1658,13 +1698,13 @@
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
-      <c r="H6" s="33"/>
+      <c r="H6" s="12">
+        <v>141</v>
+      </c>
       <c r="I6" s="20">
-        <v>46179</v>
-      </c>
-      <c r="J6" s="12">
-        <v>140.72</v>
-      </c>
+        <v>46209</v>
+      </c>
+      <c r="J6" s="12"/>
       <c r="K6" s="31"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1732,9 +1772,7 @@
       <c r="I9" s="53">
         <v>45943</v>
       </c>
-      <c r="J9" s="44">
-        <v>20</v>
-      </c>
+      <c r="J9" s="44"/>
       <c r="K9" s="54"/>
     </row>
     <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
@@ -1847,12 +1885,12 @@
       </c>
       <c r="H14" s="21">
         <f>SUBTOTAL(109,H3:H13)</f>
-        <v>0</v>
+        <v>472.15999999999997</v>
       </c>
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>481.88</v>
+        <v>155</v>
       </c>
       <c r="N14" s="3"/>
     </row>
@@ -1873,8 +1911,8 @@
         <v>36</v>
       </c>
       <c r="C17" s="24"/>
-      <c r="D17" s="24">
-        <v>46188</v>
+      <c r="D17" s="24" t="s">
+        <v>61</v>
       </c>
       <c r="E17" s="24">
         <v>46203</v>
@@ -1889,11 +1927,11 @@
         <v>35</v>
       </c>
       <c r="B18" s="57">
-        <v>185</v>
+        <v>305</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E18" s="60">
         <v>105</v>
@@ -1904,7 +1942,7 @@
       <c r="I18" s="22"/>
       <c r="J18" s="23">
         <f>SUM(B18:I18)</f>
-        <v>330</v>
+        <v>435</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1923,7 +1961,7 @@
       </c>
       <c r="I20" s="25">
         <f>+H14+J14+G14</f>
-        <v>481.88</v>
+        <v>627.16</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1933,7 +1971,7 @@
       </c>
       <c r="I21" s="25">
         <f>+J18-H14-G14</f>
-        <v>330</v>
+        <v>-37.159999999999968</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1943,7 +1981,7 @@
       </c>
       <c r="I22" s="25">
         <f>+I21-J14</f>
-        <v>-151.88</v>
+        <v>-192.15999999999997</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -2619,7 +2657,9 @@
       <c r="B13" s="11">
         <v>75</v>
       </c>
-      <c r="C13" s="11"/>
+      <c r="C13" s="11">
+        <v>50</v>
+      </c>
       <c r="D13" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
@@ -3165,7 +3205,7 @@
       </c>
       <c r="C55" s="51">
         <f>SUM(C2:C54)</f>
-        <v>500</v>
+        <v>550</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3175,7 +3215,7 @@
     <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="61">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
-        <v>-225</v>
+        <v>-250</v>
       </c>
       <c r="C57" s="62"/>
     </row>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4FB98D-48EF-4D1C-845F-A610CAC800E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E426502-94CE-4761-9D00-D5BC2BD5E062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="62">
   <si>
     <t>Totales</t>
   </si>
@@ -134,9 +134,6 @@
     <t>MASTERCARD</t>
   </si>
   <si>
-    <t>Promerica</t>
-  </si>
-  <si>
     <t>Banco Azul</t>
   </si>
   <si>
@@ -218,10 +215,13 @@
     <t>Tasa cero Sillones</t>
   </si>
   <si>
+    <t>ahrro</t>
+  </si>
+  <si>
     <t>x</t>
   </si>
   <si>
-    <t>com jun</t>
+    <t>COM</t>
   </si>
 </sst>
 </file>
@@ -558,7 +558,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -601,9 +601,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1264,7 +1261,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0DE2A9-9218-4E10-883D-DF66D771FC39}">
-  <dimension ref="B1:N37"/>
+  <dimension ref="B1:L37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -1274,7 +1271,7 @@
     <col min="7" max="7" width="3.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
         <v>14</v>
       </c>
@@ -1286,7 +1283,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1299,13 +1296,16 @@
       <c r="F2" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" s="8">
         <v>50</v>
@@ -1313,8 +1313,11 @@
       <c r="F3" s="8">
         <v>50</v>
       </c>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
@@ -1327,8 +1330,11 @@
       <c r="F4" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
@@ -1342,12 +1348,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" s="8">
         <v>60</v>
@@ -1355,136 +1361,123 @@
       <c r="F6" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" s="8">
         <v>100</v>
       </c>
-      <c r="E7" t="s">
-        <v>60</v>
-      </c>
       <c r="F7" s="8">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="58">
+        <v>43</v>
+      </c>
+      <c r="D8" s="57">
         <v>95</v>
       </c>
-      <c r="E8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F11">
         <v>25</v>
       </c>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L11">
+        <f>185-130</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D12">
         <v>15</v>
       </c>
-      <c r="E12" t="s">
-        <v>60</v>
-      </c>
       <c r="F12">
         <v>5</v>
       </c>
+      <c r="G12" t="s">
+        <v>60</v>
+      </c>
       <c r="H12">
         <v>8286917</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
-      </c>
-      <c r="L13">
-        <v>95</v>
-      </c>
-      <c r="N13">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
-      </c>
-      <c r="L14">
-        <v>-20</v>
-      </c>
-      <c r="N14">
-        <v>-95</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D15">
         <v>48</v>
-      </c>
-      <c r="E15" t="s">
-        <v>60</v>
-      </c>
-      <c r="L15">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="L16">
-        <v>75</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
@@ -1530,7 +1523,7 @@
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1568,7 +1561,7 @@
     <col min="7" max="8" width="16.140625" style="3" customWidth="1"/>
     <col min="9" max="9" width="13.7109375" style="10" customWidth="1"/>
     <col min="10" max="10" width="17.42578125" style="12" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" style="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -1592,72 +1585,70 @@
         <v>28</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="H2" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" s="27" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="32" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="52" t="s">
+      <c r="K2" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="33">
+      <c r="C3" s="32">
         <v>2100</v>
       </c>
-      <c r="D3" s="53">
+      <c r="D3" s="52">
         <v>45815</v>
       </c>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="44">
-        <v>51.16</v>
-      </c>
-      <c r="I3" s="53">
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="52">
         <v>46204</v>
       </c>
-      <c r="J3" s="44"/>
-      <c r="K3" s="54"/>
-    </row>
-    <row r="4" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="34" t="s">
+      <c r="J3" s="43"/>
+      <c r="K3" s="53"/>
+    </row>
+    <row r="4" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="34">
         <v>700</v>
       </c>
-      <c r="D4" s="36">
+      <c r="D4" s="35">
         <v>45817</v>
       </c>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="36">
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="35">
         <v>45872</v>
       </c>
-      <c r="J4" s="37"/>
-      <c r="K4" s="38"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="37"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1668,26 +1659,19 @@
       <c r="D5" s="20">
         <v>45817</v>
       </c>
-      <c r="H5" s="12">
-        <v>280</v>
-      </c>
+      <c r="H5" s="12"/>
       <c r="I5" s="20">
         <v>46207</v>
       </c>
       <c r="J5" s="12">
-        <v>155</v>
-      </c>
-      <c r="K5" s="31">
-        <v>0.27900000000000003</v>
+        <v>262.74</v>
       </c>
       <c r="N5" s="4"/>
     </row>
-    <row r="6" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>32</v>
-      </c>
+    <row r="6" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6"/>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="3">
         <v>840</v>
@@ -1698,18 +1682,18 @@
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
-      <c r="H6" s="12">
-        <v>141</v>
-      </c>
+      <c r="H6" s="12"/>
       <c r="I6" s="20">
         <v>46209</v>
       </c>
-      <c r="J6" s="12"/>
-      <c r="K6" s="31"/>
+      <c r="J6" s="12">
+        <v>94.94</v>
+      </c>
+      <c r="K6" s="30"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
@@ -1725,62 +1709,62 @@
       <c r="I7" s="20">
         <v>45874</v>
       </c>
-      <c r="K7" s="31">
+      <c r="K7" s="30">
         <v>0.18</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="34" t="s">
+    <row r="8" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="34">
         <v>1600</v>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="35">
         <v>45822</v>
       </c>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="36">
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="35">
         <v>45877</v>
       </c>
-      <c r="J8" s="37"/>
-      <c r="K8" s="38"/>
-    </row>
-    <row r="9" spans="1:14" s="52" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="52" t="s">
+      <c r="J8" s="36"/>
+      <c r="K8" s="37"/>
+    </row>
+    <row r="9" spans="1:14" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="32">
         <v>1500</v>
       </c>
-      <c r="D9" s="53">
+      <c r="D9" s="52">
         <v>45826</v>
       </c>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="53">
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="52">
         <v>45943</v>
       </c>
-      <c r="J9" s="44"/>
-      <c r="K9" s="54"/>
-    </row>
-    <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J9" s="43"/>
+      <c r="K9" s="53"/>
+    </row>
+    <row r="10" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C10" s="3">
         <v>2000</v>
@@ -1796,69 +1780,66 @@
         <v>45943</v>
       </c>
       <c r="J10" s="12"/>
-      <c r="K10" s="31"/>
-    </row>
-    <row r="11" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="34" t="s">
+      <c r="K10" s="30"/>
+    </row>
+    <row r="11" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="35">
+      <c r="B11" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="34">
         <v>1500</v>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="35">
         <v>45829</v>
       </c>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="36">
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="35">
         <v>45885</v>
       </c>
-      <c r="J11" s="37"/>
-      <c r="K11" s="38"/>
-    </row>
-    <row r="12" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="B12" s="39" t="s">
+      <c r="J11" s="36"/>
+      <c r="K11" s="37"/>
+    </row>
+    <row r="12" spans="1:14" s="38" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="40">
+      <c r="B12" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="39">
         <v>770</v>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="40">
         <v>45829</v>
       </c>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="41">
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="40">
         <v>45885</v>
       </c>
-      <c r="J12" s="42"/>
-      <c r="K12" s="43"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="42"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" s="39" t="s">
+      <c r="A13" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="41">
+      <c r="B13" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="40">
         <v>45798</v>
       </c>
       <c r="E13" s="12">
-        <v>46.7</v>
-      </c>
-      <c r="F13" s="12">
-        <v>46.32</v>
+        <v>46.42</v>
       </c>
       <c r="G13" s="12"/>
       <c r="I13" s="20">
@@ -1876,7 +1857,7 @@
       <c r="D14" s="20"/>
       <c r="E14" s="21">
         <f>SUM(SUBTOTAL(109,E3:E13)+F13)</f>
-        <v>93.02000000000001</v>
+        <v>46.42</v>
       </c>
       <c r="F14" s="21"/>
       <c r="G14" s="21">
@@ -1885,12 +1866,12 @@
       </c>
       <c r="H14" s="21">
         <f>SUBTOTAL(109,H3:H13)</f>
-        <v>472.15999999999997</v>
+        <v>0</v>
       </c>
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>155</v>
+        <v>357.68</v>
       </c>
       <c r="N14" s="3"/>
     </row>
@@ -1903,124 +1884,149 @@
       <c r="D16" s="20"/>
       <c r="I16" s="20"/>
     </row>
-    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="23">
+        <v>46218</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="23">
+        <v>46233</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+    </row>
+    <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" s="24">
-        <v>46203</v>
-      </c>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-    </row>
-    <row r="18" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="57">
-        <v>305</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2">
-        <v>25</v>
-      </c>
-      <c r="E18" s="60">
-        <v>105</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
+      <c r="B18" s="56">
+        <v>15</v>
+      </c>
+      <c r="C18" s="2">
+        <v>42</v>
+      </c>
+      <c r="D18" s="59">
+        <v>100</v>
+      </c>
+      <c r="E18" s="59">
+        <v>108</v>
+      </c>
+      <c r="F18" s="2">
+        <v>100</v>
+      </c>
+      <c r="G18" s="59"/>
       <c r="H18" s="2"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="23">
+      <c r="I18" s="2"/>
+      <c r="J18" s="22">
         <f>SUM(B18:I18)</f>
-        <v>435</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="20"/>
     </row>
-    <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D20" s="12"/>
-      <c r="H20" s="56" t="s">
+      <c r="H20" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="I20" s="24">
+        <f>+H14+J14+G14</f>
+        <v>357.68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D21" s="12"/>
+      <c r="H21" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="I20" s="25">
-        <f>+H14+J14+G14</f>
-        <v>627.16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D21" s="12"/>
-      <c r="H21" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="I21" s="25">
+      <c r="I21" s="24">
         <f>+J18-H14-G14</f>
-        <v>-37.159999999999968</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D22" s="20"/>
-      <c r="H22" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="I22" s="25">
+      <c r="H22" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="I22" s="24">
         <f>+I21-J14</f>
-        <v>-192.15999999999997</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7.3199999999999932</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D23" s="12"/>
       <c r="I23" s="20"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D24" s="12"/>
-      <c r="I24" s="20"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E24" s="20"/>
+      <c r="G24" s="30"/>
+      <c r="H24"/>
+      <c r="I24"/>
+      <c r="J24"/>
+      <c r="K24"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D25" s="12"/>
-      <c r="I25" s="20"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E25" s="20"/>
+      <c r="G25" s="30"/>
+      <c r="H25"/>
+      <c r="I25"/>
+      <c r="J25"/>
+      <c r="K25"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D26" s="12"/>
-      <c r="I26" s="20"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E26" s="20"/>
+      <c r="G26" s="30"/>
+      <c r="H26"/>
+      <c r="I26"/>
+      <c r="J26"/>
+      <c r="K26"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D27" s="12"/>
       <c r="I27" s="20"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D28" s="3"/>
       <c r="I28" s="20"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D29" s="3"/>
       <c r="I29" s="20"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D30" s="3"/>
       <c r="I30" s="20"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D31" s="3"/>
       <c r="I31" s="20"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D32" s="3"/>
       <c r="I32" s="20"/>
     </row>
@@ -2437,12 +2443,12 @@
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0-1)),YEAR(D22)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I1048576">
+  <conditionalFormatting sqref="I1:I16 I19:I23 E24:E26 I27:I1048576">
     <cfRule type="timePeriod" dxfId="7" priority="40" timePeriod="nextMonth">
-      <formula>AND(MONTH(I1)=MONTH(EDATE(TODAY(),0+1)),YEAR(I1)=YEAR(EDATE(TODAY(),0+1)))</formula>
+      <formula>AND(MONTH(E1)=MONTH(EDATE(TODAY(),0+1)),YEAR(E1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
     <cfRule type="timePeriod" dxfId="6" priority="41" timePeriod="thisMonth">
-      <formula>AND(MONTH(I1)=MONTH(TODAY()),YEAR(I1)=YEAR(TODAY()))</formula>
+      <formula>AND(MONTH(E1)=MONTH(TODAY()),YEAR(E1)=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
@@ -2479,18 +2485,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" s="48" t="s">
+      <c r="A1" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="48" t="s">
-        <v>53</v>
-      </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
+      <c r="A2" s="46"/>
       <c r="B2" s="11">
         <v>0</v>
       </c>
@@ -2501,7 +2507,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="47">
+      <c r="A3" s="46">
         <v>46037</v>
       </c>
       <c r="B3" s="11">
@@ -2516,7 +2522,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="47">
+      <c r="A4" s="46">
         <v>46053</v>
       </c>
       <c r="B4" s="11">
@@ -2531,7 +2537,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="47">
+      <c r="A5" s="46">
         <v>46068</v>
       </c>
       <c r="B5" s="11">
@@ -2546,7 +2552,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="47">
+      <c r="A6" s="46">
         <v>46081</v>
       </c>
       <c r="B6" s="11">
@@ -2561,7 +2567,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="47">
+      <c r="A7" s="46">
         <v>46096</v>
       </c>
       <c r="B7" s="11">
@@ -2576,7 +2582,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="47">
+      <c r="A8" s="46">
         <v>46112</v>
       </c>
       <c r="B8" s="11">
@@ -2591,7 +2597,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="47">
+      <c r="A9" s="46">
         <v>46127</v>
       </c>
       <c r="B9" s="11">
@@ -2606,7 +2612,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="47">
+      <c r="A10" s="46">
         <v>46142</v>
       </c>
       <c r="B10" s="11">
@@ -2621,7 +2627,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="47">
+      <c r="A11" s="46">
         <v>46157</v>
       </c>
       <c r="B11" s="11">
@@ -2636,7 +2642,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="47">
+      <c r="A12" s="46">
         <v>46173</v>
       </c>
       <c r="B12" s="11">
@@ -2651,7 +2657,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="47">
+      <c r="A13" s="46">
         <v>46188</v>
       </c>
       <c r="B13" s="11">
@@ -2666,7 +2672,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="47">
+      <c r="A14" s="46">
         <v>46203</v>
       </c>
       <c r="B14" s="11">
@@ -2679,7 +2685,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="47">
+      <c r="A15" s="46">
         <v>46218</v>
       </c>
       <c r="B15" s="11">
@@ -2692,7 +2698,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="47">
+      <c r="A16" s="46">
         <v>46234</v>
       </c>
       <c r="B16" s="11">
@@ -2705,7 +2711,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="47">
+      <c r="A17" s="46">
         <v>46249</v>
       </c>
       <c r="B17" s="11">
@@ -2718,7 +2724,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="47">
+      <c r="A18" s="46">
         <v>46265</v>
       </c>
       <c r="B18" s="11">
@@ -2731,7 +2737,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="47">
+      <c r="A19" s="46">
         <v>46280</v>
       </c>
       <c r="B19" s="11">
@@ -2744,7 +2750,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="47">
+      <c r="A20" s="46">
         <v>46295</v>
       </c>
       <c r="B20" s="11">
@@ -2757,7 +2763,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="47">
+      <c r="A21" s="46">
         <v>46310</v>
       </c>
       <c r="B21" s="11">
@@ -2770,7 +2776,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="47">
+      <c r="A22" s="46">
         <v>46326</v>
       </c>
       <c r="B22" s="11">
@@ -2783,7 +2789,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="47">
+      <c r="A23" s="46">
         <v>46341</v>
       </c>
       <c r="B23" s="11">
@@ -2796,7 +2802,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="47">
+      <c r="A24" s="46">
         <v>46356</v>
       </c>
       <c r="B24" s="11">
@@ -2809,7 +2815,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="47">
+      <c r="A25" s="46">
         <v>46371</v>
       </c>
       <c r="B25" s="11">
@@ -2822,8 +2828,8 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="46" t="s">
-        <v>50</v>
+      <c r="A26" s="45" t="s">
+        <v>49</v>
       </c>
       <c r="B26" s="11">
         <v>250</v>
@@ -2835,8 +2841,8 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="46" t="s">
-        <v>51</v>
+      <c r="A27" s="45" t="s">
+        <v>50</v>
       </c>
       <c r="B27" s="11">
         <v>315</v>
@@ -2848,20 +2854,20 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="47">
+      <c r="A28" s="46">
         <v>46387</v>
       </c>
       <c r="B28" s="11">
         <v>70</v>
       </c>
-      <c r="C28" s="49"/>
+      <c r="C28" s="48"/>
       <c r="D28" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="47">
+      <c r="A29" s="46">
         <v>46402</v>
       </c>
       <c r="B29" s="11">
@@ -2874,7 +2880,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="47">
+      <c r="A30" s="46">
         <v>46418</v>
       </c>
       <c r="B30" s="11">
@@ -2887,7 +2893,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="47">
+      <c r="A31" s="46">
         <v>46433</v>
       </c>
       <c r="B31" s="11">
@@ -2900,7 +2906,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="47">
+      <c r="A32" s="46">
         <v>46446</v>
       </c>
       <c r="B32" s="11">
@@ -2913,7 +2919,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="47">
+      <c r="A33" s="46">
         <v>46461</v>
       </c>
       <c r="B33" s="11">
@@ -2926,7 +2932,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="47">
+      <c r="A34" s="46">
         <v>46477</v>
       </c>
       <c r="B34" s="11">
@@ -2939,7 +2945,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="47">
+      <c r="A35" s="46">
         <v>46492</v>
       </c>
       <c r="B35" s="11">
@@ -2952,7 +2958,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="47">
+      <c r="A36" s="46">
         <v>46507</v>
       </c>
       <c r="B36" s="11">
@@ -2965,7 +2971,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="47">
+      <c r="A37" s="46">
         <v>46522</v>
       </c>
       <c r="B37" s="11">
@@ -2978,7 +2984,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="47">
+      <c r="A38" s="46">
         <v>46538</v>
       </c>
       <c r="B38" s="11">
@@ -2991,7 +2997,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="47">
+      <c r="A39" s="46">
         <v>46553</v>
       </c>
       <c r="B39" s="11">
@@ -3004,7 +3010,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="47">
+      <c r="A40" s="46">
         <v>46568</v>
       </c>
       <c r="B40" s="11">
@@ -3017,7 +3023,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="47">
+      <c r="A41" s="46">
         <v>46583</v>
       </c>
       <c r="B41" s="11">
@@ -3030,7 +3036,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="47">
+      <c r="A42" s="46">
         <v>46599</v>
       </c>
       <c r="B42" s="11">
@@ -3043,7 +3049,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="47">
+      <c r="A43" s="46">
         <v>46614</v>
       </c>
       <c r="B43" s="11">
@@ -3056,7 +3062,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="47">
+      <c r="A44" s="46">
         <v>46630</v>
       </c>
       <c r="B44" s="11">
@@ -3069,7 +3075,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="47">
+      <c r="A45" s="46">
         <v>46645</v>
       </c>
       <c r="B45" s="11">
@@ -3082,7 +3088,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="47">
+      <c r="A46" s="46">
         <v>46660</v>
       </c>
       <c r="B46" s="11">
@@ -3095,7 +3101,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="47">
+      <c r="A47" s="46">
         <v>46675</v>
       </c>
       <c r="B47" s="11">
@@ -3108,7 +3114,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="47">
+      <c r="A48" s="46">
         <v>46691</v>
       </c>
       <c r="B48" s="11">
@@ -3121,7 +3127,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="47">
+      <c r="A49" s="46">
         <v>46706</v>
       </c>
       <c r="B49" s="11">
@@ -3134,7 +3140,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="47">
+      <c r="A50" s="46">
         <v>46721</v>
       </c>
       <c r="B50" s="11">
@@ -3147,7 +3153,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="47">
+      <c r="A51" s="46">
         <v>46736</v>
       </c>
       <c r="B51" s="11">
@@ -3160,8 +3166,8 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="46" t="s">
-        <v>50</v>
+      <c r="A52" s="45" t="s">
+        <v>49</v>
       </c>
       <c r="B52" s="11">
         <v>250</v>
@@ -3173,8 +3179,8 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="46" t="s">
-        <v>51</v>
+      <c r="A53" s="45" t="s">
+        <v>50</v>
       </c>
       <c r="B53" s="11">
         <v>315</v>
@@ -3186,24 +3192,24 @@
       </c>
     </row>
     <row r="54" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="47">
+      <c r="A54" s="46">
         <v>46752</v>
       </c>
       <c r="B54" s="11">
         <v>70</v>
       </c>
-      <c r="C54" s="49"/>
+      <c r="C54" s="48"/>
       <c r="D54" t="b">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="50">
+      <c r="B55" s="49">
         <f>SUM(B2:B54)</f>
         <v>4610</v>
       </c>
-      <c r="C55" s="51">
+      <c r="C55" s="50">
         <f>SUM(C2:C54)</f>
         <v>550</v>
       </c>
@@ -3213,14 +3219,14 @@
       <c r="C56" s="3"/>
     </row>
     <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="61">
+      <c r="B57" s="60">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
-        <v>-250</v>
-      </c>
-      <c r="C57" s="62"/>
+        <v>-320</v>
+      </c>
+      <c r="C57" s="61"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B58" s="59"/>
+      <c r="B58" s="58"/>
       <c r="C58" s="3"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E426502-94CE-4761-9D00-D5BC2BD5E062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C7CB13-F352-44C2-BC9A-4A8599CDE459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="61">
   <si>
     <t>Totales</t>
   </si>
@@ -212,16 +212,13 @@
     <t>Cuscatlán</t>
   </si>
   <si>
-    <t>Tasa cero Sillones</t>
-  </si>
-  <si>
     <t>ahrro</t>
   </si>
   <si>
-    <t>x</t>
-  </si>
-  <si>
     <t>COM</t>
+  </si>
+  <si>
+    <t>Tasa Cero</t>
   </si>
 </sst>
 </file>
@@ -1261,7 +1258,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0DE2A9-9218-4E10-883D-DF66D771FC39}">
-  <dimension ref="B1:L37"/>
+  <dimension ref="B1:H37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -1271,7 +1268,7 @@
     <col min="7" max="7" width="3.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
         <v>14</v>
       </c>
@@ -1283,7 +1280,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1296,11 +1293,8 @@
       <c r="F2" s="8">
         <v>60</v>
       </c>
-      <c r="G2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
@@ -1313,11 +1307,8 @@
       <c r="F3" s="8">
         <v>50</v>
       </c>
-      <c r="G3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
@@ -1330,11 +1321,8 @@
       <c r="F4" s="8">
         <v>10</v>
       </c>
-      <c r="G4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
@@ -1348,7 +1336,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
@@ -1361,11 +1349,8 @@
       <c r="F6" s="8">
         <v>60</v>
       </c>
-      <c r="G6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>17</v>
       </c>
@@ -1378,11 +1363,8 @@
       <c r="F7" s="8">
         <v>100</v>
       </c>
-      <c r="G7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -1393,7 +1375,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -1403,11 +1385,8 @@
       <c r="F9">
         <v>10</v>
       </c>
-      <c r="G9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -1415,7 +1394,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -1425,15 +1404,8 @@
       <c r="F11">
         <v>25</v>
       </c>
-      <c r="G11" t="s">
-        <v>60</v>
-      </c>
-      <c r="L11">
-        <f>185-130</f>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>9</v>
       </c>
@@ -1446,14 +1418,11 @@
       <c r="F12">
         <v>5</v>
       </c>
-      <c r="G12" t="s">
-        <v>60</v>
-      </c>
       <c r="H12">
         <v>8286917</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>10</v>
       </c>
@@ -1461,7 +1430,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>15</v>
       </c>
@@ -1469,9 +1438,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
         <v>41</v>
@@ -1895,16 +1864,16 @@
         <v>46218</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17" s="23">
         <v>46233</v>
       </c>
       <c r="F17" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="23" t="s">
         <v>59</v>
-      </c>
-      <c r="G17" s="23" t="s">
-        <v>61</v>
       </c>
       <c r="H17" s="23"/>
       <c r="I17" s="23"/>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C7CB13-F352-44C2-BC9A-4A8599CDE459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1AEAD01-E5B9-4641-92BF-C59DEEFD7098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="64">
   <si>
     <t>Totales</t>
   </si>
@@ -68,9 +71,6 @@
     <t>Luz&amp;agua</t>
   </si>
   <si>
-    <t>Intrafinanciamiento</t>
-  </si>
-  <si>
     <t>GASTOS</t>
   </si>
   <si>
@@ -83,12 +83,6 @@
     <t>actual</t>
   </si>
   <si>
-    <t>Telefono</t>
-  </si>
-  <si>
-    <t>Netflix+Spotify</t>
-  </si>
-  <si>
     <t>Ahorro Obligatorio</t>
   </si>
   <si>
@@ -161,9 +155,6 @@
     <t>Efectivo</t>
   </si>
   <si>
-    <t>PagoTarjeta</t>
-  </si>
-  <si>
     <t>PagoCuenta</t>
   </si>
   <si>
@@ -212,13 +203,34 @@
     <t>Cuscatlán</t>
   </si>
   <si>
-    <t>ahrro</t>
-  </si>
-  <si>
     <t>COM</t>
   </si>
   <si>
-    <t>Tasa Cero</t>
+    <t>incpcdd</t>
+  </si>
+  <si>
+    <t>GASTOS FIJOS</t>
+  </si>
+  <si>
+    <t>AHORROS</t>
+  </si>
+  <si>
+    <t>DEUDA FIJA</t>
+  </si>
+  <si>
+    <t>SERVICIOS</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>TIPO</t>
+  </si>
+  <si>
+    <t>MONTO</t>
+  </si>
+  <si>
+    <t>OCIO</t>
   </si>
 </sst>
 </file>
@@ -555,7 +567,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -677,6 +689,10 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -898,7 +914,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="d\-mmm"/>
+      <numFmt numFmtId="21" formatCode="d\-mmm"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1258,7 +1274,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0DE2A9-9218-4E10-883D-DF66D771FC39}">
-  <dimension ref="B1:H37"/>
+  <dimension ref="B1:K36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -1266,11 +1282,12 @@
     <col min="5" max="5" width="3.140625" customWidth="1"/>
     <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="3.140625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13">
@@ -1279,13 +1296,22 @@
       <c r="F1" s="13">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="62" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" s="62" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" s="62" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D2" s="8">
         <v>60</v>
@@ -1293,13 +1319,24 @@
       <c r="F2" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2" s="11">
+        <f>SUM(D2:F6)</f>
+        <v>400</v>
+      </c>
+      <c r="K2" s="63">
+        <f>100/$J$7*J2/100</f>
+        <v>0.4219409282700422</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D3" s="8">
         <v>50</v>
@@ -1307,13 +1344,24 @@
       <c r="F3" s="8">
         <v>50</v>
       </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" s="11">
+        <f>+D7+F7</f>
+        <v>280</v>
+      </c>
+      <c r="K3" s="63">
+        <f t="shared" ref="K3:K6" si="0">100/$J$7*J3/100</f>
+        <v>0.29535864978902954</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D4" s="8">
         <v>10</v>
@@ -1321,13 +1369,24 @@
       <c r="F4" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I4" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="11">
+        <f>D8</f>
+        <v>95</v>
+      </c>
+      <c r="K4" s="63">
+        <f t="shared" si="0"/>
+        <v>0.10021097046413502</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D5" s="8">
         <v>20</v>
@@ -1335,13 +1394,24 @@
       <c r="F5" s="8">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I5" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="J5" s="11">
+        <f>SUM(D9:F11)</f>
+        <v>55</v>
+      </c>
+      <c r="K5" s="63">
+        <f t="shared" si="0"/>
+        <v>5.8016877637130808E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D6" s="8">
         <v>60</v>
@@ -1349,165 +1419,151 @@
       <c r="F6" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I6" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" s="11">
+        <f>D18+F18</f>
+        <v>118</v>
+      </c>
+      <c r="K6" s="63">
+        <f t="shared" si="0"/>
+        <v>0.12447257383966244</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D7" s="8">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="F7" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="I7" s="62" t="s">
+        <v>60</v>
+      </c>
+      <c r="J7" s="62">
+        <f>SUM(J2:J6)</f>
+        <v>948</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D8" s="57">
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F9">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="F10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>38</v>
+      </c>
+      <c r="D11">
+        <v>15</v>
       </c>
       <c r="F11">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12">
-        <v>15</v>
-      </c>
-      <c r="F12">
         <v>5</v>
       </c>
-      <c r="H12">
+      <c r="H11">
         <v>8286917</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="K12" s="3"/>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B16" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15">
-        <v>48</v>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7">
+        <f>SUM(D2:D15)</f>
+        <v>450</v>
+      </c>
+      <c r="F16" s="7">
+        <f>SUM(F2:F15)</f>
+        <v>380</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7">
-        <f>SUM(D2:D16)</f>
-        <v>458</v>
-      </c>
-      <c r="F17" s="7">
-        <f>SUM(F2:F16)</f>
-        <v>340</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6">
+      <c r="C17" s="6"/>
+      <c r="D17" s="6">
         <f>250+250</f>
         <v>500</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F17" s="6">
         <v>448</v>
       </c>
     </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5">
+        <f>D17-D16</f>
+        <v>50</v>
+      </c>
+      <c r="F18" s="5">
+        <f>F17-F16</f>
+        <v>68</v>
+      </c>
+    </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5">
-        <f>D18-D17</f>
-        <v>42</v>
-      </c>
-      <c r="F19" s="5">
-        <f>F18-F17</f>
-        <v>108</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D20" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="37" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="D19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
-      <formula>$C$10</formula>
+    <cfRule type="cellIs" dxfId="17" priority="46" operator="equal">
+      <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="47" operator="equal">
       <formula>$C$7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="48" operator="equal">
       <formula>$C$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="49" operator="equal">
       <formula>$C$2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1536,45 +1592,45 @@
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="14" t="s">
         <v>19</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="H2" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>22</v>
       </c>
       <c r="J2" s="28" t="s">
         <v>1</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:14" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="51" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B3" s="51" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C3" s="32">
         <v>2100</v>
@@ -1594,10 +1650,10 @@
     </row>
     <row r="4" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C4" s="34">
         <v>700</v>
@@ -1617,10 +1673,10 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3">
         <v>2000</v>
@@ -1628,19 +1684,21 @@
       <c r="D5" s="20">
         <v>45817</v>
       </c>
-      <c r="H5" s="12"/>
+      <c r="H5" s="12">
+        <v>263</v>
+      </c>
       <c r="I5" s="20">
         <v>46207</v>
       </c>
       <c r="J5" s="12">
-        <v>262.74</v>
+        <v>28</v>
       </c>
       <c r="N5" s="4"/>
     </row>
     <row r="6" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C6" s="3">
         <v>840</v>
@@ -1651,21 +1709,21 @@
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
+      <c r="H6" s="12">
+        <v>95</v>
+      </c>
       <c r="I6" s="20">
         <v>46209</v>
       </c>
-      <c r="J6" s="12">
-        <v>94.94</v>
-      </c>
+      <c r="J6" s="12"/>
       <c r="K6" s="30"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3">
         <v>1925</v>
@@ -1684,10 +1742,10 @@
     </row>
     <row r="8" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C8" s="34">
         <v>1600</v>
@@ -1707,10 +1765,10 @@
     </row>
     <row r="9" spans="1:14" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="51" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C9" s="32">
         <v>1500</v>
@@ -1730,10 +1788,10 @@
     </row>
     <row r="10" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C10" s="3">
         <v>2000</v>
@@ -1753,10 +1811,10 @@
     </row>
     <row r="11" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C11" s="34">
         <v>1500</v>
@@ -1776,10 +1834,10 @@
     </row>
     <row r="12" spans="1:14" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C12" s="39">
         <v>770</v>
@@ -1799,10 +1857,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="38" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D13" s="40">
         <v>45798</v>
@@ -1835,12 +1893,12 @@
       </c>
       <c r="H14" s="21">
         <f>SUBTOTAL(109,H3:H13)</f>
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>357.68</v>
+        <v>28</v>
       </c>
       <c r="N14" s="3"/>
     </row>
@@ -1855,54 +1913,48 @@
     </row>
     <row r="17" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C17" s="23">
-        <v>46218</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="23">
         <v>46233</v>
       </c>
-      <c r="F17" s="23" t="s">
-        <v>58</v>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="23">
+        <v>46249</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="H17" s="23"/>
       <c r="I17" s="23"/>
     </row>
     <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B18" s="56">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C18" s="2">
-        <v>42</v>
-      </c>
-      <c r="D18" s="59">
         <v>100</v>
       </c>
+      <c r="D18" s="59"/>
       <c r="E18" s="59">
-        <v>108</v>
-      </c>
-      <c r="F18" s="2">
-        <v>100</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="F18" s="2"/>
       <c r="G18" s="59"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="22">
         <f>SUM(B18:I18)</f>
-        <v>365</v>
+        <v>380</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1917,31 +1969,31 @@
     <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D20" s="12"/>
       <c r="H20" s="55" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I20" s="24">
         <f>+H14+J14+G14</f>
-        <v>357.68</v>
+        <v>386</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D21" s="12"/>
       <c r="H21" s="25" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I21" s="24">
         <f>+J18-H14-G14</f>
-        <v>365</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D22" s="20"/>
       <c r="H22" s="26" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I22" s="24">
         <f>+I21-J14</f>
-        <v>7.3199999999999932</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -2455,13 +2507,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="47" t="s">
         <v>48</v>
-      </c>
-      <c r="B1" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="47" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2798,7 +2850,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="45" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B26" s="11">
         <v>250</v>
@@ -2811,7 +2863,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="45" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B27" s="11">
         <v>315</v>
@@ -3136,7 +3188,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="45" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B52" s="11">
         <v>250</v>
@@ -3149,7 +3201,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="45" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B53" s="11">
         <v>315</v>
@@ -3190,7 +3242,7 @@
     <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="60">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
-        <v>-320</v>
+        <v>-395</v>
       </c>
       <c r="C57" s="61"/>
     </row>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1AEAD01-E5B9-4641-92BF-C59DEEFD7098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{298A6F3C-C8DC-4032-AE61-81C069EB6857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="65">
   <si>
     <t>Totales</t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>OCIO</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -684,15 +687,15 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -724,6 +727,68 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="21" formatCode="d\-mmm"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -872,68 +937,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="21" formatCode="d\-mmm"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -953,7 +956,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="28" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="13" tableBorderDxfId="12">
   <autoFilter ref="A2:K14" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K14">
     <sortCondition ref="D3:D14"/>
@@ -961,17 +964,17 @@
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{4E2F1548-5DA7-4ADC-946F-053ED807460A}" name="Banco"/>
     <tableColumn id="2" xr3:uid="{11D77EA7-239F-47E1-9378-FFBA07ACDD06}" name="Tarjeta"/>
-    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="24">
+    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="9">
       <calculatedColumnFormula>186.68-48</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="23"/>
-    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="18" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="3" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1274,7 +1277,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0DE2A9-9218-4E10-883D-DF66D771FC39}">
-  <dimension ref="B1:K36"/>
+  <dimension ref="B1:M36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -1285,7 +1288,7 @@
     <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
         <v>13</v>
       </c>
@@ -1296,17 +1299,17 @@
       <c r="F1" s="13">
         <v>30</v>
       </c>
-      <c r="I1" s="62" t="s">
+      <c r="I1" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="J1" s="62" t="s">
+      <c r="J1" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="K1" s="62" t="s">
+      <c r="K1" s="60" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1326,12 +1329,12 @@
         <f>SUM(D2:F6)</f>
         <v>400</v>
       </c>
-      <c r="K2" s="63">
+      <c r="K2" s="61">
         <f>100/$J$7*J2/100</f>
         <v>0.4219409282700422</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
@@ -1344,19 +1347,22 @@
       <c r="F3" s="8">
         <v>50</v>
       </c>
+      <c r="G3" t="s">
+        <v>64</v>
+      </c>
       <c r="I3" s="9" t="s">
         <v>57</v>
       </c>
       <c r="J3" s="11">
         <f>+D7+F7</f>
-        <v>280</v>
-      </c>
-      <c r="K3" s="63">
+        <v>0</v>
+      </c>
+      <c r="K3" s="61">
         <f t="shared" ref="K3:K6" si="0">100/$J$7*J3/100</f>
-        <v>0.29535864978902954</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
@@ -1376,12 +1382,12 @@
         <f>D8</f>
         <v>95</v>
       </c>
-      <c r="K4" s="63">
+      <c r="K4" s="61">
         <f t="shared" si="0"/>
         <v>0.10021097046413502</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
@@ -1401,12 +1407,12 @@
         <f>SUM(D9:F11)</f>
         <v>55</v>
       </c>
-      <c r="K5" s="63">
+      <c r="K5" s="61">
         <f t="shared" si="0"/>
         <v>5.8016877637130808E-2</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
@@ -1419,40 +1425,39 @@
       <c r="F6" s="8">
         <v>60</v>
       </c>
+      <c r="G6" t="s">
+        <v>64</v>
+      </c>
       <c r="I6" s="9" t="s">
         <v>63</v>
       </c>
       <c r="J6" s="11">
         <f>D18+F18</f>
-        <v>118</v>
-      </c>
-      <c r="K6" s="63">
+        <v>398</v>
+      </c>
+      <c r="K6" s="61">
         <f t="shared" si="0"/>
-        <v>0.12447257383966244</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+        <v>0.41983122362869196</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="8">
-        <v>140</v>
-      </c>
-      <c r="F7" s="8">
-        <v>140</v>
-      </c>
-      <c r="I7" s="62" t="s">
+      <c r="D7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="I7" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="J7" s="62">
+      <c r="J7" s="60">
         <f>SUM(J2:J6)</f>
         <v>948</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -1463,7 +1468,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>15</v>
       </c>
@@ -1473,8 +1478,14 @@
       <c r="F9">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>64</v>
+      </c>
+      <c r="M9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>8</v>
       </c>
@@ -1484,8 +1495,14 @@
       <c r="F10">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>64</v>
+      </c>
+      <c r="M10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>9</v>
       </c>
@@ -1498,25 +1515,34 @@
       <c r="F11">
         <v>5</v>
       </c>
+      <c r="G11" t="s">
+        <v>64</v>
+      </c>
       <c r="H11">
         <v>8286917</v>
       </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="M11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="K12" s="3"/>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="M12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7">
         <f>SUM(D2:D15)</f>
-        <v>450</v>
+        <v>310</v>
       </c>
       <c r="F16" s="7">
         <f>SUM(F2:F15)</f>
-        <v>380</v>
+        <v>240</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
@@ -1539,11 +1565,11 @@
       <c r="C18" s="5"/>
       <c r="D18" s="5">
         <f>D17-D16</f>
-        <v>50</v>
+        <v>190</v>
       </c>
       <c r="F18" s="5">
         <f>F17-F16</f>
-        <v>68</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
@@ -1554,16 +1580,16 @@
     <row r="36" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="17" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="46" operator="equal">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="47" operator="equal">
       <formula>$C$7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="48" operator="equal">
       <formula>$C$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="49" operator="equal">
       <formula>$C$2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1688,10 +1714,10 @@
         <v>263</v>
       </c>
       <c r="I5" s="20">
-        <v>46207</v>
+        <v>46237</v>
       </c>
       <c r="J5" s="12">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="N5" s="4"/>
     </row>
@@ -1713,9 +1739,11 @@
         <v>95</v>
       </c>
       <c r="I6" s="20">
-        <v>46209</v>
-      </c>
-      <c r="J6" s="12"/>
+        <v>46241</v>
+      </c>
+      <c r="J6" s="12">
+        <v>60</v>
+      </c>
       <c r="K6" s="30"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1898,7 +1926,7 @@
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="N14" s="3"/>
     </row>
@@ -1942,11 +1970,13 @@
         <v>30</v>
       </c>
       <c r="C18" s="2">
-        <v>100</v>
-      </c>
-      <c r="D18" s="59"/>
+        <v>300</v>
+      </c>
+      <c r="D18" s="59">
+        <v>250</v>
+      </c>
       <c r="E18" s="59">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="59"/>
@@ -1954,7 +1984,7 @@
       <c r="I18" s="2"/>
       <c r="J18" s="22">
         <f>SUM(B18:I18)</f>
-        <v>380</v>
+        <v>780</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1973,7 +2003,7 @@
       </c>
       <c r="I20" s="24">
         <f>+H14+J14+G14</f>
-        <v>386</v>
+        <v>488</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1983,7 +2013,7 @@
       </c>
       <c r="I21" s="24">
         <f>+J18-H14-G14</f>
-        <v>22</v>
+        <v>422</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1993,7 +2023,7 @@
       </c>
       <c r="I22" s="24">
         <f>+I21-J14</f>
-        <v>-6</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -2443,47 +2473,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D16">
-    <cfRule type="timePeriod" dxfId="13" priority="37" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="24" priority="37" timePeriod="nextMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0+1)),YEAR(D1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="12" priority="38" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="23" priority="38" timePeriod="thisMonth">
       <formula>AND(MONTH(D1)=MONTH(TODAY()),YEAR(D1)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="11" priority="39" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="22" priority="39" timePeriod="lastMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0-1)),YEAR(D1)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D22:D27 D43:D1048576">
-    <cfRule type="timePeriod" dxfId="10" priority="1" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="21" priority="1" timePeriod="nextMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0+1)),YEAR(D22)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="9" priority="2" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="20" priority="2" timePeriod="thisMonth">
       <formula>AND(MONTH(D22)=MONTH(TODAY()),YEAR(D22)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="8" priority="3" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="19" priority="3" timePeriod="lastMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0-1)),YEAR(D22)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I16 I19:I23 E24:E26 I27:I1048576">
-    <cfRule type="timePeriod" dxfId="7" priority="40" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="18" priority="40" timePeriod="nextMonth">
       <formula>AND(MONTH(E1)=MONTH(EDATE(TODAY(),0+1)),YEAR(E1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="6" priority="41" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="17" priority="41" timePeriod="thisMonth">
       <formula>AND(MONTH(E1)=MONTH(TODAY()),YEAR(E1)=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="cellIs" dxfId="5" priority="45" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="45" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I22">
-    <cfRule type="cellIs" dxfId="4" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="42" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
-    <cfRule type="cellIs" dxfId="3" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="43" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3240,11 +3270,11 @@
       <c r="C56" s="3"/>
     </row>
     <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="60">
+      <c r="B57" s="62">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
-        <v>-395</v>
-      </c>
-      <c r="C57" s="61"/>
+        <v>-465</v>
+      </c>
+      <c r="C57" s="63"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B58" s="58"/>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{298A6F3C-C8DC-4032-AE61-81C069EB6857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19C8E4B-3422-44A8-B07E-3C7B0439ECD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -31,15 +31,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="63">
   <si>
     <t>Totales</t>
   </si>
@@ -201,12 +198,6 @@
   </si>
   <si>
     <t>Cuscatlán</t>
-  </si>
-  <si>
-    <t>COM</t>
-  </si>
-  <si>
-    <t>incpcdd</t>
   </si>
   <si>
     <t>GASTOS FIJOS</t>
@@ -730,68 +721,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="21" formatCode="d\-mmm"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -937,6 +866,68 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="d\-mmm"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -956,7 +947,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="13" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="28" tableBorderDxfId="27">
   <autoFilter ref="A2:K14" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K14">
     <sortCondition ref="D3:D14"/>
@@ -964,17 +955,17 @@
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{4E2F1548-5DA7-4ADC-946F-053ED807460A}" name="Banco"/>
     <tableColumn id="2" xr3:uid="{11D77EA7-239F-47E1-9378-FFBA07ACDD06}" name="Tarjeta"/>
-    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="9">
+    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="24">
       <calculatedColumnFormula>186.68-48</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="3" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="23"/>
+    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="18" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1277,7 +1268,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0DE2A9-9218-4E10-883D-DF66D771FC39}">
-  <dimension ref="B1:M36"/>
+  <dimension ref="B1:N36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -1288,7 +1279,7 @@
     <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
         <v>13</v>
       </c>
@@ -1300,16 +1291,16 @@
         <v>30</v>
       </c>
       <c r="I1" s="60" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J1" s="60" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K1" s="60" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
@@ -1323,7 +1314,7 @@
         <v>60</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J2" s="11">
         <f>SUM(D2:F6)</f>
@@ -1334,7 +1325,7 @@
         <v>0.4219409282700422</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
@@ -1344,14 +1335,14 @@
       <c r="D3" s="8">
         <v>50</v>
       </c>
+      <c r="E3" t="s">
+        <v>62</v>
+      </c>
       <c r="F3" s="8">
         <v>50</v>
       </c>
-      <c r="G3" t="s">
-        <v>64</v>
-      </c>
       <c r="I3" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J3" s="11">
         <f>+D7+F7</f>
@@ -1362,7 +1353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
@@ -1376,7 +1367,7 @@
         <v>10</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J4" s="11">
         <f>D8</f>
@@ -1387,7 +1378,7 @@
         <v>0.10021097046413502</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
@@ -1401,7 +1392,7 @@
         <v>20</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J5" s="11">
         <f>SUM(D9:F11)</f>
@@ -1412,7 +1403,7 @@
         <v>5.8016877637130808E-2</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
@@ -1422,14 +1413,14 @@
       <c r="D6" s="8">
         <v>60</v>
       </c>
+      <c r="E6" t="s">
+        <v>62</v>
+      </c>
       <c r="F6" s="8">
         <v>60</v>
       </c>
-      <c r="G6" t="s">
-        <v>64</v>
-      </c>
       <c r="I6" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J6" s="11">
         <f>D18+F18</f>
@@ -1440,7 +1431,7 @@
         <v>0.41983122362869196</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>14</v>
       </c>
@@ -1450,14 +1441,14 @@
       <c r="D7" s="8"/>
       <c r="F7" s="8"/>
       <c r="I7" s="60" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J7" s="60">
         <f>SUM(J2:J6)</f>
         <v>948</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -1468,7 +1459,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>15</v>
       </c>
@@ -1478,14 +1469,8 @@
       <c r="F9">
         <v>10</v>
       </c>
-      <c r="G9" t="s">
-        <v>64</v>
-      </c>
-      <c r="M9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>8</v>
       </c>
@@ -1495,14 +1480,11 @@
       <c r="F10">
         <v>25</v>
       </c>
-      <c r="G10" t="s">
-        <v>64</v>
-      </c>
-      <c r="M10">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N10">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>9</v>
       </c>
@@ -1512,26 +1494,33 @@
       <c r="D11">
         <v>15</v>
       </c>
+      <c r="E11" t="s">
+        <v>62</v>
+      </c>
       <c r="F11">
         <v>5</v>
       </c>
-      <c r="G11" t="s">
-        <v>64</v>
-      </c>
       <c r="H11">
         <v>8286917</v>
       </c>
-      <c r="M11">
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="K12" s="3"/>
+      <c r="L12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="L13">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K12" s="3"/>
-      <c r="M12">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="L14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
         <v>10</v>
       </c>
@@ -1580,16 +1569,16 @@
     <row r="36" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="28" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="46" operator="equal">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="47" operator="equal">
       <formula>$C$7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="48" operator="equal">
       <formula>$C$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="49" operator="equal">
       <formula>$C$2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1711,13 +1700,14 @@
         <v>45817</v>
       </c>
       <c r="H5" s="12">
-        <v>263</v>
+        <v>80.010000000000005</v>
       </c>
       <c r="I5" s="20">
         <v>46237</v>
       </c>
       <c r="J5" s="12">
-        <v>70</v>
+        <f>101.3-Tabla1[[#This Row],[Cantidad Adeudada]]</f>
+        <v>21.289999999999992</v>
       </c>
       <c r="N5" s="4"/>
     </row>
@@ -1736,14 +1726,12 @@
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
       <c r="H6" s="12">
-        <v>95</v>
+        <v>59.25</v>
       </c>
       <c r="I6" s="20">
         <v>46241</v>
       </c>
-      <c r="J6" s="12">
-        <v>60</v>
-      </c>
+      <c r="J6" s="12"/>
       <c r="K6" s="30"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1894,7 +1882,11 @@
         <v>45798</v>
       </c>
       <c r="E13" s="12">
-        <v>46.42</v>
+        <f>484-Tabla1[[#This Row],[Cuota a largo plazo]]</f>
+        <v>430.23</v>
+      </c>
+      <c r="F13" s="12">
+        <v>53.77</v>
       </c>
       <c r="G13" s="12"/>
       <c r="I13" s="20">
@@ -1911,8 +1903,8 @@
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="21">
-        <f>SUM(SUBTOTAL(109,E3:E13)+F13)</f>
-        <v>46.42</v>
+        <f>+E13+F13</f>
+        <v>484</v>
       </c>
       <c r="F14" s="21"/>
       <c r="G14" s="21">
@@ -1921,12 +1913,12 @@
       </c>
       <c r="H14" s="21">
         <f>SUBTOTAL(109,H3:H13)</f>
-        <v>358</v>
+        <v>139.26</v>
       </c>
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>130</v>
+        <v>21.289999999999992</v>
       </c>
       <c r="N14" s="3"/>
     </row>
@@ -1947,18 +1939,18 @@
         <v>32</v>
       </c>
       <c r="C17" s="23">
-        <v>46233</v>
-      </c>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23" t="s">
-        <v>54</v>
+        <v>46249</v>
+      </c>
+      <c r="D17" s="23">
+        <v>46264</v>
+      </c>
+      <c r="E17" s="23">
+        <v>46280</v>
       </c>
       <c r="F17" s="23">
-        <v>46249</v>
-      </c>
-      <c r="G17" s="23" t="s">
-        <v>55</v>
-      </c>
+        <v>46295</v>
+      </c>
+      <c r="G17" s="23"/>
       <c r="H17" s="23"/>
       <c r="I17" s="23"/>
     </row>
@@ -1966,25 +1958,17 @@
       <c r="A18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="56">
-        <v>30</v>
-      </c>
-      <c r="C18" s="2">
-        <v>300</v>
-      </c>
-      <c r="D18" s="59">
-        <v>250</v>
-      </c>
-      <c r="E18" s="59">
-        <v>200</v>
-      </c>
+      <c r="B18" s="56"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
       <c r="F18" s="2"/>
       <c r="G18" s="59"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="22">
         <f>SUM(B18:I18)</f>
-        <v>780</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2003,7 +1987,7 @@
       </c>
       <c r="I20" s="24">
         <f>+H14+J14+G14</f>
-        <v>488</v>
+        <v>160.54999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2013,7 +1997,7 @@
       </c>
       <c r="I21" s="24">
         <f>+J18-H14-G14</f>
-        <v>422</v>
+        <v>-139.26</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2023,7 +2007,7 @@
       </c>
       <c r="I22" s="24">
         <f>+I21-J14</f>
-        <v>292</v>
+        <v>-160.54999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -2473,47 +2457,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D16">
-    <cfRule type="timePeriod" dxfId="24" priority="37" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="13" priority="37" timePeriod="nextMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0+1)),YEAR(D1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="23" priority="38" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="12" priority="38" timePeriod="thisMonth">
       <formula>AND(MONTH(D1)=MONTH(TODAY()),YEAR(D1)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="22" priority="39" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="11" priority="39" timePeriod="lastMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0-1)),YEAR(D1)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D22:D27 D43:D1048576">
-    <cfRule type="timePeriod" dxfId="21" priority="1" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="10" priority="1" timePeriod="nextMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0+1)),YEAR(D22)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="20" priority="2" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="9" priority="2" timePeriod="thisMonth">
       <formula>AND(MONTH(D22)=MONTH(TODAY()),YEAR(D22)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="19" priority="3" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="8" priority="3" timePeriod="lastMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0-1)),YEAR(D22)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I16 I19:I23 E24:E26 I27:I1048576">
-    <cfRule type="timePeriod" dxfId="18" priority="40" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="7" priority="40" timePeriod="nextMonth">
       <formula>AND(MONTH(E1)=MONTH(EDATE(TODAY(),0+1)),YEAR(E1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="17" priority="41" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="6" priority="41" timePeriod="thisMonth">
       <formula>AND(MONTH(E1)=MONTH(TODAY()),YEAR(E1)=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="cellIs" dxfId="16" priority="45" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="45" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I22">
-    <cfRule type="cellIs" dxfId="15" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="42" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
-    <cfRule type="cellIs" dxfId="14" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="43" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19C8E4B-3422-44A8-B07E-3C7B0439ECD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A1D365-38FE-4ED8-BF6C-A45BAB7DCF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -721,6 +724,68 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="21" formatCode="d\-mmm"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -866,68 +931,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="d\-mmm"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -947,7 +950,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="28" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="13" tableBorderDxfId="12">
   <autoFilter ref="A2:K14" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K14">
     <sortCondition ref="D3:D14"/>
@@ -955,17 +958,17 @@
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{4E2F1548-5DA7-4ADC-946F-053ED807460A}" name="Banco"/>
     <tableColumn id="2" xr3:uid="{11D77EA7-239F-47E1-9378-FFBA07ACDD06}" name="Tarjeta"/>
-    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="24">
+    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="9">
       <calculatedColumnFormula>186.68-48</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="23"/>
-    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="18" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="3" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1569,16 +1572,16 @@
     <row r="36" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="17" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="46" operator="equal">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="47" operator="equal">
       <formula>$C$7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="48" operator="equal">
       <formula>$C$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="49" operator="equal">
       <formula>$C$2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1653,8 +1656,13 @@
       <c r="D3" s="52">
         <v>45815</v>
       </c>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
+      <c r="E3" s="12">
+        <f>484-Tabla1[[#This Row],[Cuota a largo plazo]]</f>
+        <v>430.23</v>
+      </c>
+      <c r="F3" s="12">
+        <v>53.77</v>
+      </c>
       <c r="G3" s="32"/>
       <c r="H3" s="43"/>
       <c r="I3" s="52">
@@ -1703,11 +1711,10 @@
         <v>80.010000000000005</v>
       </c>
       <c r="I5" s="20">
-        <v>46237</v>
+        <v>46268</v>
       </c>
       <c r="J5" s="12">
-        <f>101.3-Tabla1[[#This Row],[Cantidad Adeudada]]</f>
-        <v>21.289999999999992</v>
+        <v>178.99</v>
       </c>
       <c r="N5" s="4"/>
     </row>
@@ -1729,7 +1736,7 @@
         <v>59.25</v>
       </c>
       <c r="I6" s="20">
-        <v>46241</v>
+        <v>46272</v>
       </c>
       <c r="J6" s="12"/>
       <c r="K6" s="30"/>
@@ -1881,16 +1888,9 @@
       <c r="D13" s="40">
         <v>45798</v>
       </c>
-      <c r="E13" s="12">
-        <f>484-Tabla1[[#This Row],[Cuota a largo plazo]]</f>
-        <v>430.23</v>
-      </c>
-      <c r="F13" s="12">
-        <v>53.77</v>
-      </c>
       <c r="G13" s="12"/>
       <c r="I13" s="20">
-        <v>45946</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="21">
-        <f>+E13+F13</f>
+        <f>+E3+F3</f>
         <v>484</v>
       </c>
       <c r="F14" s="21"/>
@@ -1918,7 +1918,7 @@
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>21.289999999999992</v>
+        <v>178.99</v>
       </c>
       <c r="N14" s="3"/>
     </row>
@@ -1938,9 +1938,7 @@
       <c r="B17" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="23">
-        <v>46249</v>
-      </c>
+      <c r="C17" s="23"/>
       <c r="D17" s="23">
         <v>46264</v>
       </c>
@@ -1963,12 +1961,14 @@
       <c r="D18" s="59"/>
       <c r="E18" s="59"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="59"/>
+      <c r="G18" s="59">
+        <v>350</v>
+      </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="22">
         <f>SUM(B18:I18)</f>
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="I20" s="24">
         <f>+H14+J14+G14</f>
-        <v>160.54999999999998</v>
+        <v>318.25</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="I21" s="24">
         <f>+J18-H14-G14</f>
-        <v>-139.26</v>
+        <v>210.74</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="I22" s="24">
         <f>+I21-J14</f>
-        <v>-160.54999999999998</v>
+        <v>31.75</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -2457,47 +2457,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D16">
-    <cfRule type="timePeriod" dxfId="13" priority="37" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="24" priority="37" timePeriod="nextMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0+1)),YEAR(D1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="12" priority="38" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="23" priority="38" timePeriod="thisMonth">
       <formula>AND(MONTH(D1)=MONTH(TODAY()),YEAR(D1)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="11" priority="39" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="22" priority="39" timePeriod="lastMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0-1)),YEAR(D1)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D22:D27 D43:D1048576">
-    <cfRule type="timePeriod" dxfId="10" priority="1" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="21" priority="1" timePeriod="nextMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0+1)),YEAR(D22)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="9" priority="2" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="20" priority="2" timePeriod="thisMonth">
       <formula>AND(MONTH(D22)=MONTH(TODAY()),YEAR(D22)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="8" priority="3" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="19" priority="3" timePeriod="lastMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0-1)),YEAR(D22)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I16 I19:I23 E24:E26 I27:I1048576">
-    <cfRule type="timePeriod" dxfId="7" priority="40" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="18" priority="40" timePeriod="nextMonth">
       <formula>AND(MONTH(E1)=MONTH(EDATE(TODAY(),0+1)),YEAR(E1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="6" priority="41" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="17" priority="41" timePeriod="thisMonth">
       <formula>AND(MONTH(E1)=MONTH(TODAY()),YEAR(E1)=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="cellIs" dxfId="5" priority="45" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="45" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I22">
-    <cfRule type="cellIs" dxfId="4" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="42" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
-    <cfRule type="cellIs" dxfId="3" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="43" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3256,7 +3256,7 @@
     <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="62">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
-        <v>-465</v>
+        <v>-540</v>
       </c>
       <c r="C57" s="63"/>
     </row>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A1D365-38FE-4ED8-BF6C-A45BAB7DCF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EAAE01D-830D-48AC-B24A-400C4DA4E08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="2" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="65">
   <si>
     <t>Totales</t>
   </si>
@@ -227,7 +227,13 @@
     <t>OCIO</t>
   </si>
   <si>
-    <t>x</t>
+    <t>ISSS</t>
+  </si>
+  <si>
+    <t>% SEG</t>
+  </si>
+  <si>
+    <t>% COMI</t>
   </si>
 </sst>
 </file>
@@ -1338,9 +1344,6 @@
       <c r="D3" s="8">
         <v>50</v>
       </c>
-      <c r="E3" t="s">
-        <v>62</v>
-      </c>
       <c r="F3" s="8">
         <v>50</v>
       </c>
@@ -1349,11 +1352,11 @@
       </c>
       <c r="J3" s="11">
         <f>+D7+F7</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K3" s="61">
         <f t="shared" ref="K3:K6" si="0">100/$J$7*J3/100</f>
-        <v>0</v>
+        <v>0.31645569620253167</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
@@ -1416,9 +1419,6 @@
       <c r="D6" s="8">
         <v>60</v>
       </c>
-      <c r="E6" t="s">
-        <v>62</v>
-      </c>
       <c r="F6" s="8">
         <v>60</v>
       </c>
@@ -1427,11 +1427,11 @@
       </c>
       <c r="J6" s="11">
         <f>D18+F18</f>
-        <v>398</v>
+        <v>98</v>
       </c>
       <c r="K6" s="61">
         <f t="shared" si="0"/>
-        <v>0.41983122362869196</v>
+        <v>0.10337552742616034</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
@@ -1441,8 +1441,12 @@
       <c r="C7" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="F7" s="8"/>
+      <c r="D7" s="8">
+        <v>150</v>
+      </c>
+      <c r="F7" s="8">
+        <v>150</v>
+      </c>
       <c r="I7" s="60" t="s">
         <v>58</v>
       </c>
@@ -1496,9 +1500,6 @@
       </c>
       <c r="D11">
         <v>15</v>
-      </c>
-      <c r="E11" t="s">
-        <v>62</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -1530,11 +1531,11 @@
       <c r="C16" s="7"/>
       <c r="D16" s="7">
         <f>SUM(D2:D15)</f>
-        <v>310</v>
+        <v>460</v>
       </c>
       <c r="F16" s="7">
         <f>SUM(F2:F15)</f>
-        <v>240</v>
+        <v>390</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
@@ -1557,11 +1558,11 @@
       <c r="C18" s="5"/>
       <c r="D18" s="5">
         <f>D17-D16</f>
-        <v>190</v>
+        <v>40</v>
       </c>
       <c r="F18" s="5">
         <f>F17-F16</f>
-        <v>208</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
@@ -1666,7 +1667,7 @@
       <c r="G3" s="32"/>
       <c r="H3" s="43"/>
       <c r="I3" s="52">
-        <v>46204</v>
+        <v>46269</v>
       </c>
       <c r="J3" s="43"/>
       <c r="K3" s="53"/>
@@ -1714,7 +1715,7 @@
         <v>46268</v>
       </c>
       <c r="J5" s="12">
-        <v>178.99</v>
+        <v>198.99</v>
       </c>
       <c r="N5" s="4"/>
     </row>
@@ -1738,7 +1739,9 @@
       <c r="I6" s="20">
         <v>46272</v>
       </c>
-      <c r="J6" s="12"/>
+      <c r="J6" s="12">
+        <v>79.650000000000006</v>
+      </c>
       <c r="K6" s="30"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1918,7 +1921,7 @@
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>178.99</v>
+        <v>278.64</v>
       </c>
       <c r="N14" s="3"/>
     </row>
@@ -1938,18 +1941,24 @@
       <c r="B17" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="23"/>
+      <c r="C17" s="23">
+        <v>46265</v>
+      </c>
       <c r="D17" s="23">
-        <v>46264</v>
+        <v>46280</v>
       </c>
       <c r="E17" s="23">
-        <v>46280</v>
-      </c>
-      <c r="F17" s="23">
         <v>46295</v>
       </c>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23"/>
+      <c r="F17" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="H17" s="23" t="s">
+        <v>64</v>
+      </c>
       <c r="I17" s="23"/>
     </row>
     <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1957,18 +1966,28 @@
         <v>31</v>
       </c>
       <c r="B18" s="56"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="59"/>
-      <c r="F18" s="2"/>
+      <c r="C18" s="2">
+        <v>40</v>
+      </c>
+      <c r="D18" s="59">
+        <v>58</v>
+      </c>
+      <c r="E18" s="59">
+        <v>40</v>
+      </c>
+      <c r="F18" s="2">
+        <v>350</v>
+      </c>
       <c r="G18" s="59">
-        <v>350</v>
-      </c>
-      <c r="H18" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="H18" s="2">
+        <v>70</v>
+      </c>
       <c r="I18" s="2"/>
       <c r="J18" s="22">
         <f>SUM(B18:I18)</f>
-        <v>350</v>
+        <v>718</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1987,7 +2006,7 @@
       </c>
       <c r="I20" s="24">
         <f>+H14+J14+G14</f>
-        <v>318.25</v>
+        <v>417.9</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1997,7 +2016,7 @@
       </c>
       <c r="I21" s="24">
         <f>+J18-H14-G14</f>
-        <v>210.74</v>
+        <v>578.74</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2007,7 +2026,7 @@
       </c>
       <c r="I22" s="24">
         <f>+I21-J14</f>
-        <v>31.75</v>
+        <v>300.10000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -2713,7 +2732,9 @@
       <c r="B14" s="11">
         <v>70</v>
       </c>
-      <c r="C14" s="11"/>
+      <c r="C14" s="11">
+        <v>0</v>
+      </c>
       <c r="D14" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
@@ -2726,7 +2747,9 @@
       <c r="B15" s="11">
         <v>75</v>
       </c>
-      <c r="C15" s="11"/>
+      <c r="C15" s="11">
+        <v>0</v>
+      </c>
       <c r="D15" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
@@ -2739,7 +2762,9 @@
       <c r="B16" s="11">
         <v>70</v>
       </c>
-      <c r="C16" s="11"/>
+      <c r="C16" s="11">
+        <v>0</v>
+      </c>
       <c r="D16" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
@@ -2752,7 +2777,9 @@
       <c r="B17" s="11">
         <v>75</v>
       </c>
-      <c r="C17" s="11"/>
+      <c r="C17" s="11">
+        <v>0</v>
+      </c>
       <c r="D17" t="b">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EAAE01D-830D-48AC-B24A-400C4DA4E08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2405D16D-C5F9-433B-81ED-402E3C2B907C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="2" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -31,15 +31,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="65">
   <si>
     <t>Totales</t>
   </si>
@@ -227,13 +224,13 @@
     <t>OCIO</t>
   </si>
   <si>
-    <t>ISSS</t>
-  </si>
-  <si>
-    <t>% SEG</t>
-  </si>
-  <si>
-    <t>% COMI</t>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Way</t>
+  </si>
+  <si>
+    <t>%Com</t>
   </si>
 </sst>
 </file>
@@ -730,68 +727,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="21" formatCode="d\-mmm"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -937,6 +872,68 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="d\-mmm"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$$-440A]* #,##0.00_-;\-[$$-440A]* #,##0.00_-;_-[$$-440A]* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -956,7 +953,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="13" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}" name="Tabla1" displayName="Tabla1" ref="A2:K14" totalsRowShown="0" headerRowBorderDxfId="28" tableBorderDxfId="27">
   <autoFilter ref="A2:K14" xr:uid="{34D0B394-EFA3-4F1F-B95B-C46D43801A73}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K14">
     <sortCondition ref="D3:D14"/>
@@ -964,17 +961,17 @@
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{4E2F1548-5DA7-4ADC-946F-053ED807460A}" name="Banco"/>
     <tableColumn id="2" xr3:uid="{11D77EA7-239F-47E1-9378-FFBA07ACDD06}" name="Tarjeta"/>
-    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="9">
+    <tableColumn id="3" xr3:uid="{EFA2D810-AA01-4F56-B9AC-1F88A60DCC7F}" name="Monto" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{B3C14A42-22A4-422A-B5B2-35BF05E35EEF}" name="Fecha Corte" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{6869DC75-BE3A-4901-B724-828BF9F9A7D0}" name="Deuda a largo Plazo" dataDxfId="24">
       <calculatedColumnFormula>186.68-48</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="3" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{2810DEE2-032A-4175-802A-5F857D20294D}" name="Cuota a largo plazo" dataDxfId="23"/>
+    <tableColumn id="13" xr3:uid="{F7FEE37A-0726-482F-99D8-F9C07724EC3E}" name="Suscripciones y otros gastos automáticos" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{F6732F4E-388B-4DFE-91E1-BA3615EF330A}" name="Cantidad Adeudada" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{1F40E7A5-C692-4043-8A55-5DC3E0A18EC9}" name="Fecha de pago" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{186BC069-E422-445A-BA99-6BBE52ACA160}" name="Pendiente para siguiente corte" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{ABA9A903-D4C5-4280-9E9A-38F020209A6A}" name="%" dataDxfId="18" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1331,7 +1328,7 @@
       </c>
       <c r="K2" s="61">
         <f>100/$J$7*J2/100</f>
-        <v>0.4219409282700422</v>
+        <v>0.44792833146696531</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
@@ -1347,6 +1344,9 @@
       <c r="F3" s="8">
         <v>50</v>
       </c>
+      <c r="G3" t="s">
+        <v>62</v>
+      </c>
       <c r="I3" s="9" t="s">
         <v>55</v>
       </c>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="K3" s="61">
         <f t="shared" ref="K3:K6" si="0">100/$J$7*J3/100</f>
-        <v>0.31645569620253167</v>
+        <v>0.33594624860022398</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
@@ -1372,6 +1372,9 @@
       <c r="F4" s="8">
         <v>10</v>
       </c>
+      <c r="G4" t="s">
+        <v>62</v>
+      </c>
       <c r="I4" s="9" t="s">
         <v>56</v>
       </c>
@@ -1381,7 +1384,7 @@
       </c>
       <c r="K4" s="61">
         <f t="shared" si="0"/>
-        <v>0.10021097046413502</v>
+        <v>0.10638297872340426</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
@@ -1397,6 +1400,9 @@
       <c r="F5" s="8">
         <v>20</v>
       </c>
+      <c r="G5" t="s">
+        <v>62</v>
+      </c>
       <c r="I5" s="9" t="s">
         <v>57</v>
       </c>
@@ -1406,7 +1412,7 @@
       </c>
       <c r="K5" s="61">
         <f t="shared" si="0"/>
-        <v>5.8016877637130808E-2</v>
+        <v>6.1590145576707729E-2</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
@@ -1422,16 +1428,19 @@
       <c r="F6" s="8">
         <v>60</v>
       </c>
+      <c r="G6" t="s">
+        <v>62</v>
+      </c>
       <c r="I6" s="9" t="s">
         <v>61</v>
       </c>
       <c r="J6" s="11">
         <f>D18+F18</f>
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="K6" s="61">
         <f t="shared" si="0"/>
-        <v>0.10337552742616034</v>
+        <v>4.8152295632698773E-2</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
@@ -1447,12 +1456,15 @@
       <c r="F7" s="8">
         <v>150</v>
       </c>
+      <c r="G7" t="s">
+        <v>62</v>
+      </c>
       <c r="I7" s="60" t="s">
         <v>58</v>
       </c>
       <c r="J7" s="60">
         <f>SUM(J2:J6)</f>
-        <v>948</v>
+        <v>893</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.25">
@@ -1476,6 +1488,9 @@
       <c r="F9">
         <v>10</v>
       </c>
+      <c r="G9" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
@@ -1487,6 +1502,9 @@
       <c r="F10">
         <v>25</v>
       </c>
+      <c r="G10" t="s">
+        <v>62</v>
+      </c>
       <c r="N10">
         <v>226</v>
       </c>
@@ -1504,11 +1522,20 @@
       <c r="F11">
         <v>5</v>
       </c>
+      <c r="G11" t="s">
+        <v>62</v>
+      </c>
       <c r="H11">
         <v>8286917</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12">
+        <v>55</v>
+      </c>
       <c r="K12" s="3"/>
       <c r="L12">
         <v>60</v>
@@ -1535,7 +1562,7 @@
       </c>
       <c r="F16" s="7">
         <f>SUM(F2:F15)</f>
-        <v>390</v>
+        <v>445</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
@@ -1562,7 +1589,7 @@
       </c>
       <c r="F18" s="5">
         <f>F17-F16</f>
-        <v>58</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
@@ -1573,16 +1600,16 @@
     <row r="36" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="28" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="46" operator="equal">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="47" operator="equal">
       <formula>$C$7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="48" operator="equal">
       <formula>$C$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="49" operator="equal">
       <formula>$C$2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1708,14 +1735,12 @@
       <c r="D5" s="20">
         <v>45817</v>
       </c>
-      <c r="H5" s="12">
-        <v>80.010000000000005</v>
-      </c>
+      <c r="H5" s="12"/>
       <c r="I5" s="20">
         <v>46268</v>
       </c>
       <c r="J5" s="12">
-        <v>198.99</v>
+        <v>116.66</v>
       </c>
       <c r="N5" s="4"/>
     </row>
@@ -1733,14 +1758,12 @@
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
-      <c r="H6" s="12">
-        <v>59.25</v>
-      </c>
+      <c r="H6" s="12"/>
       <c r="I6" s="20">
         <v>46272</v>
       </c>
       <c r="J6" s="12">
-        <v>79.650000000000006</v>
+        <v>38.9</v>
       </c>
       <c r="K6" s="30"/>
     </row>
@@ -1857,6 +1880,7 @@
       </c>
       <c r="J11" s="36"/>
       <c r="K11" s="37"/>
+      <c r="M11" s="34"/>
     </row>
     <row r="12" spans="1:14" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
@@ -1916,12 +1940,12 @@
       </c>
       <c r="H14" s="21">
         <f>SUBTOTAL(109,H3:H13)</f>
-        <v>139.26</v>
+        <v>0</v>
       </c>
       <c r="I14" s="21"/>
       <c r="J14" s="21">
         <f>SUBTOTAL(109,J3:J13)</f>
-        <v>278.64</v>
+        <v>155.56</v>
       </c>
       <c r="N14" s="3"/>
     </row>
@@ -1941,53 +1965,41 @@
       <c r="B17" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="23">
-        <v>46265</v>
-      </c>
+      <c r="C17" s="23"/>
       <c r="D17" s="23">
         <v>46280</v>
       </c>
       <c r="E17" s="23">
         <v>46295</v>
       </c>
-      <c r="F17" s="23" t="s">
-        <v>62</v>
-      </c>
+      <c r="F17" s="23"/>
       <c r="G17" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="H17" s="23" t="s">
         <v>64</v>
       </c>
+      <c r="H17" s="23"/>
       <c r="I17" s="23"/>
     </row>
     <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="56"/>
-      <c r="C18" s="2">
+      <c r="B18" s="56">
+        <v>170</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="59">
         <v>40</v>
       </c>
-      <c r="D18" s="59">
-        <v>58</v>
-      </c>
       <c r="E18" s="59">
-        <v>40</v>
-      </c>
-      <c r="F18" s="2">
-        <v>350</v>
-      </c>
-      <c r="G18" s="59">
-        <v>160</v>
-      </c>
-      <c r="H18" s="2">
-        <v>70</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="22">
         <f>SUM(B18:I18)</f>
-        <v>718</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2006,7 +2018,7 @@
       </c>
       <c r="I20" s="24">
         <f>+H14+J14+G14</f>
-        <v>417.9</v>
+        <v>155.56</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2016,7 +2028,7 @@
       </c>
       <c r="I21" s="24">
         <f>+J18-H14-G14</f>
-        <v>578.74</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2026,7 +2038,7 @@
       </c>
       <c r="I22" s="24">
         <f>+I21-J14</f>
-        <v>300.10000000000002</v>
+        <v>59.44</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -2476,47 +2488,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D16">
-    <cfRule type="timePeriod" dxfId="24" priority="37" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="13" priority="37" timePeriod="nextMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0+1)),YEAR(D1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="23" priority="38" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="12" priority="38" timePeriod="thisMonth">
       <formula>AND(MONTH(D1)=MONTH(TODAY()),YEAR(D1)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="22" priority="39" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="11" priority="39" timePeriod="lastMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0-1)),YEAR(D1)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D22:D27 D43:D1048576">
-    <cfRule type="timePeriod" dxfId="21" priority="1" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="10" priority="1" timePeriod="nextMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0+1)),YEAR(D22)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="20" priority="2" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="9" priority="2" timePeriod="thisMonth">
       <formula>AND(MONTH(D22)=MONTH(TODAY()),YEAR(D22)=YEAR(TODAY()))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="19" priority="3" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="8" priority="3" timePeriod="lastMonth">
       <formula>AND(MONTH(D22)=MONTH(EDATE(TODAY(),0-1)),YEAR(D22)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I16 I19:I23 E24:E26 I27:I1048576">
-    <cfRule type="timePeriod" dxfId="18" priority="40" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="7" priority="40" timePeriod="nextMonth">
       <formula>AND(MONTH(E1)=MONTH(EDATE(TODAY(),0+1)),YEAR(E1)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="17" priority="41" timePeriod="thisMonth">
+    <cfRule type="timePeriod" dxfId="6" priority="41" timePeriod="thisMonth">
       <formula>AND(MONTH(E1)=MONTH(TODAY()),YEAR(E1)=YEAR(TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="cellIs" dxfId="16" priority="45" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="45" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I22">
-    <cfRule type="cellIs" dxfId="15" priority="42" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="42" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
-    <cfRule type="cellIs" dxfId="14" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="43" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2792,10 +2804,12 @@
       <c r="B18" s="11">
         <v>70</v>
       </c>
-      <c r="C18" s="11"/>
+      <c r="C18" s="11">
+        <v>150</v>
+      </c>
       <c r="D18" t="b">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -3273,7 +3287,7 @@
       </c>
       <c r="C55" s="50">
         <f>SUM(C2:C54)</f>
-        <v>550</v>
+        <v>700</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3283,7 +3297,7 @@
     <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="62">
         <f ca="1">IFERROR(SUMIFS(C2:C54,A2:A54,"&lt;="&amp;TODAY()),0)-IFERROR(SUMIFS(B2:B54,A2:A54,"&lt;="&amp;TODAY()),0)</f>
-        <v>-540</v>
+        <v>-460</v>
       </c>
       <c r="C57" s="63"/>
     </row>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2405D16D-C5F9-433B-81ED-402E3C2B907C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE8BD3D-8F42-495D-ACEF-46ED81E6B5D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB526614-3037-4115-BDD6-0ED9B92D9E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="64">
   <si>
     <t>Totales</t>
   </si>
@@ -222,9 +222,6 @@
   </si>
   <si>
     <t>OCIO</t>
-  </si>
-  <si>
-    <t>x</t>
   </si>
   <si>
     <t>Way</t>
@@ -1328,7 +1325,7 @@
       </c>
       <c r="K2" s="61">
         <f>100/$J$7*J2/100</f>
-        <v>0.44792833146696531</v>
+        <v>0.44742729306487694</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
@@ -1344,9 +1341,6 @@
       <c r="F3" s="8">
         <v>50</v>
       </c>
-      <c r="G3" t="s">
-        <v>62</v>
-      </c>
       <c r="I3" s="9" t="s">
         <v>55</v>
       </c>
@@ -1356,7 +1350,7 @@
       </c>
       <c r="K3" s="61">
         <f t="shared" ref="K3:K6" si="0">100/$J$7*J3/100</f>
-        <v>0.33594624860022398</v>
+        <v>0.33557046979865773</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
@@ -1372,9 +1366,6 @@
       <c r="F4" s="8">
         <v>10</v>
       </c>
-      <c r="G4" t="s">
-        <v>62</v>
-      </c>
       <c r="I4" s="9" t="s">
         <v>56</v>
       </c>
@@ -1384,7 +1375,7 @@
       </c>
       <c r="K4" s="61">
         <f t="shared" si="0"/>
-        <v>0.10638297872340426</v>
+        <v>0.10626398210290827</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
@@ -1400,9 +1391,6 @@
       <c r="F5" s="8">
         <v>20</v>
       </c>
-      <c r="G5" t="s">
-        <v>62</v>
-      </c>
       <c r="I5" s="9" t="s">
         <v>57</v>
       </c>
@@ -1412,7 +1400,7 @@
       </c>
       <c r="K5" s="61">
         <f t="shared" si="0"/>
-        <v>6.1590145576707729E-2</v>
+        <v>6.1521252796420581E-2</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
@@ -1428,19 +1416,16 @@
       <c r="F6" s="8">
         <v>60</v>
       </c>
-      <c r="G6" t="s">
-        <v>62</v>
-      </c>
       <c r="I6" s="9" t="s">
         <v>61</v>
       </c>
       <c r="J6" s="11">
         <f>D18+F18</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K6" s="61">
         <f t="shared" si="0"/>
-        <v>4.8152295632698773E-2</v>
+        <v>4.9217002237136459E-2</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
@@ -1456,15 +1441,12 @@
       <c r="F7" s="8">
         <v>150</v>
       </c>
-      <c r="G7" t="s">
-        <v>62</v>
-      </c>
       <c r="I7" s="60" t="s">
         <v>58</v>
       </c>
       <c r="J7" s="60">
         <f>SUM(J2:J6)</f>
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.25">
@@ -1488,9 +1470,6 @@
       <c r="F9">
         <v>10</v>
       </c>
-      <c r="G9" t="s">
-        <v>62</v>
-      </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
@@ -1502,9 +1481,6 @@
       <c r="F10">
         <v>25</v>
       </c>
-      <c r="G10" t="s">
-        <v>62</v>
-      </c>
       <c r="N10">
         <v>226</v>
       </c>
@@ -1522,19 +1498,16 @@
       <c r="F11">
         <v>5</v>
       </c>
-      <c r="G11" t="s">
-        <v>62</v>
-      </c>
       <c r="H11">
         <v>8286917</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F12">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12">
@@ -1562,7 +1535,7 @@
       </c>
       <c r="F16" s="7">
         <f>SUM(F2:F15)</f>
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
@@ -1589,7 +1562,7 @@
       </c>
       <c r="F18" s="5">
         <f>F17-F16</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
@@ -1974,7 +1947,7 @@
       </c>
       <c r="F17" s="23"/>
       <c r="G17" s="23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H17" s="23"/>
       <c r="I17" s="23"/>
@@ -2809,7 +2782,7 @@
       </c>
       <c r="D18" t="b">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
